--- a/examples/ex010.PVT.xlsx
+++ b/examples/ex010.PVT.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\unifloc_vba\examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unifloc\unifloc_vba\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF1CB34-BE2C-4482-9845-2117489513B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="графики от давления" sheetId="1" r:id="rId1"/>
@@ -46,7 +47,7 @@
     <definedName name="Начало">'графики от давления'!$C$22</definedName>
     <definedName name="Температура">'графики от давления'!$C$26</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -58,6 +59,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -351,7 +354,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -479,37 +482,37 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -592,7 +595,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -618,7 +620,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -760,40 +762,40 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.40799738531524365</c:v>
+                  <c:v>0.40799738531524399</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.2876798732693953</c:v>
+                  <c:v>7.2876798732693988</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.871341736906061</c:v>
+                  <c:v>15.871341736906073</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25.364647959839644</c:v>
+                  <c:v>25.364647959839669</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>35.514409899723034</c:v>
+                  <c:v>35.514409899723063</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46.186737869660284</c:v>
+                  <c:v>46.186737869660327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>57.297169628895659</c:v>
+                  <c:v>57.297169628895695</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>68.786981354050553</c:v>
+                  <c:v>68.78698135405061</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>80.61270806753825</c:v>
+                  <c:v>80.612708067538293</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>92.740735470779853</c:v>
+                  <c:v>92.74073547077991</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>105.1442067038592</c:v>
+                  <c:v>105.14420670385927</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>117.80111687961006</c:v>
+                  <c:v>117.80111687961013</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>120</c:v>
@@ -905,7 +907,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1033,7 +1034,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1114,7 +1114,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1223,7 +1222,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1427,46 +1425,46 @@
                   <c:v>1.1677607082700996</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.1681208648753281</c:v>
+                  <c:v>1.1681208648753278</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.1653095028377118</c:v>
+                  <c:v>1.1653095028377116</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.1629022995124061</c:v>
+                  <c:v>1.1629022995124059</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.1608179512669565</c:v>
+                  <c:v>1.1608179512669563</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.158995590664182</c:v>
+                  <c:v>1.1589955906641818</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.1573887453687508</c:v>
+                  <c:v>1.1573887453687506</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.1559613203126462</c:v>
+                  <c:v>1.155961320312646</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.154684854379308</c:v>
+                  <c:v>1.1546848543793078</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.1535366036244399</c:v>
+                  <c:v>1.1535366036244397</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.1524981743992879</c:v>
+                  <c:v>1.1524981743992877</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.1515545307250845</c:v>
+                  <c:v>1.1515545307250843</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.1506932615900212</c:v>
+                  <c:v>1.1506932615900209</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.1499040320855165</c:v>
+                  <c:v>1.1499040320855163</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.149178166728744</c:v>
+                  <c:v>1.1491781667287437</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1610,82 +1608,82 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>1.0708724189280916</c:v>
+                  <c:v>1.0708724189280914</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.6109856165750726E-2</c:v>
+                  <c:v>9.610985616575074E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.9471364513937736E-2</c:v>
+                  <c:v>4.947136451393775E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.2889633443549199E-2</c:v>
+                  <c:v>3.2889633443549185E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.4380684165360093E-2</c:v>
+                  <c:v>2.4380684165360097E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9205142672414868E-2</c:v>
+                  <c:v>1.9205142672414865E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.5732975062920214E-2</c:v>
+                  <c:v>1.5732975062920217E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3252751759032448E-2</c:v>
+                  <c:v>1.3252751759032443E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.1403718927349827E-2</c:v>
+                  <c:v>1.1403718927349822E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.9825502937632253E-3</c:v>
+                  <c:v>9.9825502937632201E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>8.8651544161101083E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.9709595167177984E-3</c:v>
+                  <c:v>7.9709595167177967E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>7.2450472603989326E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.6485393070144045E-3</c:v>
+                  <c:v>6.6485393070144037E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>6.1530936470736543E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.7375767199946684E-3</c:v>
+                  <c:v>5.7375767199946692E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.385951121139803E-3</c:v>
+                  <c:v>5.3859511211398012E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>5.0858769654652343E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.8277520838183943E-3</c:v>
+                  <c:v>4.8277520838183926E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.604033785957304E-3</c:v>
+                  <c:v>4.6040337859573023E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.4087482379972188E-3</c:v>
+                  <c:v>4.4087482379972179E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>4.2371289485194606E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.0853464950866506E-3</c:v>
+                  <c:v>4.0853464950866497E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3.9503041209294218E-3</c:v>
+                  <c:v>3.950304120929421E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>3.8294816963589679E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3.7208156688107053E-3</c:v>
+                  <c:v>3.720815668810704E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1829,13 +1827,13 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>1.0096706043181007</c:v>
+                  <c:v>1.0096706043181005</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.0095813961309568</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0094816652760843</c:v>
+                  <c:v>1.0094816652760841</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1.0093714117534831</c:v>
@@ -1844,43 +1842,43 @@
                   <c:v>1.0092506355631534</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0091193367050952</c:v>
+                  <c:v>1.009119336705095</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1.0089775151793081</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0088251709857927</c:v>
+                  <c:v>1.0088251709857925</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0086623041245486</c:v>
+                  <c:v>1.0086623041245484</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.008488914595576</c:v>
+                  <c:v>1.0084889145955758</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0083050023988747</c:v>
+                  <c:v>1.0083050023988744</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>1.0081105675344446</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0079056100022863</c:v>
+                  <c:v>1.0079056100022861</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1.007690129802399</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.0074641269347835</c:v>
+                  <c:v>1.0074641269347833</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.0072276013994392</c:v>
+                  <c:v>1.007227601399439</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>1.0069805531963663</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.0067229823255648</c:v>
+                  <c:v>1.0067229823255646</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>1.0064548887870346</c:v>
@@ -1895,16 +1893,16 @@
                   <c:v>1.0055874721650728</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.0052772879556284</c:v>
+                  <c:v>1.0052772879556282</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.0049565810784553</c:v>
+                  <c:v>1.0049565810784551</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>1.0046253515335535</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.0042835993209234</c:v>
+                  <c:v>1.0042835993209231</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1974,7 +1972,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2188,7 +2185,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2300,7 +2296,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2468,82 +2463,82 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>9.7713156529231888</c:v>
+                  <c:v>9.7713156529231906</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.9930993456852466</c:v>
+                  <c:v>6.9930993456852475</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.1397568149463062</c:v>
+                  <c:v>5.1397568149463044</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.9709702064959602</c:v>
+                  <c:v>3.9709702064959589</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.1972861301457325</c:v>
+                  <c:v>3.1972861301457316</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.6582574292633616</c:v>
+                  <c:v>2.6582574292633621</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2.2659362081661159</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.9699222555167235</c:v>
+                  <c:v>1.9699222555167233</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.7398587672578572</c:v>
+                  <c:v>1.7398587672578569</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.556606911111144</c:v>
+                  <c:v>1.5566069111111438</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.4076080220116913</c:v>
+                  <c:v>1.4076080220116909</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.2843310127570022</c:v>
+                  <c:v>1.2843310127570018</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.2926930197501152</c:v>
+                  <c:v>1.2926930197501159</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.3261910177947958</c:v>
+                  <c:v>1.326191017794796</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.3622131528629118</c:v>
+                  <c:v>1.3622131528629122</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.4005814298483223</c:v>
+                  <c:v>1.4005814298483232</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.4411346327141066</c:v>
+                  <c:v>1.4411346327141075</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.4837236136051819</c:v>
+                  <c:v>1.4837236136051828</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.5282077500006936</c:v>
+                  <c:v>1.5282077500006945</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.5744522715735518</c:v>
+                  <c:v>1.5744522715735527</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.6223262473590112</c:v>
+                  <c:v>1.6223262473590123</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.6717010831085291</c:v>
+                  <c:v>1.6717010831085302</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.7224494190043653</c:v>
+                  <c:v>1.7224494190043667</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.7744443457903811</c:v>
+                  <c:v>1.7744443457903813</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.8275588769643218</c:v>
+                  <c:v>1.8275588769643232</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.8816656286382238</c:v>
+                  <c:v>1.8816656286382254</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2687,82 +2682,82 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.82711135330023133</c:v>
+                  <c:v>0.82711135330023045</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.83205590390069484</c:v>
+                  <c:v>0.83205590390069384</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.83711054604977453</c:v>
+                  <c:v>0.83711054604977353</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.84227527974747018</c:v>
+                  <c:v>0.84227527974746919</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.84755010499378214</c:v>
+                  <c:v>0.84755010499378114</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.85293502178871006</c:v>
+                  <c:v>0.85293502178870917</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.85843003013225416</c:v>
+                  <c:v>0.85843003013225316</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.86403513002441446</c:v>
+                  <c:v>0.86403513002441357</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.86975032146519071</c:v>
+                  <c:v>0.86975032146518971</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.87557560445458327</c:v>
+                  <c:v>0.87557560445458216</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.88151097899259179</c:v>
+                  <c:v>0.88151097899259068</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.88755644507921649</c:v>
+                  <c:v>0.88755644507921549</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.89371200271445739</c:v>
+                  <c:v>0.89371200271445617</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.89997765189831436</c:v>
+                  <c:v>0.89997765189831325</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.9063533926307874</c:v>
+                  <c:v>0.90635339263078618</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.91283922491187663</c:v>
+                  <c:v>0.91283922491187541</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.91943514874158194</c:v>
+                  <c:v>0.91943514874158094</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.92614116411990333</c:v>
+                  <c:v>0.92614116411990222</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.9329572710468409</c:v>
+                  <c:v>0.93295727104683968</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.93988346952239465</c:v>
+                  <c:v>0.93988346952239354</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.94691975954656449</c:v>
+                  <c:v>0.94691975954656327</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.9540661411193504</c:v>
+                  <c:v>0.95406614111934906</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.96132261424075238</c:v>
+                  <c:v>0.96132261424075138</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.96868917891077067</c:v>
+                  <c:v>0.96868917891076944</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.97616583512940491</c:v>
+                  <c:v>0.9761658351294038</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.98375258289665535</c:v>
+                  <c:v>0.98375258289665413</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2912,7 +2907,7 @@
                   <c:v>1.1803262208544711E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.1986250575720442E-2</c:v>
+                  <c:v>1.198625057572044E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1.220611654701194E-2</c:v>
@@ -2924,61 +2919,61 @@
                   <c:v>1.2750782199815394E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.3076968510634203E-2</c:v>
+                  <c:v>1.3076968510634199E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3440112930067173E-2</c:v>
+                  <c:v>1.3440112930067171E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.3840188691857097E-2</c:v>
+                  <c:v>1.3840188691857094E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>1.4276159115543989E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.4745918799782596E-2</c:v>
+                  <c:v>1.4745918799782593E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.5246397964708501E-2</c:v>
+                  <c:v>1.5246397964708497E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.5773782410755829E-2</c:v>
+                  <c:v>1.5773782410755825E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.6323793809058018E-2</c:v>
+                  <c:v>1.6323793809058015E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.6891977917657237E-2</c:v>
+                  <c:v>1.6891977917657234E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.7473960164598037E-2</c:v>
+                  <c:v>1.7473960164598033E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.8065644186917872E-2</c:v>
+                  <c:v>1.8065644186917869E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.866334463351299E-2</c:v>
+                  <c:v>1.866334463351298E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.9263857676805881E-2</c:v>
+                  <c:v>1.9263857676805878E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>1.9864480053938104E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.0462990438987645E-2</c:v>
+                  <c:v>2.0462990438987638E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.1057606715007234E-2</c:v>
+                  <c:v>2.1057606715007227E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.164693062048741E-2</c:v>
+                  <c:v>2.1646930620487406E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.222988841787437E-2</c:v>
+                  <c:v>2.222988841787436E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.2805673430647554E-2</c:v>
+                  <c:v>2.2805673430647544E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>2.3373693925737973E-2</c:v>
@@ -3051,7 +3046,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -3258,7 +3252,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3367,7 +3360,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3535,82 +3527,82 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.68450731108914831</c:v>
+                  <c:v>0.68450731108914853</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.6268972740510215</c:v>
+                  <c:v>7.6268972740510206</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.817056436627773</c:v>
+                  <c:v>14.81705643662777</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>22.287265720310746</c:v>
+                  <c:v>22.287265720310756</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30.065604190118247</c:v>
+                  <c:v>30.065604190118243</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38.167901822091984</c:v>
+                  <c:v>38.167901822091991</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46.591315187907213</c:v>
+                  <c:v>46.591315187907206</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>55.310777212770795</c:v>
+                  <c:v>55.310777212770816</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>64.279030785472941</c:v>
+                  <c:v>64.279030785472969</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>73.430133425720598</c:v>
+                  <c:v>73.430133425720641</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>82.685530966942565</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>91.96132516576067</c:v>
+                  <c:v>91.961325165760698</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>101.1753234525675</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>110.25278879326807</c:v>
+                  <c:v>110.25278879326808</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>119.13031753524773</c:v>
+                  <c:v>119.13031753524774</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>127.75776878861171</c:v>
+                  <c:v>127.7577687886117</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>136.09852438558232</c:v>
+                  <c:v>136.09852438558238</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>144.12853574269397</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>151.83464007129285</c:v>
+                  <c:v>151.83464007129291</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>159.21255882955802</c:v>
+                  <c:v>159.21255882955808</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>166.26488073925313</c:v>
+                  <c:v>166.26488073925319</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>172.99921926051653</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>179.42664126080513</c:v>
+                  <c:v>179.42664126080516</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>185.56039675941105</c:v>
+                  <c:v>185.56039675941111</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>191.41493761334542</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>197.00519059421646</c:v>
+                  <c:v>197.00519059421654</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3760,7 +3752,7 @@
                   <c:v>850.07405329425592</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>847.79750461929552</c:v>
+                  <c:v>847.79750461929541</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>844.99285399566725</c:v>
@@ -3775,7 +3767,7 @@
                   <c:v>834.08186937898347</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>829.78712419752674</c:v>
+                  <c:v>829.78712419752685</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>825.23630653349448</c:v>
@@ -3790,46 +3782,46 @@
                   <c:v>810.39768506768735</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>811.52766678915089</c:v>
+                  <c:v>811.52766678915111</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>813.48551409866866</c:v>
+                  <c:v>813.48551409866877</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>815.16942601065591</c:v>
+                  <c:v>815.16942601065614</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>816.63313266766875</c:v>
+                  <c:v>816.63313266766897</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>817.91717555780701</c:v>
+                  <c:v>817.91717555780713</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>819.05272000720345</c:v>
+                  <c:v>819.05272000720367</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>820.06411749452832</c:v>
+                  <c:v>820.06411749452855</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>820.97067126559818</c:v>
+                  <c:v>820.9706712655983</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>821.78788000439624</c:v>
+                  <c:v>821.78788000439636</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>822.52833111349844</c:v>
+                  <c:v>822.52833111349867</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>823.20235360726576</c:v>
+                  <c:v>823.20235360726588</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>823.81850284767563</c:v>
+                  <c:v>823.81850284767575</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>824.38392557049622</c:v>
+                  <c:v>824.38392557049644</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>824.90463832816647</c:v>
+                  <c:v>824.9046383281667</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3976,16 +3968,16 @@
                   <c:v>1089.4642225846567</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1089.5604893429661</c:v>
+                  <c:v>1089.5604893429659</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1089.668131514959</c:v>
+                  <c:v>1089.6681315149592</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1089.7871558389759</c:v>
+                  <c:v>1089.7871558389757</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1089.9175697681967</c:v>
+                  <c:v>1089.9175697681965</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1090.0593814718109</c:v>
@@ -3994,37 +3986,37 @@
                   <c:v>1090.2125998362967</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1090.3772344668146</c:v>
+                  <c:v>1090.3772344668148</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1090.5532956887157</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1090.7407945491616</c:v>
+                  <c:v>1090.7407945491618</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1090.9397428188618</c:v>
+                  <c:v>1090.939742818862</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>1091.1501529939233</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1091.3720382978172</c:v>
+                  <c:v>1091.3720382978174</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1091.6054126834629</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1091.8502908354242</c:v>
+                  <c:v>1091.8502908354244</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1092.1066881722295</c:v>
+                  <c:v>1092.1066881722297</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1092.3746208488046</c:v>
+                  <c:v>1092.3746208488044</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1092.6541057590264</c:v>
+                  <c:v>1092.6541057590266</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>1092.945160538397</c:v>
@@ -4048,7 +4040,7 @@
                   <c:v>1094.9355382291099</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1095.3081388004327</c:v>
+                  <c:v>1095.308138800433</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4118,7 +4110,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -4324,7 +4315,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4438,7 +4428,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4591,67 +4580,67 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>3.9516569619629691</c:v>
+                  <c:v>3.9516569619629709</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.20426525769534</c:v>
+                  <c:v>26.204265257695354</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>65.220275414584904</c:v>
+                  <c:v>65.220275414584947</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>99.659129780601489</c:v>
+                  <c:v>99.65912978060156</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>131.76599936161296</c:v>
+                  <c:v>131.76599936161304</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>162.32793720118292</c:v>
+                  <c:v>162.32793720118303</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>191.74670764006237</c:v>
+                  <c:v>191.74670764006245</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>248.04343216453705</c:v>
+                  <c:v>248.04343216453722</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>301.81267586222066</c:v>
+                  <c:v>301.81267586222083</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>353.67640780212275</c:v>
+                  <c:v>353.67640780212287</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>404.02097397611681</c:v>
+                  <c:v>404.02097397611703</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>453.10848286447026</c:v>
+                  <c:v>453.10848286447049</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>501.12776305350866</c:v>
+                  <c:v>501.12776305350894</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>548.22092849987689</c:v>
+                  <c:v>548.22092849987712</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>594.49855745182049</c:v>
+                  <c:v>594.49855745182083</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>640.04897894804401</c:v>
+                  <c:v>640.04897894804446</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>684.9442641679459</c:v>
+                  <c:v>684.94426416794636</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>729.24425980965975</c:v>
+                  <c:v>729.24425980966021</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>772.99939974004769</c:v>
+                  <c:v>772.99939974004803</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>816.25272295477441</c:v>
+                  <c:v>816.25272295477498</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>859.04135817139502</c:v>
+                  <c:v>859.04135817139559</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4780,64 +4769,64 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>4.7652176471718688</c:v>
+                  <c:v>4.7652176471718679</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.622604514708939</c:v>
+                  <c:v>27.622604514708922</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70.525292114122379</c:v>
+                  <c:v>70.525292114122337</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108.56201380760596</c:v>
+                  <c:v>108.56201380760591</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>142.80213140879411</c:v>
+                  <c:v>142.80213140879403</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>173.89555548851553</c:v>
+                  <c:v>173.89555548851538</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>202.31347221879295</c:v>
+                  <c:v>202.31347221879278</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>252.49547384519579</c:v>
+                  <c:v>252.49547384519565</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>295.46729132686249</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>332.67223073950203</c:v>
+                  <c:v>332.67223073950186</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>365.15217984314586</c:v>
+                  <c:v>365.15217984314569</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>393.69006660795321</c:v>
+                  <c:v>393.69006660795338</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>418.89203273740918</c:v>
+                  <c:v>418.89203273740901</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>441.23836560123277</c:v>
+                  <c:v>441.23836560123243</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>461.11679300751973</c:v>
+                  <c:v>461.1167930075195</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>478.84516848321897</c:v>
+                  <c:v>478.84516848321852</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>494.68745080004754</c:v>
+                  <c:v>494.68745080004715</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>508.86527275976425</c:v>
+                  <c:v>508.86527275976403</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>521.56651174046658</c:v>
+                  <c:v>521.56651174046624</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>532.9517649485374</c:v>
+                  <c:v>532.95176494853706</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>543.15932534142394</c:v>
@@ -4896,7 +4885,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -5014,7 +5002,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -5095,7 +5082,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5127,7 +5113,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -5135,6 +5120,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5214,7 +5200,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5367,67 +5352,67 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>3.9516569619629691</c:v>
+                  <c:v>3.9516569619629709</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.20426525769534</c:v>
+                  <c:v>26.204265257695354</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>65.220275414584904</c:v>
+                  <c:v>65.220275414584947</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>99.659129780601489</c:v>
+                  <c:v>99.65912978060156</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>131.76599936161296</c:v>
+                  <c:v>131.76599936161304</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>162.32793720118292</c:v>
+                  <c:v>162.32793720118303</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>191.74670764006237</c:v>
+                  <c:v>191.74670764006245</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>248.04343216453705</c:v>
+                  <c:v>248.04343216453722</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>301.81267586222066</c:v>
+                  <c:v>301.81267586222083</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>353.67640780212275</c:v>
+                  <c:v>353.67640780212287</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>404.02097397611681</c:v>
+                  <c:v>404.02097397611703</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>453.10848286447026</c:v>
+                  <c:v>453.10848286447049</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>501.12776305350866</c:v>
+                  <c:v>501.12776305350894</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>548.22092849987689</c:v>
+                  <c:v>548.22092849987712</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>594.49855745182049</c:v>
+                  <c:v>594.49855745182083</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>640.04897894804401</c:v>
+                  <c:v>640.04897894804446</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>684.9442641679459</c:v>
+                  <c:v>684.94426416794636</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>729.24425980965975</c:v>
+                  <c:v>729.24425980966021</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>772.99939974004769</c:v>
+                  <c:v>772.99939974004803</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>816.25272295477441</c:v>
+                  <c:v>816.25272295477498</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>859.04135817139502</c:v>
+                  <c:v>859.04135817139559</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5556,64 +5541,64 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>4.7652176471718688</c:v>
+                  <c:v>4.7652176471718679</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.622604514708939</c:v>
+                  <c:v>27.622604514708922</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70.525292114122379</c:v>
+                  <c:v>70.525292114122337</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108.56201380760596</c:v>
+                  <c:v>108.56201380760591</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>142.80213140879411</c:v>
+                  <c:v>142.80213140879403</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>173.89555548851553</c:v>
+                  <c:v>173.89555548851538</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>202.31347221879295</c:v>
+                  <c:v>202.31347221879278</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>252.49547384519579</c:v>
+                  <c:v>252.49547384519565</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>295.46729132686249</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>332.67223073950203</c:v>
+                  <c:v>332.67223073950186</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>365.15217984314586</c:v>
+                  <c:v>365.15217984314569</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>393.69006660795321</c:v>
+                  <c:v>393.69006660795338</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>418.89203273740918</c:v>
+                  <c:v>418.89203273740901</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>441.23836560123277</c:v>
+                  <c:v>441.23836560123243</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>461.11679300751973</c:v>
+                  <c:v>461.1167930075195</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>478.84516848321897</c:v>
+                  <c:v>478.84516848321852</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>494.68745080004754</c:v>
+                  <c:v>494.68745080004715</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>508.86527275976425</c:v>
+                  <c:v>508.86527275976403</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>521.56651174046658</c:v>
+                  <c:v>521.56651174046624</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>532.9517649485374</c:v>
+                  <c:v>532.95176494853706</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>543.15932534142394</c:v>
@@ -5745,64 +5730,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>4.7652176471718688</c:v>
+                  <c:v>4.7652176471718679</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.622604514708939</c:v>
+                  <c:v>27.622604514708922</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70.525292114122365</c:v>
+                  <c:v>70.525292114122337</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108.56201380760596</c:v>
+                  <c:v>108.56201380760591</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>142.80213140879411</c:v>
+                  <c:v>142.80213140879403</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>173.89555548851553</c:v>
+                  <c:v>173.89555548851538</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>202.31347221879295</c:v>
+                  <c:v>202.31347221879278</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>252.49547384519579</c:v>
+                  <c:v>252.49547384519565</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>295.46729132686249</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>332.67223073950203</c:v>
+                  <c:v>332.67223073950191</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>365.15217984314586</c:v>
+                  <c:v>365.15217984314569</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>393.69006660795321</c:v>
+                  <c:v>393.69006660795338</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>418.89203273740918</c:v>
+                  <c:v>418.89203273740895</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>441.23836560123283</c:v>
+                  <c:v>441.23836560123249</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>461.11679300751973</c:v>
+                  <c:v>461.1167930075195</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>478.84516848321897</c:v>
+                  <c:v>478.84516848321852</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>494.68745080004754</c:v>
+                  <c:v>494.68745080004715</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>508.8652727597642</c:v>
+                  <c:v>508.86527275976397</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>521.56651174046658</c:v>
+                  <c:v>521.56651174046613</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>532.9517649485374</c:v>
+                  <c:v>532.95176494853717</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>543.15932534142382</c:v>
@@ -5861,7 +5846,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -5979,7 +5963,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -6060,7 +6043,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6092,7 +6074,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6100,6 +6081,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6179,7 +6161,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6252,64 +6233,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>4.7652176471718688</c:v>
+                  <c:v>4.7652176471718679</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.622604514708939</c:v>
+                  <c:v>27.622604514708922</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70.525292114122365</c:v>
+                  <c:v>70.525292114122337</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108.56201380760596</c:v>
+                  <c:v>108.56201380760591</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>142.80213140879411</c:v>
+                  <c:v>142.80213140879403</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>173.89555548851553</c:v>
+                  <c:v>173.89555548851538</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>202.31347221879295</c:v>
+                  <c:v>202.31347221879278</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>252.49547384519579</c:v>
+                  <c:v>252.49547384519565</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>295.46729132686249</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>332.67223073950203</c:v>
+                  <c:v>332.67223073950191</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>365.15217984314586</c:v>
+                  <c:v>365.15217984314569</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>393.69006660795321</c:v>
+                  <c:v>393.69006660795338</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>418.89203273740918</c:v>
+                  <c:v>418.89203273740895</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>441.23836560123283</c:v>
+                  <c:v>441.23836560123249</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>461.11679300751973</c:v>
+                  <c:v>461.1167930075195</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>478.84516848321897</c:v>
+                  <c:v>478.84516848321852</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>494.68745080004754</c:v>
+                  <c:v>494.68745080004715</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>508.8652727597642</c:v>
+                  <c:v>508.86527275976397</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>521.56651174046658</c:v>
+                  <c:v>521.56651174046613</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>532.9517649485374</c:v>
+                  <c:v>532.95176494853717</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>543.15932534142382</c:v>
@@ -6520,73 +6501,73 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>8.2271659062697899E-2</c:v>
+                  <c:v>8.2271659062691072E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>18.022014659826571</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>28.259056830115654</c:v>
+                  <c:v>28.259056830115661</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>36.880577262600646</c:v>
+                  <c:v>36.880577262600667</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>44.700919980779858</c:v>
+                  <c:v>44.700919980779865</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>52.074681365632486</c:v>
+                  <c:v>52.074681365632507</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>59.2054516936917</c:v>
+                  <c:v>59.205451693691721</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>66.229037764954583</c:v>
+                  <c:v>66.229037764954597</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>73.245164700554881</c:v>
+                  <c:v>73.245164700554909</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>80.332105990458729</c:v>
+                  <c:v>80.332105990458743</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>87.554340117432034</c:v>
+                  <c:v>87.554340117432062</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>94.96693491792567</c:v>
+                  <c:v>94.966934917925684</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>102.61823487507657</c:v>
+                  <c:v>102.61823487507661</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>110.55159866234952</c:v>
+                  <c:v>110.55159866234955</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>118.80719158854971</c:v>
+                  <c:v>118.80719158854976</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>127.42035661422511</c:v>
+                  <c:v>127.42035661422514</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>136.42584203788834</c:v>
+                  <c:v>136.4258420378884</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>145.85583986198873</c:v>
+                  <c:v>145.85583986198881</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>155.74091151119103</c:v>
+                  <c:v>155.74091151119109</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>166.11024348451087</c:v>
+                  <c:v>166.1102434845109</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>176.99184801102425</c:v>
+                  <c:v>176.99184801102427</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>188.41272296709593</c:v>
+                  <c:v>188.4127229670959</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>200.39898108307841</c:v>
+                  <c:v>200.39898108307844</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>212.97595563227983</c:v>
@@ -6656,7 +6637,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -6862,7 +6842,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6894,7 +6873,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -6902,6 +6880,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6981,7 +6960,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7134,67 +7112,67 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>3.9516569619629691</c:v>
+                  <c:v>3.9516569619629709</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.20426525769534</c:v>
+                  <c:v>26.204265257695354</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>65.220275414584904</c:v>
+                  <c:v>65.220275414584947</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>99.659129780601489</c:v>
+                  <c:v>99.65912978060156</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>131.76599936161296</c:v>
+                  <c:v>131.76599936161304</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>162.32793720118292</c:v>
+                  <c:v>162.32793720118303</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>191.74670764006237</c:v>
+                  <c:v>191.74670764006245</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>248.04343216453705</c:v>
+                  <c:v>248.04343216453722</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>301.81267586222066</c:v>
+                  <c:v>301.81267586222083</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>353.67640780212275</c:v>
+                  <c:v>353.67640780212287</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>404.02097397611681</c:v>
+                  <c:v>404.02097397611703</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>453.10848286447026</c:v>
+                  <c:v>453.10848286447049</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>501.12776305350866</c:v>
+                  <c:v>501.12776305350894</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>548.22092849987689</c:v>
+                  <c:v>548.22092849987712</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>594.49855745182049</c:v>
+                  <c:v>594.49855745182083</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>640.04897894804401</c:v>
+                  <c:v>640.04897894804446</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>684.9442641679459</c:v>
+                  <c:v>684.94426416794636</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>729.24425980965975</c:v>
+                  <c:v>729.24425980966021</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>772.99939974004769</c:v>
+                  <c:v>772.99939974004803</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>816.25272295477441</c:v>
+                  <c:v>816.25272295477498</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>859.04135817139502</c:v>
+                  <c:v>859.04135817139559</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7323,64 +7301,64 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>4.7652176471718688</c:v>
+                  <c:v>4.7652176471718679</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.622604514708939</c:v>
+                  <c:v>27.622604514708922</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70.525292114122379</c:v>
+                  <c:v>70.525292114122337</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108.56201380760596</c:v>
+                  <c:v>108.56201380760591</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>142.80213140879411</c:v>
+                  <c:v>142.80213140879403</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>173.89555548851553</c:v>
+                  <c:v>173.89555548851538</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>202.31347221879295</c:v>
+                  <c:v>202.31347221879278</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>252.49547384519579</c:v>
+                  <c:v>252.49547384519565</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>295.46729132686249</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>332.67223073950203</c:v>
+                  <c:v>332.67223073950186</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>365.15217984314586</c:v>
+                  <c:v>365.15217984314569</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>393.69006660795321</c:v>
+                  <c:v>393.69006660795338</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>418.89203273740918</c:v>
+                  <c:v>418.89203273740901</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>441.23836560123277</c:v>
+                  <c:v>441.23836560123243</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>461.11679300751973</c:v>
+                  <c:v>461.1167930075195</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>478.84516848321897</c:v>
+                  <c:v>478.84516848321852</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>494.68745080004754</c:v>
+                  <c:v>494.68745080004715</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>508.86527275976425</c:v>
+                  <c:v>508.86527275976403</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>521.56651174046658</c:v>
+                  <c:v>521.56651174046624</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>532.9517649485374</c:v>
+                  <c:v>532.95176494853706</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>543.15932534142394</c:v>
@@ -7440,16 +7418,16 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>1.0000000000000002</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.11627514475664</c:v>
+                  <c:v>10.116275144756642</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30.027970672961324</c:v>
+                  <c:v>30.027970672961317</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>50.016124941183307</c:v>
+                  <c:v>50.016124941183321</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>70.011337046209462</c:v>
@@ -7458,34 +7436,34 @@
                   <c:v>90.008743154762044</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>110.00711568881246</c:v>
+                  <c:v>110.00711568881245</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>150.00518563484465</c:v>
+                  <c:v>150.00518563484462</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>190.0040793277731</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>230.00336210460028</c:v>
+                  <c:v>230.00336210460026</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>270.00285938923201</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>310.00248746260195</c:v>
+                  <c:v>310.00248746260189</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>350.00220115787874</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>390.00197395933083</c:v>
+                  <c:v>390.00197395933077</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>430.00178927573404</c:v>
+                  <c:v>430.00178927573398</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>470.00163619429253</c:v>
+                  <c:v>470.0016361942927</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>510.00150724273357</c:v>
@@ -7494,13 +7472,13 @@
                   <c:v>550.00139713245892</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>590.0013020151564</c:v>
+                  <c:v>590.00130201515628</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>630.0012190237419</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>670.00114597835807</c:v>
+                  <c:v>670.00114597835829</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7512,67 +7490,67 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>3.9516569619629691</c:v>
+                  <c:v>3.9516569619629709</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.20426525769534</c:v>
+                  <c:v>26.204265257695354</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>65.220275414584904</c:v>
+                  <c:v>65.220275414584947</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>99.659129780601489</c:v>
+                  <c:v>99.65912978060156</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>131.76599936161296</c:v>
+                  <c:v>131.76599936161304</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>162.32793720118292</c:v>
+                  <c:v>162.32793720118303</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>191.74670764006237</c:v>
+                  <c:v>191.74670764006245</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>248.04343216453705</c:v>
+                  <c:v>248.04343216453722</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>301.81267586222066</c:v>
+                  <c:v>301.81267586222083</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>353.67640780212275</c:v>
+                  <c:v>353.67640780212287</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>404.02097397611681</c:v>
+                  <c:v>404.02097397611703</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>453.10848286447026</c:v>
+                  <c:v>453.10848286447049</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>501.12776305350866</c:v>
+                  <c:v>501.12776305350894</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>548.22092849987689</c:v>
+                  <c:v>548.22092849987712</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>594.49855745182049</c:v>
+                  <c:v>594.49855745182083</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>640.04897894804401</c:v>
+                  <c:v>640.04897894804446</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>684.9442641679459</c:v>
+                  <c:v>684.94426416794636</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>729.24425980965975</c:v>
+                  <c:v>729.24425980966021</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>772.99939974004769</c:v>
+                  <c:v>772.99939974004803</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>816.25272295477441</c:v>
+                  <c:v>816.25272295477498</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>859.04135817139502</c:v>
+                  <c:v>859.04135817139559</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7628,7 +7606,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -7746,7 +7723,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -7827,7 +7803,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7859,7 +7834,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -7867,6 +7841,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -13049,8 +13024,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Info"/>
     </sheetNames>
@@ -13384,31 +13362,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1"/>
   <dimension ref="A1:U56"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.15234375" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B5" s="16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
@@ -13416,7 +13394,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
@@ -13424,7 +13402,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
@@ -13432,7 +13410,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
@@ -13440,7 +13418,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -13448,7 +13426,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
@@ -13456,7 +13434,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
@@ -13464,7 +13442,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
@@ -13472,7 +13450,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
@@ -13480,7 +13458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
@@ -13489,17 +13467,17 @@
         <v>{"gamma_gas":0.6,"gamma_oil":0.86,"gamma_wat":1.1,"rsb_m3m3":120,"pb_atma":130,"t_res_C":80,"bob_m3m3":1.2,"muob_cP":0.6,"PVT_corr_set":0}</v>
       </c>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B19" s="15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B22" s="2" t="s">
         <v>15</v>
       </c>
@@ -13507,7 +13485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
@@ -13515,7 +13493,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B24" s="2" t="s">
         <v>17</v>
       </c>
@@ -13523,7 +13501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B25" s="2" t="s">
         <v>18</v>
       </c>
@@ -13532,7 +13510,7 @@
         <v>[1,10.96,20.92,30.88,40.84,50.8,60.76,70.72,80.68,90.64,100.6,110.56,120.52,130.48,140.44,150.4,160.36,170.32,180.28,190.24,200.2,210.16,220.12,230.08,240.04,250]</v>
       </c>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B26" s="2" t="s">
         <v>19</v>
       </c>
@@ -13540,12 +13518,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B28" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B30" s="4" t="s">
         <v>12</v>
       </c>
@@ -13607,7 +13585,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B31" s="7">
         <f t="array" ref="B31:B56">[1]!decode_json(Массив_точек)</f>
         <v>1</v>
@@ -13618,7 +13596,7 @@
       </c>
       <c r="D31" s="8">
         <f t="array" ref="D31">[1]!PVT_rs_m3m3(B31,C31,PVT_json)</f>
-        <v>0.40799738531524365</v>
+        <v>0.40799738531524399</v>
       </c>
       <c r="E31" s="8">
         <f>[1]!PVT_bo_m3m3(B31,C31,PVT_json)</f>
@@ -13626,7 +13604,7 @@
       </c>
       <c r="F31" s="9">
         <f>[1]!PVT_mu_oil_cP(B31,C31,PVT_json)</f>
-        <v>9.7713156529231888</v>
+        <v>9.7713156529231906</v>
       </c>
       <c r="G31" s="10">
         <f>[1]!PVT_mu_gas_cP(B31,C31,PVT_json)</f>
@@ -13634,11 +13612,11 @@
       </c>
       <c r="H31" s="8">
         <f>[1]!PVT_mu_wat_cP(B31,C31,PVT_json)</f>
-        <v>0.82711135330023133</v>
+        <v>0.82711135330023045</v>
       </c>
       <c r="I31" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B31,C31,PVT_json)</f>
-        <v>0.68450731108914831</v>
+        <v>0.68450731108914853</v>
       </c>
       <c r="J31" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B31,C31,PVT_json)</f>
@@ -13650,15 +13628,15 @@
       </c>
       <c r="L31" s="12">
         <f>[1]!PVT_bg_m3m3(B31,C31,PVT_json)</f>
-        <v>1.0708724189280916</v>
+        <v>1.0708724189280914</v>
       </c>
       <c r="M31" s="12">
         <f>[1]!PVT_bw_m3m3(B31,C31,PVT_json)</f>
-        <v>1.0096706043181007</v>
+        <v>1.0096706043181005</v>
       </c>
       <c r="N31" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B31,C31,PVT_json)</f>
-        <v>2.8969477236995007E-2</v>
+        <v>2.8969477236995011E-2</v>
       </c>
       <c r="O31" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B31,C31,PVT_json)</f>
@@ -13670,7 +13648,7 @@
       </c>
       <c r="Q31" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B31,C31,PVT_json)</f>
-        <v>2180.5754923629329</v>
+        <v>2180.5754923629324</v>
       </c>
       <c r="R31" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B31,C31,PVT_json)</f>
@@ -13678,7 +13656,7 @@
       </c>
       <c r="S31" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B31,C31,PVT_json)</f>
-        <v>3.4370661312794921E-5</v>
+        <v>3.4370661312794928E-5</v>
       </c>
       <c r="T31" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B31,C31,PVT_json)</f>
@@ -13686,10 +13664,10 @@
       </c>
       <c r="U31" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B31,C31,PVT_json)</f>
-        <v>1.0016044501325005</v>
+        <v>1.0016044501324981</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B32" s="7">
         <v>10.96</v>
       </c>
@@ -13699,7 +13677,7 @@
       </c>
       <c r="D32" s="8">
         <f t="array" ref="D32">[1]!PVT_rs_m3m3(B32,C32,PVT_json)</f>
-        <v>7.2876798732693953</v>
+        <v>7.2876798732693988</v>
       </c>
       <c r="E32" s="8">
         <f>[1]!PVT_bo_m3m3(B32,C32,PVT_json)</f>
@@ -13707,7 +13685,7 @@
       </c>
       <c r="F32" s="9">
         <f>[1]!PVT_mu_oil_cP(B32,C32,PVT_json)</f>
-        <v>6.9930993456852466</v>
+        <v>6.9930993456852475</v>
       </c>
       <c r="G32" s="10">
         <f>[1]!PVT_mu_gas_cP(B32,C32,PVT_json)</f>
@@ -13715,15 +13693,15 @@
       </c>
       <c r="H32" s="8">
         <f>[1]!PVT_mu_wat_cP(B32,C32,PVT_json)</f>
-        <v>0.83205590390069484</v>
+        <v>0.83205590390069384</v>
       </c>
       <c r="I32" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B32,C32,PVT_json)</f>
-        <v>7.6268972740510215</v>
+        <v>7.6268972740510206</v>
       </c>
       <c r="J32" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B32,C32,PVT_json)</f>
-        <v>1089.5604893429661</v>
+        <v>1089.5604893429659</v>
       </c>
       <c r="K32" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B32,C32,PVT_json)</f>
@@ -13731,7 +13709,7 @@
       </c>
       <c r="L32" s="12">
         <f>[1]!PVT_bg_m3m3(B32,C32,PVT_json)</f>
-        <v>9.6109856165750726E-2</v>
+        <v>9.610985616575074E-2</v>
       </c>
       <c r="M32" s="12">
         <f>[1]!PVT_bw_m3m3(B32,C32,PVT_json)</f>
@@ -13739,7 +13717,7 @@
       </c>
       <c r="N32" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B32,C32,PVT_json)</f>
-        <v>2.8601027331509519E-2</v>
+        <v>2.8601027331509522E-2</v>
       </c>
       <c r="O32" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B32,C32,PVT_json)</f>
@@ -13751,7 +13729,7 @@
       </c>
       <c r="Q32" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B32,C32,PVT_json)</f>
-        <v>2144.9238338280929</v>
+        <v>2144.9238338280934</v>
       </c>
       <c r="R32" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B32,C32,PVT_json)</f>
@@ -13759,18 +13737,18 @@
       </c>
       <c r="S32" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B32,C32,PVT_json)</f>
-        <v>3.4287017433847835E-5</v>
+        <v>3.4287017433847842E-5</v>
       </c>
       <c r="T32" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B32,C32,PVT_json)</f>
-        <v>4.1443404591609029E-2</v>
+        <v>4.1443404591609036E-2</v>
       </c>
       <c r="U32" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B32,C32,PVT_json)</f>
-        <v>9.2952069162459822E-2</v>
+        <v>9.2952069162462111E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B33" s="7">
         <v>20.92</v>
       </c>
@@ -13780,7 +13758,7 @@
       </c>
       <c r="D33" s="8">
         <f t="array" ref="D33">[1]!PVT_rs_m3m3(B33,C33,PVT_json)</f>
-        <v>15.871341736906061</v>
+        <v>15.871341736906073</v>
       </c>
       <c r="E33" s="8">
         <f>[1]!PVT_bo_m3m3(B33,C33,PVT_json)</f>
@@ -13788,39 +13766,39 @@
       </c>
       <c r="F33" s="9">
         <f>[1]!PVT_mu_oil_cP(B33,C33,PVT_json)</f>
-        <v>5.1397568149463062</v>
+        <v>5.1397568149463044</v>
       </c>
       <c r="G33" s="10">
         <f>[1]!PVT_mu_gas_cP(B33,C33,PVT_json)</f>
-        <v>1.1986250575720442E-2</v>
+        <v>1.198625057572044E-2</v>
       </c>
       <c r="H33" s="8">
         <f>[1]!PVT_mu_wat_cP(B33,C33,PVT_json)</f>
-        <v>0.83711054604977453</v>
+        <v>0.83711054604977353</v>
       </c>
       <c r="I33" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B33,C33,PVT_json)</f>
-        <v>14.817056436627773</v>
+        <v>14.81705643662777</v>
       </c>
       <c r="J33" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B33,C33,PVT_json)</f>
-        <v>1089.668131514959</v>
+        <v>1089.6681315149592</v>
       </c>
       <c r="K33" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B33,C33,PVT_json)</f>
-        <v>847.79750461929552</v>
+        <v>847.79750461929541</v>
       </c>
       <c r="L33" s="12">
         <f>[1]!PVT_bg_m3m3(B33,C33,PVT_json)</f>
-        <v>4.9471364513937736E-2</v>
+        <v>4.947136451393775E-2</v>
       </c>
       <c r="M33" s="12">
         <f>[1]!PVT_bw_m3m3(B33,C33,PVT_json)</f>
-        <v>1.0094816652760843</v>
+        <v>1.0094816652760841</v>
       </c>
       <c r="N33" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B33,C33,PVT_json)</f>
-        <v>2.8237263576614238E-2</v>
+        <v>2.8237263576614241E-2</v>
       </c>
       <c r="O33" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B33,C33,PVT_json)</f>
@@ -13832,7 +13810,7 @@
       </c>
       <c r="Q33" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B33,C33,PVT_json)</f>
-        <v>2107.4096430143254</v>
+        <v>2107.4096430143263</v>
       </c>
       <c r="R33" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B33,C33,PVT_json)</f>
@@ -13840,18 +13818,18 @@
       </c>
       <c r="S33" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B33,C33,PVT_json)</f>
-        <v>3.4203779675322932E-5</v>
+        <v>3.4203779675322945E-5</v>
       </c>
       <c r="T33" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B33,C33,PVT_json)</f>
-        <v>2.3799326989926185E-2</v>
+        <v>2.3799326989926199E-2</v>
       </c>
       <c r="U33" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B33,C33,PVT_json)</f>
-        <v>4.9634378950722882E-2</v>
+        <v>4.9634378950726386E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B34" s="7">
         <v>30.88</v>
       </c>
@@ -13861,7 +13839,7 @@
       </c>
       <c r="D34" s="8">
         <f t="array" ref="D34">[1]!PVT_rs_m3m3(B34,C34,PVT_json)</f>
-        <v>25.364647959839644</v>
+        <v>25.364647959839669</v>
       </c>
       <c r="E34" s="8">
         <f>[1]!PVT_bo_m3m3(B34,C34,PVT_json)</f>
@@ -13869,7 +13847,7 @@
       </c>
       <c r="F34" s="9">
         <f>[1]!PVT_mu_oil_cP(B34,C34,PVT_json)</f>
-        <v>3.9709702064959602</v>
+        <v>3.9709702064959589</v>
       </c>
       <c r="G34" s="10">
         <f>[1]!PVT_mu_gas_cP(B34,C34,PVT_json)</f>
@@ -13877,15 +13855,15 @@
       </c>
       <c r="H34" s="8">
         <f>[1]!PVT_mu_wat_cP(B34,C34,PVT_json)</f>
-        <v>0.84227527974747018</v>
+        <v>0.84227527974746919</v>
       </c>
       <c r="I34" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B34,C34,PVT_json)</f>
-        <v>22.287265720310746</v>
+        <v>22.287265720310756</v>
       </c>
       <c r="J34" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B34,C34,PVT_json)</f>
-        <v>1089.7871558389759</v>
+        <v>1089.7871558389757</v>
       </c>
       <c r="K34" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B34,C34,PVT_json)</f>
@@ -13893,7 +13871,7 @@
       </c>
       <c r="L34" s="12">
         <f>[1]!PVT_bg_m3m3(B34,C34,PVT_json)</f>
-        <v>3.2889633443549199E-2</v>
+        <v>3.2889633443549185E-2</v>
       </c>
       <c r="M34" s="12">
         <f>[1]!PVT_bw_m3m3(B34,C34,PVT_json)</f>
@@ -13921,18 +13899,18 @@
       </c>
       <c r="S34" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B34,C34,PVT_json)</f>
-        <v>3.4120945086597352E-5</v>
+        <v>3.4120945086597366E-5</v>
       </c>
       <c r="T34" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B34,C34,PVT_json)</f>
-        <v>1.6702949182722176E-2</v>
+        <v>1.6702949182722172E-2</v>
       </c>
       <c r="U34" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B34,C34,PVT_json)</f>
-        <v>3.4329183017041652E-2</v>
+        <v>3.4329183017040465E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B35" s="7">
         <v>40.840000000000003</v>
       </c>
@@ -13942,7 +13920,7 @@
       </c>
       <c r="D35" s="8">
         <f t="array" ref="D35">[1]!PVT_rs_m3m3(B35,C35,PVT_json)</f>
-        <v>35.514409899723034</v>
+        <v>35.514409899723063</v>
       </c>
       <c r="E35" s="8">
         <f>[1]!PVT_bo_m3m3(B35,C35,PVT_json)</f>
@@ -13950,7 +13928,7 @@
       </c>
       <c r="F35" s="9">
         <f>[1]!PVT_mu_oil_cP(B35,C35,PVT_json)</f>
-        <v>3.1972861301457325</v>
+        <v>3.1972861301457316</v>
       </c>
       <c r="G35" s="10">
         <f>[1]!PVT_mu_gas_cP(B35,C35,PVT_json)</f>
@@ -13958,15 +13936,15 @@
       </c>
       <c r="H35" s="8">
         <f>[1]!PVT_mu_wat_cP(B35,C35,PVT_json)</f>
-        <v>0.84755010499378214</v>
+        <v>0.84755010499378114</v>
       </c>
       <c r="I35" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B35,C35,PVT_json)</f>
-        <v>30.065604190118247</v>
+        <v>30.065604190118243</v>
       </c>
       <c r="J35" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B35,C35,PVT_json)</f>
-        <v>1089.9175697681967</v>
+        <v>1089.9175697681965</v>
       </c>
       <c r="K35" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B35,C35,PVT_json)</f>
@@ -13974,7 +13952,7 @@
       </c>
       <c r="L35" s="12">
         <f>[1]!PVT_bg_m3m3(B35,C35,PVT_json)</f>
-        <v>2.4380684165360093E-2</v>
+        <v>2.4380684165360097E-2</v>
       </c>
       <c r="M35" s="12">
         <f>[1]!PVT_bw_m3m3(B35,C35,PVT_json)</f>
@@ -13982,7 +13960,7 @@
       </c>
       <c r="N35" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B35,C35,PVT_json)</f>
-        <v>2.7523556872367409E-2</v>
+        <v>2.7523556872367412E-2</v>
       </c>
       <c r="O35" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B35,C35,PVT_json)</f>
@@ -13994,7 +13972,7 @@
       </c>
       <c r="Q35" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B35,C35,PVT_json)</f>
-        <v>2027.5193865688188</v>
+        <v>2027.5193865688193</v>
       </c>
       <c r="R35" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B35,C35,PVT_json)</f>
@@ -14002,18 +13980,18 @@
       </c>
       <c r="S35" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B35,C35,PVT_json)</f>
-        <v>3.4038510745562402E-5</v>
+        <v>3.4038510745562415E-5</v>
       </c>
       <c r="T35" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B35,C35,PVT_json)</f>
-        <v>1.2748477737173854E-2</v>
+        <v>1.274847773717386E-2</v>
       </c>
       <c r="U35" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B35,C35,PVT_json)</f>
-        <v>2.6511926884427977E-2</v>
+        <v>2.6511926884434035E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B36" s="7">
         <v>50.8</v>
       </c>
@@ -14023,7 +14001,7 @@
       </c>
       <c r="D36" s="8">
         <f t="array" ref="D36">[1]!PVT_rs_m3m3(B36,C36,PVT_json)</f>
-        <v>46.186737869660284</v>
+        <v>46.186737869660327</v>
       </c>
       <c r="E36" s="8">
         <f>[1]!PVT_bo_m3m3(B36,C36,PVT_json)</f>
@@ -14031,7 +14009,7 @@
       </c>
       <c r="F36" s="9">
         <f>[1]!PVT_mu_oil_cP(B36,C36,PVT_json)</f>
-        <v>2.6582574292633616</v>
+        <v>2.6582574292633621</v>
       </c>
       <c r="G36" s="10">
         <f>[1]!PVT_mu_gas_cP(B36,C36,PVT_json)</f>
@@ -14039,11 +14017,11 @@
       </c>
       <c r="H36" s="8">
         <f>[1]!PVT_mu_wat_cP(B36,C36,PVT_json)</f>
-        <v>0.85293502178871006</v>
+        <v>0.85293502178870917</v>
       </c>
       <c r="I36" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B36,C36,PVT_json)</f>
-        <v>38.167901822091984</v>
+        <v>38.167901822091991</v>
       </c>
       <c r="J36" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B36,C36,PVT_json)</f>
@@ -14055,15 +14033,15 @@
       </c>
       <c r="L36" s="12">
         <f>[1]!PVT_bg_m3m3(B36,C36,PVT_json)</f>
-        <v>1.9205142672414868E-2</v>
+        <v>1.9205142672414865E-2</v>
       </c>
       <c r="M36" s="12">
         <f>[1]!PVT_bw_m3m3(B36,C36,PVT_json)</f>
-        <v>1.0091193367050952</v>
+        <v>1.009119336705095</v>
       </c>
       <c r="N36" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B36,C36,PVT_json)</f>
-        <v>2.7173496985359927E-2</v>
+        <v>2.7173496985359931E-2</v>
       </c>
       <c r="O36" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B36,C36,PVT_json)</f>
@@ -14083,7 +14061,7 @@
       </c>
       <c r="S36" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B36,C36,PVT_json)</f>
-        <v>3.3956473758279953E-5</v>
+        <v>3.395647375827996E-5</v>
       </c>
       <c r="T36" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B36,C36,PVT_json)</f>
@@ -14091,10 +14069,10 @@
       </c>
       <c r="U36" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B36,C36,PVT_json)</f>
-        <v>2.1741398826457058E-2</v>
+        <v>2.1741398826454584E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B37" s="7">
         <v>60.76</v>
       </c>
@@ -14104,7 +14082,7 @@
       </c>
       <c r="D37" s="8">
         <f t="array" ref="D37">[1]!PVT_rs_m3m3(B37,C37,PVT_json)</f>
-        <v>57.297169628895659</v>
+        <v>57.297169628895695</v>
       </c>
       <c r="E37" s="8">
         <f>[1]!PVT_bo_m3m3(B37,C37,PVT_json)</f>
@@ -14116,15 +14094,15 @@
       </c>
       <c r="G37" s="10">
         <f>[1]!PVT_mu_gas_cP(B37,C37,PVT_json)</f>
-        <v>1.3076968510634203E-2</v>
+        <v>1.3076968510634199E-2</v>
       </c>
       <c r="H37" s="8">
         <f>[1]!PVT_mu_wat_cP(B37,C37,PVT_json)</f>
-        <v>0.85843003013225416</v>
+        <v>0.85843003013225316</v>
       </c>
       <c r="I37" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B37,C37,PVT_json)</f>
-        <v>46.591315187907213</v>
+        <v>46.591315187907206</v>
       </c>
       <c r="J37" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B37,C37,PVT_json)</f>
@@ -14136,7 +14114,7 @@
       </c>
       <c r="L37" s="12">
         <f>[1]!PVT_bg_m3m3(B37,C37,PVT_json)</f>
-        <v>1.5732975062920214E-2</v>
+        <v>1.5732975062920217E-2</v>
       </c>
       <c r="M37" s="12">
         <f>[1]!PVT_bw_m3m3(B37,C37,PVT_json)</f>
@@ -14144,7 +14122,7 @@
       </c>
       <c r="N37" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B37,C37,PVT_json)</f>
-        <v>2.6827889354471078E-2</v>
+        <v>2.6827889354471082E-2</v>
       </c>
       <c r="O37" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B37,C37,PVT_json)</f>
@@ -14156,7 +14134,7 @@
       </c>
       <c r="Q37" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B37,C37,PVT_json)</f>
-        <v>1946.5340857482613</v>
+        <v>1946.5340857482618</v>
       </c>
       <c r="R37" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B37,C37,PVT_json)</f>
@@ -14164,18 +14142,18 @@
       </c>
       <c r="S37" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B37,C37,PVT_json)</f>
-        <v>3.3874831258643775E-5</v>
+        <v>3.3874831258643788E-5</v>
       </c>
       <c r="T37" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B37,C37,PVT_json)</f>
-        <v>8.3777197633504198E-3</v>
+        <v>8.3777197633504233E-3</v>
       </c>
       <c r="U37" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B37,C37,PVT_json)</f>
-        <v>1.8483563307189196E-2</v>
+        <v>1.8483563307194244E-2</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B38" s="7">
         <v>70.72</v>
       </c>
@@ -14185,7 +14163,7 @@
       </c>
       <c r="D38" s="8">
         <f t="array" ref="D38">[1]!PVT_rs_m3m3(B38,C38,PVT_json)</f>
-        <v>68.786981354050553</v>
+        <v>68.78698135405061</v>
       </c>
       <c r="E38" s="8">
         <f>[1]!PVT_bo_m3m3(B38,C38,PVT_json)</f>
@@ -14193,39 +14171,39 @@
       </c>
       <c r="F38" s="9">
         <f>[1]!PVT_mu_oil_cP(B38,C38,PVT_json)</f>
-        <v>1.9699222555167235</v>
+        <v>1.9699222555167233</v>
       </c>
       <c r="G38" s="10">
         <f>[1]!PVT_mu_gas_cP(B38,C38,PVT_json)</f>
-        <v>1.3440112930067173E-2</v>
+        <v>1.3440112930067171E-2</v>
       </c>
       <c r="H38" s="8">
         <f>[1]!PVT_mu_wat_cP(B38,C38,PVT_json)</f>
-        <v>0.86403513002441446</v>
+        <v>0.86403513002441357</v>
       </c>
       <c r="I38" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B38,C38,PVT_json)</f>
-        <v>55.310777212770795</v>
+        <v>55.310777212770816</v>
       </c>
       <c r="J38" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B38,C38,PVT_json)</f>
-        <v>1090.3772344668146</v>
+        <v>1090.3772344668148</v>
       </c>
       <c r="K38" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B38,C38,PVT_json)</f>
-        <v>829.78712419752674</v>
+        <v>829.78712419752685</v>
       </c>
       <c r="L38" s="12">
         <f>[1]!PVT_bg_m3m3(B38,C38,PVT_json)</f>
-        <v>1.3252751759032448E-2</v>
+        <v>1.3252751759032443E-2</v>
       </c>
       <c r="M38" s="12">
         <f>[1]!PVT_bw_m3m3(B38,C38,PVT_json)</f>
-        <v>1.0088251709857927</v>
+        <v>1.0088251709857925</v>
       </c>
       <c r="N38" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B38,C38,PVT_json)</f>
-        <v>2.6486677353434109E-2</v>
+        <v>2.6486677353434112E-2</v>
       </c>
       <c r="O38" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B38,C38,PVT_json)</f>
@@ -14237,7 +14215,7 @@
       </c>
       <c r="Q38" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B38,C38,PVT_json)</f>
-        <v>1908.4540537444457</v>
+        <v>1908.4540537444454</v>
       </c>
       <c r="R38" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B38,C38,PVT_json)</f>
@@ -14245,7 +14223,7 @@
       </c>
       <c r="S38" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B38,C38,PVT_json)</f>
-        <v>3.3793580408045776E-5</v>
+        <v>3.3793580408045789E-5</v>
       </c>
       <c r="T38" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B38,C38,PVT_json)</f>
@@ -14256,7 +14234,7 @@
         <v>1.6070225769133948E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B39" s="7">
         <v>80.680000000000007</v>
       </c>
@@ -14266,7 +14244,7 @@
       </c>
       <c r="D39" s="8">
         <f t="array" ref="D39">[1]!PVT_rs_m3m3(B39,C39,PVT_json)</f>
-        <v>80.61270806753825</v>
+        <v>80.612708067538293</v>
       </c>
       <c r="E39" s="8">
         <f>[1]!PVT_bo_m3m3(B39,C39,PVT_json)</f>
@@ -14274,19 +14252,19 @@
       </c>
       <c r="F39" s="9">
         <f>[1]!PVT_mu_oil_cP(B39,C39,PVT_json)</f>
-        <v>1.7398587672578572</v>
+        <v>1.7398587672578569</v>
       </c>
       <c r="G39" s="10">
         <f>[1]!PVT_mu_gas_cP(B39,C39,PVT_json)</f>
-        <v>1.3840188691857097E-2</v>
+        <v>1.3840188691857094E-2</v>
       </c>
       <c r="H39" s="8">
         <f>[1]!PVT_mu_wat_cP(B39,C39,PVT_json)</f>
-        <v>0.86975032146519071</v>
+        <v>0.86975032146518971</v>
       </c>
       <c r="I39" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B39,C39,PVT_json)</f>
-        <v>64.279030785472941</v>
+        <v>64.279030785472969</v>
       </c>
       <c r="J39" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B39,C39,PVT_json)</f>
@@ -14298,11 +14276,11 @@
       </c>
       <c r="L39" s="12">
         <f>[1]!PVT_bg_m3m3(B39,C39,PVT_json)</f>
-        <v>1.1403718927349827E-2</v>
+        <v>1.1403718927349822E-2</v>
       </c>
       <c r="M39" s="12">
         <f>[1]!PVT_bw_m3m3(B39,C39,PVT_json)</f>
-        <v>1.0086623041245486</v>
+        <v>1.0086623041245484</v>
       </c>
       <c r="N39" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B39,C39,PVT_json)</f>
@@ -14318,7 +14296,7 @@
       </c>
       <c r="Q39" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B39,C39,PVT_json)</f>
-        <v>1873.4658782230829</v>
+        <v>1873.4658782230824</v>
       </c>
       <c r="R39" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B39,C39,PVT_json)</f>
@@ -14326,18 +14304,18 @@
       </c>
       <c r="S39" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B39,C39,PVT_json)</f>
-        <v>3.3712718395046981E-5</v>
+        <v>3.3712718395046994E-5</v>
       </c>
       <c r="T39" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B39,C39,PVT_json)</f>
-        <v>5.9886551116846501E-3</v>
+        <v>5.9886551116846484E-3</v>
       </c>
       <c r="U39" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B39,C39,PVT_json)</f>
-        <v>1.4169013400171022E-2</v>
+        <v>1.4169013400165777E-2</v>
       </c>
     </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B40" s="7">
         <v>90.64</v>
       </c>
@@ -14347,7 +14325,7 @@
       </c>
       <c r="D40" s="8">
         <f t="array" ref="D40">[1]!PVT_rs_m3m3(B40,C40,PVT_json)</f>
-        <v>92.740735470779853</v>
+        <v>92.74073547077991</v>
       </c>
       <c r="E40" s="8">
         <f>[1]!PVT_bo_m3m3(B40,C40,PVT_json)</f>
@@ -14355,7 +14333,7 @@
       </c>
       <c r="F40" s="9">
         <f>[1]!PVT_mu_oil_cP(B40,C40,PVT_json)</f>
-        <v>1.556606911111144</v>
+        <v>1.5566069111111438</v>
       </c>
       <c r="G40" s="10">
         <f>[1]!PVT_mu_gas_cP(B40,C40,PVT_json)</f>
@@ -14363,15 +14341,15 @@
       </c>
       <c r="H40" s="8">
         <f>[1]!PVT_mu_wat_cP(B40,C40,PVT_json)</f>
-        <v>0.87557560445458327</v>
+        <v>0.87557560445458216</v>
       </c>
       <c r="I40" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B40,C40,PVT_json)</f>
-        <v>73.430133425720598</v>
+        <v>73.430133425720641</v>
       </c>
       <c r="J40" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B40,C40,PVT_json)</f>
-        <v>1090.7407945491616</v>
+        <v>1090.7407945491618</v>
       </c>
       <c r="K40" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B40,C40,PVT_json)</f>
@@ -14379,11 +14357,11 @@
       </c>
       <c r="L40" s="12">
         <f>[1]!PVT_bg_m3m3(B40,C40,PVT_json)</f>
-        <v>9.9825502937632253E-3</v>
+        <v>9.9825502937632201E-3</v>
       </c>
       <c r="M40" s="12">
         <f>[1]!PVT_bw_m3m3(B40,C40,PVT_json)</f>
-        <v>1.008488914595576</v>
+        <v>1.0084889145955758</v>
       </c>
       <c r="N40" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B40,C40,PVT_json)</f>
@@ -14399,7 +14377,7 @@
       </c>
       <c r="Q40" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B40,C40,PVT_json)</f>
-        <v>1842.4461242884263</v>
+        <v>1842.4461242884254</v>
       </c>
       <c r="R40" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B40,C40,PVT_json)</f>
@@ -14407,18 +14385,18 @@
       </c>
       <c r="S40" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B40,C40,PVT_json)</f>
-        <v>3.363224243505328E-5</v>
+        <v>3.3632242435053287E-5</v>
       </c>
       <c r="T40" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B40,C40,PVT_json)</f>
-        <v>5.1635950123179704E-3</v>
+        <v>5.1635950123179696E-3</v>
       </c>
       <c r="U40" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B40,C40,PVT_json)</f>
-        <v>1.2601282976993014E-2</v>
+        <v>1.2601282976989016E-2</v>
       </c>
     </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B41" s="7">
         <v>100.6</v>
       </c>
@@ -14428,7 +14406,7 @@
       </c>
       <c r="D41" s="8">
         <f t="array" ref="D41">[1]!PVT_rs_m3m3(B41,C41,PVT_json)</f>
-        <v>105.1442067038592</v>
+        <v>105.14420670385927</v>
       </c>
       <c r="E41" s="8">
         <f>[1]!PVT_bo_m3m3(B41,C41,PVT_json)</f>
@@ -14436,15 +14414,15 @@
       </c>
       <c r="F41" s="9">
         <f>[1]!PVT_mu_oil_cP(B41,C41,PVT_json)</f>
-        <v>1.4076080220116913</v>
+        <v>1.4076080220116909</v>
       </c>
       <c r="G41" s="10">
         <f>[1]!PVT_mu_gas_cP(B41,C41,PVT_json)</f>
-        <v>1.4745918799782596E-2</v>
+        <v>1.4745918799782593E-2</v>
       </c>
       <c r="H41" s="8">
         <f>[1]!PVT_mu_wat_cP(B41,C41,PVT_json)</f>
-        <v>0.88151097899259179</v>
+        <v>0.88151097899259068</v>
       </c>
       <c r="I41" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B41,C41,PVT_json)</f>
@@ -14452,7 +14430,7 @@
       </c>
       <c r="J41" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B41,C41,PVT_json)</f>
-        <v>1090.9397428188618</v>
+        <v>1090.939742818862</v>
       </c>
       <c r="K41" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B41,C41,PVT_json)</f>
@@ -14464,11 +14442,11 @@
       </c>
       <c r="M41" s="12">
         <f>[1]!PVT_bw_m3m3(B41,C41,PVT_json)</f>
-        <v>1.0083050023988747</v>
+        <v>1.0083050023988744</v>
       </c>
       <c r="N41" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B41,C41,PVT_json)</f>
-        <v>2.5488859614988299E-2</v>
+        <v>2.5488859614988302E-2</v>
       </c>
       <c r="O41" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B41,C41,PVT_json)</f>
@@ -14488,18 +14466,18 @@
       </c>
       <c r="S41" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B41,C41,PVT_json)</f>
-        <v>3.3552149769995756E-5</v>
+        <v>3.3552149769995769E-5</v>
       </c>
       <c r="T41" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B41,C41,PVT_json)</f>
-        <v>4.4975548856352838E-3</v>
+        <v>4.4975548856352856E-3</v>
       </c>
       <c r="U41" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B41,C41,PVT_json)</f>
-        <v>1.1266546320236766E-2</v>
+        <v>1.126654632023812E-2</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B42" s="7">
         <v>110.56</v>
       </c>
@@ -14509,7 +14487,7 @@
       </c>
       <c r="D42" s="8">
         <f t="array" ref="D42">[1]!PVT_rs_m3m3(B42,C42,PVT_json)</f>
-        <v>117.80111687961006</v>
+        <v>117.80111687961013</v>
       </c>
       <c r="E42" s="8">
         <f>[1]!PVT_bo_m3m3(B42,C42,PVT_json)</f>
@@ -14517,19 +14495,19 @@
       </c>
       <c r="F42" s="9">
         <f>[1]!PVT_mu_oil_cP(B42,C42,PVT_json)</f>
-        <v>1.2843310127570022</v>
+        <v>1.2843310127570018</v>
       </c>
       <c r="G42" s="10">
         <f>[1]!PVT_mu_gas_cP(B42,C42,PVT_json)</f>
-        <v>1.5246397964708501E-2</v>
+        <v>1.5246397964708497E-2</v>
       </c>
       <c r="H42" s="8">
         <f>[1]!PVT_mu_wat_cP(B42,C42,PVT_json)</f>
-        <v>0.88755644507921649</v>
+        <v>0.88755644507921549</v>
       </c>
       <c r="I42" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B42,C42,PVT_json)</f>
-        <v>91.96132516576067</v>
+        <v>91.961325165760698</v>
       </c>
       <c r="J42" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B42,C42,PVT_json)</f>
@@ -14541,7 +14519,7 @@
       </c>
       <c r="L42" s="12">
         <f>[1]!PVT_bg_m3m3(B42,C42,PVT_json)</f>
-        <v>7.9709595167177984E-3</v>
+        <v>7.9709595167177967E-3</v>
       </c>
       <c r="M42" s="12">
         <f>[1]!PVT_bw_m3m3(B42,C42,PVT_json)</f>
@@ -14549,7 +14527,7 @@
       </c>
       <c r="N42" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B42,C42,PVT_json)</f>
-        <v>2.5164678138075682E-2</v>
+        <v>2.5164678138075686E-2</v>
       </c>
       <c r="O42" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B42,C42,PVT_json)</f>
@@ -14561,7 +14539,7 @@
       </c>
       <c r="Q42" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B42,C42,PVT_json)</f>
-        <v>1794.4940678864402</v>
+        <v>1794.49406788644</v>
       </c>
       <c r="R42" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B42,C42,PVT_json)</f>
@@ -14569,7 +14547,7 @@
       </c>
       <c r="S42" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B42,C42,PVT_json)</f>
-        <v>3.347243766801564E-5</v>
+        <v>3.3472437668015654E-5</v>
       </c>
       <c r="T42" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B42,C42,PVT_json)</f>
@@ -14577,10 +14555,10 @@
       </c>
       <c r="U42" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B42,C42,PVT_json)</f>
-        <v>1.010645707425032E-2</v>
+        <v>1.0106457074250322E-2</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B43" s="7">
         <v>120.52</v>
       </c>
@@ -14594,19 +14572,19 @@
       </c>
       <c r="E43" s="8">
         <f>[1]!PVT_bo_m3m3(B43,C43,PVT_json)</f>
-        <v>1.1681208648753281</v>
+        <v>1.1681208648753278</v>
       </c>
       <c r="F43" s="9">
         <f>[1]!PVT_mu_oil_cP(B43,C43,PVT_json)</f>
-        <v>1.2926930197501152</v>
+        <v>1.2926930197501159</v>
       </c>
       <c r="G43" s="10">
         <f>[1]!PVT_mu_gas_cP(B43,C43,PVT_json)</f>
-        <v>1.5773782410755829E-2</v>
+        <v>1.5773782410755825E-2</v>
       </c>
       <c r="H43" s="8">
         <f>[1]!PVT_mu_wat_cP(B43,C43,PVT_json)</f>
-        <v>0.89371200271445739</v>
+        <v>0.89371200271445617</v>
       </c>
       <c r="I43" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B43,C43,PVT_json)</f>
@@ -14614,11 +14592,11 @@
       </c>
       <c r="J43" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B43,C43,PVT_json)</f>
-        <v>1091.3720382978172</v>
+        <v>1091.3720382978174</v>
       </c>
       <c r="K43" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B43,C43,PVT_json)</f>
-        <v>811.52766678915089</v>
+        <v>811.52766678915111</v>
       </c>
       <c r="L43" s="12">
         <f>[1]!PVT_bg_m3m3(B43,C43,PVT_json)</f>
@@ -14626,11 +14604,11 @@
       </c>
       <c r="M43" s="12">
         <f>[1]!PVT_bw_m3m3(B43,C43,PVT_json)</f>
-        <v>1.0079056100022863</v>
+        <v>1.0079056100022861</v>
       </c>
       <c r="N43" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B43,C43,PVT_json)</f>
-        <v>2.4844619781285382E-2</v>
+        <v>2.4844619781285385E-2</v>
       </c>
       <c r="O43" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B43,C43,PVT_json)</f>
@@ -14642,7 +14620,7 @@
       </c>
       <c r="Q43" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B43,C43,PVT_json)</f>
-        <v>1778.0081172029581</v>
+        <v>1778.0081172029584</v>
       </c>
       <c r="R43" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B43,C43,PVT_json)</f>
@@ -14650,18 +14628,18 @@
       </c>
       <c r="S43" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B43,C43,PVT_json)</f>
-        <v>3.3393103423153651E-5</v>
+        <v>3.3393103423153658E-5</v>
       </c>
       <c r="T43" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B43,C43,PVT_json)</f>
-        <v>1.5685504418005018E-4</v>
+        <v>1.568550441800501E-4</v>
       </c>
       <c r="U43" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B43,C43,PVT_json)</f>
         <v>9.0859261789447837E-3</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B44" s="7">
         <v>130.47999999999999</v>
       </c>
@@ -14675,23 +14653,23 @@
       </c>
       <c r="E44" s="8">
         <f>[1]!PVT_bo_m3m3(B44,C44,PVT_json)</f>
-        <v>1.1653095028377118</v>
+        <v>1.1653095028377116</v>
       </c>
       <c r="F44" s="9">
         <f>[1]!PVT_mu_oil_cP(B44,C44,PVT_json)</f>
-        <v>1.3261910177947958</v>
+        <v>1.326191017794796</v>
       </c>
       <c r="G44" s="10">
         <f>[1]!PVT_mu_gas_cP(B44,C44,PVT_json)</f>
-        <v>1.6323793809058018E-2</v>
+        <v>1.6323793809058015E-2</v>
       </c>
       <c r="H44" s="8">
         <f>[1]!PVT_mu_wat_cP(B44,C44,PVT_json)</f>
-        <v>0.89997765189831436</v>
+        <v>0.89997765189831325</v>
       </c>
       <c r="I44" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B44,C44,PVT_json)</f>
-        <v>110.25278879326807</v>
+        <v>110.25278879326808</v>
       </c>
       <c r="J44" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B44,C44,PVT_json)</f>
@@ -14699,11 +14677,11 @@
       </c>
       <c r="K44" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B44,C44,PVT_json)</f>
-        <v>813.48551409866866</v>
+        <v>813.48551409866877</v>
       </c>
       <c r="L44" s="12">
         <f>[1]!PVT_bg_m3m3(B44,C44,PVT_json)</f>
-        <v>6.6485393070144045E-3</v>
+        <v>6.6485393070144037E-3</v>
       </c>
       <c r="M44" s="12">
         <f>[1]!PVT_bw_m3m3(B44,C44,PVT_json)</f>
@@ -14711,7 +14689,7 @@
       </c>
       <c r="N44" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B44,C44,PVT_json)</f>
-        <v>2.4528632104485072E-2</v>
+        <v>2.4528632104485075E-2</v>
       </c>
       <c r="O44" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B44,C44,PVT_json)</f>
@@ -14723,7 +14701,7 @@
       </c>
       <c r="Q44" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B44,C44,PVT_json)</f>
-        <v>1766.4590833965171</v>
+        <v>1766.4590833965174</v>
       </c>
       <c r="R44" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B44,C44,PVT_json)</f>
@@ -14731,18 +14709,18 @@
       </c>
       <c r="S44" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B44,C44,PVT_json)</f>
-        <v>3.3314144355043821E-5</v>
+        <v>3.3314144355043828E-5</v>
       </c>
       <c r="T44" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B44,C44,PVT_json)</f>
-        <v>1.4488174375061044E-4</v>
+        <v>1.4488174375061033E-4</v>
       </c>
       <c r="U44" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B44,C44,PVT_json)</f>
-        <v>8.1826702166252763E-3</v>
+        <v>8.1826702166266641E-3</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B45" s="7">
         <v>140.44</v>
       </c>
@@ -14756,31 +14734,31 @@
       </c>
       <c r="E45" s="8">
         <f>[1]!PVT_bo_m3m3(B45,C45,PVT_json)</f>
-        <v>1.1629022995124061</v>
+        <v>1.1629022995124059</v>
       </c>
       <c r="F45" s="9">
         <f>[1]!PVT_mu_oil_cP(B45,C45,PVT_json)</f>
-        <v>1.3622131528629118</v>
+        <v>1.3622131528629122</v>
       </c>
       <c r="G45" s="10">
         <f>[1]!PVT_mu_gas_cP(B45,C45,PVT_json)</f>
-        <v>1.6891977917657237E-2</v>
+        <v>1.6891977917657234E-2</v>
       </c>
       <c r="H45" s="8">
         <f>[1]!PVT_mu_wat_cP(B45,C45,PVT_json)</f>
-        <v>0.9063533926307874</v>
+        <v>0.90635339263078618</v>
       </c>
       <c r="I45" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B45,C45,PVT_json)</f>
-        <v>119.13031753524773</v>
+        <v>119.13031753524774</v>
       </c>
       <c r="J45" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B45,C45,PVT_json)</f>
-        <v>1091.8502908354242</v>
+        <v>1091.8502908354244</v>
       </c>
       <c r="K45" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B45,C45,PVT_json)</f>
-        <v>815.16942601065591</v>
+        <v>815.16942601065614</v>
       </c>
       <c r="L45" s="12">
         <f>[1]!PVT_bg_m3m3(B45,C45,PVT_json)</f>
@@ -14788,11 +14766,11 @@
       </c>
       <c r="M45" s="12">
         <f>[1]!PVT_bw_m3m3(B45,C45,PVT_json)</f>
-        <v>1.0074641269347835</v>
+        <v>1.0074641269347833</v>
       </c>
       <c r="N45" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B45,C45,PVT_json)</f>
-        <v>2.4216663334505176E-2</v>
+        <v>2.421666333450518E-2</v>
       </c>
       <c r="O45" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B45,C45,PVT_json)</f>
@@ -14804,7 +14782,7 @@
       </c>
       <c r="Q45" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B45,C45,PVT_json)</f>
-        <v>1759.6153392775939</v>
+        <v>1759.6153392775941</v>
       </c>
       <c r="R45" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B45,C45,PVT_json)</f>
@@ -14812,18 +14790,18 @@
       </c>
       <c r="S45" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B45,C45,PVT_json)</f>
-        <v>3.3235557808611641E-5</v>
+        <v>3.3235557808611648E-5</v>
       </c>
       <c r="T45" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B45,C45,PVT_json)</f>
-        <v>1.3460673543562836E-4</v>
+        <v>1.3460673543562828E-4</v>
       </c>
       <c r="U45" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B45,C45,PVT_json)</f>
-        <v>7.3813348221404311E-3</v>
+        <v>7.3813348221432222E-3</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B46" s="7">
         <v>150.4</v>
       </c>
@@ -14837,43 +14815,43 @@
       </c>
       <c r="E46" s="8">
         <f>[1]!PVT_bo_m3m3(B46,C46,PVT_json)</f>
-        <v>1.1608179512669565</v>
+        <v>1.1608179512669563</v>
       </c>
       <c r="F46" s="9">
         <f>[1]!PVT_mu_oil_cP(B46,C46,PVT_json)</f>
-        <v>1.4005814298483223</v>
+        <v>1.4005814298483232</v>
       </c>
       <c r="G46" s="10">
         <f>[1]!PVT_mu_gas_cP(B46,C46,PVT_json)</f>
-        <v>1.7473960164598037E-2</v>
+        <v>1.7473960164598033E-2</v>
       </c>
       <c r="H46" s="8">
         <f>[1]!PVT_mu_wat_cP(B46,C46,PVT_json)</f>
-        <v>0.91283922491187663</v>
+        <v>0.91283922491187541</v>
       </c>
       <c r="I46" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B46,C46,PVT_json)</f>
-        <v>127.75776878861171</v>
+        <v>127.7577687886117</v>
       </c>
       <c r="J46" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B46,C46,PVT_json)</f>
-        <v>1092.1066881722295</v>
+        <v>1092.1066881722297</v>
       </c>
       <c r="K46" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B46,C46,PVT_json)</f>
-        <v>816.63313266766875</v>
+        <v>816.63313266766897</v>
       </c>
       <c r="L46" s="12">
         <f>[1]!PVT_bg_m3m3(B46,C46,PVT_json)</f>
-        <v>5.7375767199946684E-3</v>
+        <v>5.7375767199946692E-3</v>
       </c>
       <c r="M46" s="12">
         <f>[1]!PVT_bw_m3m3(B46,C46,PVT_json)</f>
-        <v>1.0072276013994392</v>
+        <v>1.007227601399439</v>
       </c>
       <c r="N46" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B46,C46,PVT_json)</f>
-        <v>2.3908662356656053E-2</v>
+        <v>2.3908662356656056E-2</v>
       </c>
       <c r="O46" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B46,C46,PVT_json)</f>
@@ -14885,7 +14863,7 @@
       </c>
       <c r="Q46" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B46,C46,PVT_json)</f>
-        <v>1757.1536362210618</v>
+        <v>1757.1536362210625</v>
       </c>
       <c r="R46" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B46,C46,PVT_json)</f>
@@ -14893,18 +14871,18 @@
       </c>
       <c r="S46" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B46,C46,PVT_json)</f>
-        <v>3.3157341153776427E-5</v>
+        <v>3.315734115377644E-5</v>
       </c>
       <c r="T46" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B46,C46,PVT_json)</f>
-        <v>1.2569261917938593E-4</v>
+        <v>1.2569261917938588E-4</v>
       </c>
       <c r="U46" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B46,C46,PVT_json)</f>
-        <v>6.6702438953240911E-3</v>
+        <v>6.6702438953282856E-3</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B47" s="7">
         <v>160.36000000000001</v>
       </c>
@@ -14918,35 +14896,35 @@
       </c>
       <c r="E47" s="8">
         <f>[1]!PVT_bo_m3m3(B47,C47,PVT_json)</f>
-        <v>1.158995590664182</v>
+        <v>1.1589955906641818</v>
       </c>
       <c r="F47" s="9">
         <f>[1]!PVT_mu_oil_cP(B47,C47,PVT_json)</f>
-        <v>1.4411346327141066</v>
+        <v>1.4411346327141075</v>
       </c>
       <c r="G47" s="10">
         <f>[1]!PVT_mu_gas_cP(B47,C47,PVT_json)</f>
-        <v>1.8065644186917872E-2</v>
+        <v>1.8065644186917869E-2</v>
       </c>
       <c r="H47" s="8">
         <f>[1]!PVT_mu_wat_cP(B47,C47,PVT_json)</f>
-        <v>0.91943514874158194</v>
+        <v>0.91943514874158094</v>
       </c>
       <c r="I47" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B47,C47,PVT_json)</f>
-        <v>136.09852438558232</v>
+        <v>136.09852438558238</v>
       </c>
       <c r="J47" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B47,C47,PVT_json)</f>
-        <v>1092.3746208488046</v>
+        <v>1092.3746208488044</v>
       </c>
       <c r="K47" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B47,C47,PVT_json)</f>
-        <v>817.91717555780701</v>
+        <v>817.91717555780713</v>
       </c>
       <c r="L47" s="12">
         <f>[1]!PVT_bg_m3m3(B47,C47,PVT_json)</f>
-        <v>5.385951121139803E-3</v>
+        <v>5.3859511211398012E-3</v>
       </c>
       <c r="M47" s="12">
         <f>[1]!PVT_bw_m3m3(B47,C47,PVT_json)</f>
@@ -14966,7 +14944,7 @@
       </c>
       <c r="Q47" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B47,C47,PVT_json)</f>
-        <v>1758.7003454838443</v>
+        <v>1758.7003454838439</v>
       </c>
       <c r="R47" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B47,C47,PVT_json)</f>
@@ -14974,18 +14952,18 @@
       </c>
       <c r="S47" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B47,C47,PVT_json)</f>
-        <v>3.3079491785157932E-5</v>
+        <v>3.3079491785157945E-5</v>
       </c>
       <c r="T47" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B47,C47,PVT_json)</f>
-        <v>1.1788581893601677E-4</v>
+        <v>1.1788581893601666E-4</v>
       </c>
       <c r="U47" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B47,C47,PVT_json)</f>
-        <v>6.0396792286972183E-3</v>
+        <v>6.0396792287000121E-3</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B48" s="7">
         <v>170.32</v>
       </c>
@@ -14999,19 +14977,19 @@
       </c>
       <c r="E48" s="8">
         <f>[1]!PVT_bo_m3m3(B48,C48,PVT_json)</f>
-        <v>1.1573887453687508</v>
+        <v>1.1573887453687506</v>
       </c>
       <c r="F48" s="9">
         <f>[1]!PVT_mu_oil_cP(B48,C48,PVT_json)</f>
-        <v>1.4837236136051819</v>
+        <v>1.4837236136051828</v>
       </c>
       <c r="G48" s="10">
         <f>[1]!PVT_mu_gas_cP(B48,C48,PVT_json)</f>
-        <v>1.866334463351299E-2</v>
+        <v>1.866334463351298E-2</v>
       </c>
       <c r="H48" s="8">
         <f>[1]!PVT_mu_wat_cP(B48,C48,PVT_json)</f>
-        <v>0.92614116411990333</v>
+        <v>0.92614116411990222</v>
       </c>
       <c r="I48" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B48,C48,PVT_json)</f>
@@ -15019,11 +14997,11 @@
       </c>
       <c r="J48" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B48,C48,PVT_json)</f>
-        <v>1092.6541057590264</v>
+        <v>1092.6541057590266</v>
       </c>
       <c r="K48" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B48,C48,PVT_json)</f>
-        <v>819.05272000720345</v>
+        <v>819.05272000720367</v>
       </c>
       <c r="L48" s="12">
         <f>[1]!PVT_bg_m3m3(B48,C48,PVT_json)</f>
@@ -15031,11 +15009,11 @@
       </c>
       <c r="M48" s="12">
         <f>[1]!PVT_bw_m3m3(B48,C48,PVT_json)</f>
-        <v>1.0067229823255648</v>
+        <v>1.0067229823255646</v>
       </c>
       <c r="N48" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B48,C48,PVT_json)</f>
-        <v>2.3304362560848245E-2</v>
+        <v>2.3304362560848248E-2</v>
       </c>
       <c r="O48" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B48,C48,PVT_json)</f>
@@ -15047,7 +15025,7 @@
       </c>
       <c r="Q48" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B48,C48,PVT_json)</f>
-        <v>1763.8631685330097</v>
+        <v>1763.8631685330099</v>
       </c>
       <c r="R48" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B48,C48,PVT_json)</f>
@@ -15055,18 +15033,18 @@
       </c>
       <c r="S48" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B48,C48,PVT_json)</f>
-        <v>3.300200712178704E-5</v>
+        <v>3.3002007121787047E-5</v>
       </c>
       <c r="T48" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B48,C48,PVT_json)</f>
-        <v>1.1099207330072599E-4</v>
+        <v>1.1099207330072591E-4</v>
       </c>
       <c r="U48" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B48,C48,PVT_json)</f>
-        <v>5.4810353399547635E-3</v>
+        <v>5.4810353399603355E-3</v>
       </c>
     </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B49" s="7">
         <v>180.28</v>
       </c>
@@ -15080,23 +15058,23 @@
       </c>
       <c r="E49" s="8">
         <f>[1]!PVT_bo_m3m3(B49,C49,PVT_json)</f>
-        <v>1.1559613203126462</v>
+        <v>1.155961320312646</v>
       </c>
       <c r="F49" s="9">
         <f>[1]!PVT_mu_oil_cP(B49,C49,PVT_json)</f>
-        <v>1.5282077500006936</v>
+        <v>1.5282077500006945</v>
       </c>
       <c r="G49" s="10">
         <f>[1]!PVT_mu_gas_cP(B49,C49,PVT_json)</f>
-        <v>1.9263857676805881E-2</v>
+        <v>1.9263857676805878E-2</v>
       </c>
       <c r="H49" s="8">
         <f>[1]!PVT_mu_wat_cP(B49,C49,PVT_json)</f>
-        <v>0.9329572710468409</v>
+        <v>0.93295727104683968</v>
       </c>
       <c r="I49" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B49,C49,PVT_json)</f>
-        <v>151.83464007129285</v>
+        <v>151.83464007129291</v>
       </c>
       <c r="J49" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B49,C49,PVT_json)</f>
@@ -15104,11 +15082,11 @@
       </c>
       <c r="K49" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B49,C49,PVT_json)</f>
-        <v>820.06411749452832</v>
+        <v>820.06411749452855</v>
       </c>
       <c r="L49" s="12">
         <f>[1]!PVT_bg_m3m3(B49,C49,PVT_json)</f>
-        <v>4.8277520838183943E-3</v>
+        <v>4.8277520838183926E-3</v>
       </c>
       <c r="M49" s="12">
         <f>[1]!PVT_bw_m3m3(B49,C49,PVT_json)</f>
@@ -15128,7 +15106,7 @@
       </c>
       <c r="Q49" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B49,C49,PVT_json)</f>
-        <v>1772.253745779939</v>
+        <v>1772.2537457799388</v>
       </c>
       <c r="R49" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B49,C49,PVT_json)</f>
@@ -15136,18 +15114,18 @@
       </c>
       <c r="S49" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B49,C49,PVT_json)</f>
-        <v>3.2924884606820539E-5</v>
+        <v>3.2924884606820553E-5</v>
       </c>
       <c r="T49" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B49,C49,PVT_json)</f>
-        <v>1.0486005061337724E-4</v>
+        <v>1.0486005061337717E-4</v>
       </c>
       <c r="U49" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B49,C49,PVT_json)</f>
-        <v>4.9864510387451991E-3</v>
+        <v>4.9864510387410401E-3</v>
       </c>
     </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B50" s="7">
         <v>190.24</v>
       </c>
@@ -15161,11 +15139,11 @@
       </c>
       <c r="E50" s="8">
         <f>[1]!PVT_bo_m3m3(B50,C50,PVT_json)</f>
-        <v>1.154684854379308</v>
+        <v>1.1546848543793078</v>
       </c>
       <c r="F50" s="9">
         <f>[1]!PVT_mu_oil_cP(B50,C50,PVT_json)</f>
-        <v>1.5744522715735518</v>
+        <v>1.5744522715735527</v>
       </c>
       <c r="G50" s="10">
         <f>[1]!PVT_mu_gas_cP(B50,C50,PVT_json)</f>
@@ -15173,11 +15151,11 @@
       </c>
       <c r="H50" s="8">
         <f>[1]!PVT_mu_wat_cP(B50,C50,PVT_json)</f>
-        <v>0.93988346952239465</v>
+        <v>0.93988346952239354</v>
       </c>
       <c r="I50" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B50,C50,PVT_json)</f>
-        <v>159.21255882955802</v>
+        <v>159.21255882955808</v>
       </c>
       <c r="J50" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B50,C50,PVT_json)</f>
@@ -15185,11 +15163,11 @@
       </c>
       <c r="K50" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B50,C50,PVT_json)</f>
-        <v>820.97067126559818</v>
+        <v>820.9706712655983</v>
       </c>
       <c r="L50" s="12">
         <f>[1]!PVT_bg_m3m3(B50,C50,PVT_json)</f>
-        <v>4.604033785957304E-3</v>
+        <v>4.6040337859573023E-3</v>
       </c>
       <c r="M50" s="12">
         <f>[1]!PVT_bw_m3m3(B50,C50,PVT_json)</f>
@@ -15197,7 +15175,7 @@
       </c>
       <c r="N50" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B50,C50,PVT_json)</f>
-        <v>2.271533665354853E-2</v>
+        <v>2.2715336653548534E-2</v>
       </c>
       <c r="O50" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B50,C50,PVT_json)</f>
@@ -15209,7 +15187,7 @@
       </c>
       <c r="Q50" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B50,C50,PVT_json)</f>
-        <v>1783.5025425591439</v>
+        <v>1783.5025425591436</v>
       </c>
       <c r="R50" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B50,C50,PVT_json)</f>
@@ -15217,18 +15195,18 @@
       </c>
       <c r="S50" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B50,C50,PVT_json)</f>
-        <v>3.2848121707259892E-5</v>
+        <v>3.2848121707259906E-5</v>
       </c>
       <c r="T50" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B50,C50,PVT_json)</f>
-        <v>9.9370111041734908E-5</v>
+        <v>9.9370111041734814E-5</v>
       </c>
       <c r="U50" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B50,C50,PVT_json)</f>
-        <v>4.5486800289187583E-3</v>
+        <v>4.5486800289201356E-3</v>
       </c>
     </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B51" s="7">
         <v>200.2</v>
       </c>
@@ -15242,23 +15220,23 @@
       </c>
       <c r="E51" s="8">
         <f>[1]!PVT_bo_m3m3(B51,C51,PVT_json)</f>
-        <v>1.1535366036244399</v>
+        <v>1.1535366036244397</v>
       </c>
       <c r="F51" s="9">
         <f>[1]!PVT_mu_oil_cP(B51,C51,PVT_json)</f>
-        <v>1.6223262473590112</v>
+        <v>1.6223262473590123</v>
       </c>
       <c r="G51" s="10">
         <f>[1]!PVT_mu_gas_cP(B51,C51,PVT_json)</f>
-        <v>2.0462990438987645E-2</v>
+        <v>2.0462990438987638E-2</v>
       </c>
       <c r="H51" s="8">
         <f>[1]!PVT_mu_wat_cP(B51,C51,PVT_json)</f>
-        <v>0.94691975954656449</v>
+        <v>0.94691975954656327</v>
       </c>
       <c r="I51" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B51,C51,PVT_json)</f>
-        <v>166.26488073925313</v>
+        <v>166.26488073925319</v>
       </c>
       <c r="J51" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B51,C51,PVT_json)</f>
@@ -15266,11 +15244,11 @@
       </c>
       <c r="K51" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B51,C51,PVT_json)</f>
-        <v>821.78788000439624</v>
+        <v>821.78788000439636</v>
       </c>
       <c r="L51" s="12">
         <f>[1]!PVT_bg_m3m3(B51,C51,PVT_json)</f>
-        <v>4.4087482379972188E-3</v>
+        <v>4.4087482379972179E-3</v>
       </c>
       <c r="M51" s="12">
         <f>[1]!PVT_bw_m3m3(B51,C51,PVT_json)</f>
@@ -15278,7 +15256,7 @@
       </c>
       <c r="N51" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B51,C51,PVT_json)</f>
-        <v>2.2426430382489454E-2</v>
+        <v>2.2426430382489457E-2</v>
       </c>
       <c r="O51" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B51,C51,PVT_json)</f>
@@ -15290,7 +15268,7 @@
       </c>
       <c r="Q51" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B51,C51,PVT_json)</f>
-        <v>1797.267685307892</v>
+        <v>1797.2676853078917</v>
       </c>
       <c r="R51" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B51,C51,PVT_json)</f>
@@ -15298,18 +15276,18 @@
       </c>
       <c r="S51" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B51,C51,PVT_json)</f>
-        <v>3.2771715913673899E-5</v>
+        <v>3.2771715913673913E-5</v>
       </c>
       <c r="T51" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B51,C51,PVT_json)</f>
-        <v>9.4426423199698545E-5</v>
+        <v>9.4426423199698477E-5</v>
       </c>
       <c r="U51" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B51,C51,PVT_json)</f>
         <v>4.161065204668986E-3</v>
       </c>
     </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B52" s="7">
         <v>210.16</v>
       </c>
@@ -15323,19 +15301,19 @@
       </c>
       <c r="E52" s="8">
         <f>[1]!PVT_bo_m3m3(B52,C52,PVT_json)</f>
-        <v>1.1524981743992879</v>
+        <v>1.1524981743992877</v>
       </c>
       <c r="F52" s="9">
         <f>[1]!PVT_mu_oil_cP(B52,C52,PVT_json)</f>
-        <v>1.6717010831085291</v>
+        <v>1.6717010831085302</v>
       </c>
       <c r="G52" s="10">
         <f>[1]!PVT_mu_gas_cP(B52,C52,PVT_json)</f>
-        <v>2.1057606715007234E-2</v>
+        <v>2.1057606715007227E-2</v>
       </c>
       <c r="H52" s="8">
         <f>[1]!PVT_mu_wat_cP(B52,C52,PVT_json)</f>
-        <v>0.9540661411193504</v>
+        <v>0.95406614111934906</v>
       </c>
       <c r="I52" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B52,C52,PVT_json)</f>
@@ -15347,7 +15325,7 @@
       </c>
       <c r="K52" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B52,C52,PVT_json)</f>
-        <v>822.52833111349844</v>
+        <v>822.52833111349867</v>
       </c>
       <c r="L52" s="12">
         <f>[1]!PVT_bg_m3m3(B52,C52,PVT_json)</f>
@@ -15359,7 +15337,7 @@
       </c>
       <c r="N52" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B52,C52,PVT_json)</f>
-        <v>2.2141198581887508E-2</v>
+        <v>2.2141198581887511E-2</v>
       </c>
       <c r="O52" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B52,C52,PVT_json)</f>
@@ -15371,7 +15349,7 @@
       </c>
       <c r="Q52" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B52,C52,PVT_json)</f>
-        <v>1813.2393462205036</v>
+        <v>1813.2393462205034</v>
       </c>
       <c r="R52" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B52,C52,PVT_json)</f>
@@ -15379,18 +15357,18 @@
       </c>
       <c r="S52" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B52,C52,PVT_json)</f>
-        <v>3.2695664739925253E-5</v>
+        <v>3.2695664739925259E-5</v>
       </c>
       <c r="T52" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B52,C52,PVT_json)</f>
-        <v>8.9951322442803814E-5</v>
+        <v>8.9951322442803733E-5</v>
       </c>
       <c r="U52" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B52,C52,PVT_json)</f>
         <v>3.8175450846443947E-3</v>
       </c>
     </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B53" s="7">
         <v>220.12</v>
       </c>
@@ -15404,23 +15382,23 @@
       </c>
       <c r="E53" s="8">
         <f>[1]!PVT_bo_m3m3(B53,C53,PVT_json)</f>
-        <v>1.1515545307250845</v>
+        <v>1.1515545307250843</v>
       </c>
       <c r="F53" s="9">
         <f>[1]!PVT_mu_oil_cP(B53,C53,PVT_json)</f>
-        <v>1.7224494190043653</v>
+        <v>1.7224494190043667</v>
       </c>
       <c r="G53" s="10">
         <f>[1]!PVT_mu_gas_cP(B53,C53,PVT_json)</f>
-        <v>2.164693062048741E-2</v>
+        <v>2.1646930620487406E-2</v>
       </c>
       <c r="H53" s="8">
         <f>[1]!PVT_mu_wat_cP(B53,C53,PVT_json)</f>
-        <v>0.96132261424075238</v>
+        <v>0.96132261424075138</v>
       </c>
       <c r="I53" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B53,C53,PVT_json)</f>
-        <v>179.42664126080513</v>
+        <v>179.42664126080516</v>
       </c>
       <c r="J53" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B53,C53,PVT_json)</f>
@@ -15428,19 +15406,19 @@
       </c>
       <c r="K53" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B53,C53,PVT_json)</f>
-        <v>823.20235360726576</v>
+        <v>823.20235360726588</v>
       </c>
       <c r="L53" s="12">
         <f>[1]!PVT_bg_m3m3(B53,C53,PVT_json)</f>
-        <v>4.0853464950866506E-3</v>
+        <v>4.0853464950866497E-3</v>
       </c>
       <c r="M53" s="12">
         <f>[1]!PVT_bw_m3m3(B53,C53,PVT_json)</f>
-        <v>1.0052772879556284</v>
+        <v>1.0052772879556282</v>
       </c>
       <c r="N53" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B53,C53,PVT_json)</f>
-        <v>2.1859594517786067E-2</v>
+        <v>2.1859594517786071E-2</v>
       </c>
       <c r="O53" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B53,C53,PVT_json)</f>
@@ -15452,7 +15430,7 @@
       </c>
       <c r="Q53" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B53,C53,PVT_json)</f>
-        <v>1831.1410323141026</v>
+        <v>1831.1410323141022</v>
       </c>
       <c r="R53" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B53,C53,PVT_json)</f>
@@ -15460,18 +15438,18 @@
       </c>
       <c r="S53" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B53,C53,PVT_json)</f>
-        <v>3.2619965722900872E-5</v>
+        <v>3.2619965722900879E-5</v>
       </c>
       <c r="T53" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B53,C53,PVT_json)</f>
-        <v>8.5881200820369109E-5</v>
+        <v>8.5881200820369042E-5</v>
       </c>
       <c r="U53" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B53,C53,PVT_json)</f>
-        <v>3.5126588071723703E-3</v>
+        <v>3.5126588071656612E-3</v>
       </c>
     </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B54" s="7">
         <v>230.08</v>
       </c>
@@ -15485,23 +15463,23 @@
       </c>
       <c r="E54" s="8">
         <f>[1]!PVT_bo_m3m3(B54,C54,PVT_json)</f>
-        <v>1.1506932615900212</v>
+        <v>1.1506932615900209</v>
       </c>
       <c r="F54" s="9">
         <f>[1]!PVT_mu_oil_cP(B54,C54,PVT_json)</f>
-        <v>1.7744443457903811</v>
+        <v>1.7744443457903813</v>
       </c>
       <c r="G54" s="10">
         <f>[1]!PVT_mu_gas_cP(B54,C54,PVT_json)</f>
-        <v>2.222988841787437E-2</v>
+        <v>2.222988841787436E-2</v>
       </c>
       <c r="H54" s="8">
         <f>[1]!PVT_mu_wat_cP(B54,C54,PVT_json)</f>
-        <v>0.96868917891077067</v>
+        <v>0.96868917891076944</v>
       </c>
       <c r="I54" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B54,C54,PVT_json)</f>
-        <v>185.56039675941105</v>
+        <v>185.56039675941111</v>
       </c>
       <c r="J54" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B54,C54,PVT_json)</f>
@@ -15509,19 +15487,19 @@
       </c>
       <c r="K54" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B54,C54,PVT_json)</f>
-        <v>823.81850284767563</v>
+        <v>823.81850284767575</v>
       </c>
       <c r="L54" s="12">
         <f>[1]!PVT_bg_m3m3(B54,C54,PVT_json)</f>
-        <v>3.9503041209294218E-3</v>
+        <v>3.950304120929421E-3</v>
       </c>
       <c r="M54" s="12">
         <f>[1]!PVT_bw_m3m3(B54,C54,PVT_json)</f>
-        <v>1.0049565810784553</v>
+        <v>1.0049565810784551</v>
       </c>
       <c r="N54" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B54,C54,PVT_json)</f>
-        <v>2.1581572050616935E-2</v>
+        <v>2.1581572050616938E-2</v>
       </c>
       <c r="O54" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B54,C54,PVT_json)</f>
@@ -15541,18 +15519,18 @@
       </c>
       <c r="S54" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B54,C54,PVT_json)</f>
-        <v>3.2544616422246003E-5</v>
+        <v>3.2544616422246009E-5</v>
       </c>
       <c r="T54" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B54,C54,PVT_json)</f>
-        <v>8.2163464553979695E-5</v>
+        <v>8.2163464553979641E-5</v>
       </c>
       <c r="U54" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B54,C54,PVT_json)</f>
-        <v>3.2415372867212271E-3</v>
+        <v>3.2415372867238821E-3</v>
       </c>
     </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B55" s="7">
         <v>240.04</v>
       </c>
@@ -15566,19 +15544,19 @@
       </c>
       <c r="E55" s="8">
         <f>[1]!PVT_bo_m3m3(B55,C55,PVT_json)</f>
-        <v>1.1499040320855165</v>
+        <v>1.1499040320855163</v>
       </c>
       <c r="F55" s="9">
         <f>[1]!PVT_mu_oil_cP(B55,C55,PVT_json)</f>
-        <v>1.8275588769643218</v>
+        <v>1.8275588769643232</v>
       </c>
       <c r="G55" s="10">
         <f>[1]!PVT_mu_gas_cP(B55,C55,PVT_json)</f>
-        <v>2.2805673430647554E-2</v>
+        <v>2.2805673430647544E-2</v>
       </c>
       <c r="H55" s="8">
         <f>[1]!PVT_mu_wat_cP(B55,C55,PVT_json)</f>
-        <v>0.97616583512940491</v>
+        <v>0.9761658351294038</v>
       </c>
       <c r="I55" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B55,C55,PVT_json)</f>
@@ -15590,7 +15568,7 @@
       </c>
       <c r="K55" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B55,C55,PVT_json)</f>
-        <v>824.38392557049622</v>
+        <v>824.38392557049644</v>
       </c>
       <c r="L55" s="12">
         <f>[1]!PVT_bg_m3m3(B55,C55,PVT_json)</f>
@@ -15614,7 +15592,7 @@
       </c>
       <c r="Q55" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B55,C55,PVT_json)</f>
-        <v>1871.789512976419</v>
+        <v>1871.7895129764195</v>
       </c>
       <c r="R55" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B55,C55,PVT_json)</f>
@@ -15622,18 +15600,18 @@
       </c>
       <c r="S55" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B55,C55,PVT_json)</f>
-        <v>3.2469614420101945E-5</v>
+        <v>3.2469614420101958E-5</v>
       </c>
       <c r="T55" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B55,C55,PVT_json)</f>
-        <v>7.8754248977585604E-5</v>
+        <v>7.875424897758555E-5</v>
       </c>
       <c r="U55" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B55,C55,PVT_json)</f>
-        <v>2.9998788826381484E-3</v>
+        <v>2.9998788826407735E-3</v>
       </c>
     </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:21" x14ac:dyDescent="0.4">
       <c r="B56" s="7">
         <v>250</v>
       </c>
@@ -15647,11 +15625,11 @@
       </c>
       <c r="E56" s="8">
         <f>[1]!PVT_bo_m3m3(B56,C56,PVT_json)</f>
-        <v>1.149178166728744</v>
+        <v>1.1491781667287437</v>
       </c>
       <c r="F56" s="9">
         <f>[1]!PVT_mu_oil_cP(B56,C56,PVT_json)</f>
-        <v>1.8816656286382238</v>
+        <v>1.8816656286382254</v>
       </c>
       <c r="G56" s="10">
         <f>[1]!PVT_mu_gas_cP(B56,C56,PVT_json)</f>
@@ -15659,31 +15637,31 @@
       </c>
       <c r="H56" s="8">
         <f>[1]!PVT_mu_wat_cP(B56,C56,PVT_json)</f>
-        <v>0.98375258289665535</v>
+        <v>0.98375258289665413</v>
       </c>
       <c r="I56" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B56,C56,PVT_json)</f>
-        <v>197.00519059421646</v>
+        <v>197.00519059421654</v>
       </c>
       <c r="J56" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B56,C56,PVT_json)</f>
-        <v>1095.3081388004327</v>
+        <v>1095.308138800433</v>
       </c>
       <c r="K56" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B56,C56,PVT_json)</f>
-        <v>824.90463832816647</v>
+        <v>824.9046383281667</v>
       </c>
       <c r="L56" s="12">
         <f>[1]!PVT_bg_m3m3(B56,C56,PVT_json)</f>
-        <v>3.7208156688107053E-3</v>
+        <v>3.720815668810704E-3</v>
       </c>
       <c r="M56" s="12">
         <f>[1]!PVT_bw_m3m3(B56,C56,PVT_json)</f>
-        <v>1.0042835993209234</v>
+        <v>1.0042835993209231</v>
       </c>
       <c r="N56" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B56,C56,PVT_json)</f>
-        <v>2.1036090275482471E-2</v>
+        <v>2.1036090275482474E-2</v>
       </c>
       <c r="O56" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B56,C56,PVT_json)</f>
@@ -15695,7 +15673,7 @@
       </c>
       <c r="Q56" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B56,C56,PVT_json)</f>
-        <v>1894.1377412469892</v>
+        <v>1894.1377412469885</v>
       </c>
       <c r="R56" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B56,C56,PVT_json)</f>
@@ -15703,15 +15681,15 @@
       </c>
       <c r="S56" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B56,C56,PVT_json)</f>
-        <v>3.2394957320847461E-5</v>
+        <v>3.2394957320847468E-5</v>
       </c>
       <c r="T56" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B56,C56,PVT_json)</f>
-        <v>7.5616679698318586E-5</v>
+        <v>7.5616679698318546E-5</v>
       </c>
       <c r="U56" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B56,C56,PVT_json)</f>
-        <v>2.7839125929281922E-3</v>
+        <v>2.7839125929281917E-3</v>
       </c>
     </row>
   </sheetData>
@@ -15722,22 +15700,22 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Лист2"/>
   <dimension ref="B5:J84"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.53515625" customWidth="1"/>
+    <col min="3" max="3" width="12.69140625" customWidth="1"/>
+    <col min="4" max="4" width="11.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B7" s="17" t="s">
         <v>2</v>
       </c>
@@ -15745,7 +15723,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B8" s="17" t="s">
         <v>3</v>
       </c>
@@ -15753,7 +15731,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B9" s="17" t="s">
         <v>4</v>
       </c>
@@ -15761,7 +15739,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B10" s="17" t="s">
         <v>5</v>
       </c>
@@ -15769,13 +15747,13 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B11" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="20"/>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B12" s="17" t="s">
         <v>7</v>
       </c>
@@ -15783,19 +15761,19 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B13" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="20"/>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B14" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="20"/>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B15" s="17" t="s">
         <v>10</v>
       </c>
@@ -15803,7 +15781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B16" s="17" t="s">
         <v>11</v>
       </c>
@@ -15812,7 +15790,7 @@
         <v>{"gamma_gas":0.7,"gamma_oil":0.86,"gamma_wat":1.1,"rsb_m3m3":200,"PVT_corr_set":1}</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B19" s="22" t="s">
         <v>41</v>
       </c>
@@ -15823,12 +15801,12 @@
       <c r="G19" s="20"/>
       <c r="H19" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.4">
       <c r="I21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
         <v>42</v>
       </c>
@@ -15853,17 +15831,17 @@
         <v>{"gamma_gas":0.7,"gamma_oil":0.86,"gamma_wat":1.1,"rsb_m3m3":200,"PVT_corr_set":1}</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" s="23">
         <f t="array" ref="C23">[1]!unf_pvt_pb_Standing_MPa(B23,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>3.9516569619629691</v>
+        <v>3.9516569619629709</v>
       </c>
       <c r="D23" s="23">
         <f t="array" ref="D23">[1]!unf_pvt_pb_Valko_McCain_MPa(B23,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>4.7652176471718688</v>
+        <v>4.7652176471718679</v>
       </c>
       <c r="F23" t="str">
         <f t="array" ref="F23">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B23,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -15871,28 +15849,28 @@
       </c>
       <c r="G23">
         <f t="array" ref="G23">[1]!PVT_pb_atma(t_res_C,F23)</f>
-        <v>4.7652176471718688</v>
+        <v>4.7652176471718679</v>
       </c>
       <c r="I23" s="24">
         <f t="array" ref="I23">[1]!PVT_rsb_m3m3(C23,t_res_C,$I$22)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="J23" s="24">
         <f t="array" ref="J23">[1]!PVT_rsb_m3m3(D23,t_res_C,$J$22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B24">
         <v>10</v>
       </c>
       <c r="C24" s="23">
         <f t="array" ref="C24">[1]!unf_pvt_pb_Standing_MPa(B24,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>26.20426525769534</v>
+        <v>26.204265257695354</v>
       </c>
       <c r="D24" s="23">
         <f t="array" ref="D24">[1]!unf_pvt_pb_Valko_McCain_MPa(B24,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>27.622604514708939</v>
+        <v>27.622604514708922</v>
       </c>
       <c r="F24" t="str">
         <f t="array" ref="F24">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B24,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -15900,28 +15878,28 @@
       </c>
       <c r="G24">
         <f t="array" ref="G24">[1]!PVT_pb_atma(t_res_C,F24)</f>
-        <v>27.622604514708939</v>
+        <v>27.622604514708922</v>
       </c>
       <c r="I24" s="24">
         <f t="array" ref="I24">[1]!PVT_rsb_m3m3(C24,t_res_C,$I$22)</f>
-        <v>10.11627514475664</v>
+        <v>10.116275144756642</v>
       </c>
       <c r="J24" s="24">
         <f t="array" ref="J24">[1]!PVT_rsb_m3m3(D24,t_res_C,$J$22)</f>
-        <v>10.08835018373529</v>
+        <v>10.088350183735288</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B25">
         <v>30</v>
       </c>
       <c r="C25" s="23">
         <f t="array" ref="C25">[1]!unf_pvt_pb_Standing_MPa(B25,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>65.220275414584904</v>
+        <v>65.220275414584947</v>
       </c>
       <c r="D25" s="23">
         <f t="array" ref="D25">[1]!unf_pvt_pb_Valko_McCain_MPa(B25,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>70.525292114122379</v>
+        <v>70.525292114122337</v>
       </c>
       <c r="F25" t="str">
         <f t="array" ref="F25">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B25,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -15929,28 +15907,28 @@
       </c>
       <c r="G25">
         <f t="array" ref="G25">[1]!PVT_pb_atma(t_res_C,F25)</f>
-        <v>70.525292114122365</v>
+        <v>70.525292114122337</v>
       </c>
       <c r="I25" s="24">
         <f t="array" ref="I25">[1]!PVT_rsb_m3m3(C25,t_res_C,$I$22)</f>
-        <v>30.027970672961324</v>
+        <v>30.027970672961317</v>
       </c>
       <c r="J25" s="24">
         <f t="array" ref="J25">[1]!PVT_rsb_m3m3(D25,t_res_C,$J$22)</f>
-        <v>30.02699818793042</v>
+        <v>30.02699818793041</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B26">
         <v>50</v>
       </c>
       <c r="C26" s="23">
         <f t="array" ref="C26">[1]!unf_pvt_pb_Standing_MPa(B26,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>99.659129780601489</v>
+        <v>99.65912978060156</v>
       </c>
       <c r="D26" s="23">
         <f t="array" ref="D26">[1]!unf_pvt_pb_Valko_McCain_MPa(B26,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>108.56201380760596</v>
+        <v>108.56201380760591</v>
       </c>
       <c r="F26" t="str">
         <f t="array" ref="F26">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B26,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -15958,28 +15936,28 @@
       </c>
       <c r="G26">
         <f t="array" ref="G26">[1]!PVT_pb_atma(t_res_C,F26)</f>
-        <v>108.56201380760596</v>
+        <v>108.56201380760591</v>
       </c>
       <c r="I26" s="24">
         <f t="array" ref="I26">[1]!PVT_rsb_m3m3(C26,t_res_C,$I$22)</f>
-        <v>50.016124941183307</v>
+        <v>50.016124941183321</v>
       </c>
       <c r="J26" s="24">
         <f t="array" ref="J26">[1]!PVT_rsb_m3m3(D26,t_res_C,$J$22)</f>
-        <v>50.023708263487215</v>
+        <v>50.023708263487187</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B27">
         <v>70</v>
       </c>
       <c r="C27" s="23">
         <f t="array" ref="C27">[1]!unf_pvt_pb_Standing_MPa(B27,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>131.76599936161296</v>
+        <v>131.76599936161304</v>
       </c>
       <c r="D27" s="23">
         <f t="array" ref="D27">[1]!unf_pvt_pb_Valko_McCain_MPa(B27,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>142.80213140879411</v>
+        <v>142.80213140879403</v>
       </c>
       <c r="F27" t="str">
         <f t="array" ref="F27">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B27,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -15987,7 +15965,7 @@
       </c>
       <c r="G27">
         <f t="array" ref="G27">[1]!PVT_pb_atma(t_res_C,F27)</f>
-        <v>142.80213140879411</v>
+        <v>142.80213140879403</v>
       </c>
       <c r="I27" s="24">
         <f t="array" ref="I27">[1]!PVT_rsb_m3m3(C27,t_res_C,$I$22)</f>
@@ -15995,20 +15973,20 @@
       </c>
       <c r="J27" s="24">
         <f t="array" ref="J27">[1]!PVT_rsb_m3m3(D27,t_res_C,$J$22)</f>
-        <v>70.021720723616852</v>
+        <v>70.021720723616838</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B28">
         <v>90</v>
       </c>
       <c r="C28" s="23">
         <f t="array" ref="C28">[1]!unf_pvt_pb_Standing_MPa(B28,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>162.32793720118292</v>
+        <v>162.32793720118303</v>
       </c>
       <c r="D28" s="23">
         <f t="array" ref="D28">[1]!unf_pvt_pb_Valko_McCain_MPa(B28,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>173.89555548851553</v>
+        <v>173.89555548851538</v>
       </c>
       <c r="F28" t="str">
         <f t="array" ref="F28">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B28,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16016,7 +15994,7 @@
       </c>
       <c r="G28">
         <f t="array" ref="G28">[1]!PVT_pb_atma(t_res_C,F28)</f>
-        <v>173.89555548851553</v>
+        <v>173.89555548851538</v>
       </c>
       <c r="I28" s="24">
         <f t="array" ref="I28">[1]!PVT_rsb_m3m3(C28,t_res_C,$I$22)</f>
@@ -16024,20 +16002,20 @@
       </c>
       <c r="J28" s="24">
         <f t="array" ref="J28">[1]!PVT_rsb_m3m3(D28,t_res_C,$J$22)</f>
-        <v>90.02026004431832</v>
+        <v>90.020260044318292</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B29">
         <v>110</v>
       </c>
       <c r="C29" s="23">
         <f t="array" ref="C29">[1]!unf_pvt_pb_Standing_MPa(B29,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>191.74670764006237</v>
+        <v>191.74670764006245</v>
       </c>
       <c r="D29" s="23">
         <f t="array" ref="D29">[1]!unf_pvt_pb_Valko_McCain_MPa(B29,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>202.31347221879295</v>
+        <v>202.31347221879278</v>
       </c>
       <c r="F29" t="str">
         <f t="array" ref="F29">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B29,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16045,28 +16023,28 @@
       </c>
       <c r="G29">
         <f t="array" ref="G29">[1]!PVT_pb_atma(t_res_C,F29)</f>
-        <v>202.31347221879295</v>
+        <v>202.31347221879278</v>
       </c>
       <c r="I29" s="24">
         <f t="array" ref="I29">[1]!PVT_rsb_m3m3(C29,t_res_C,$I$22)</f>
-        <v>110.00711568881246</v>
+        <v>110.00711568881245</v>
       </c>
       <c r="J29" s="24">
         <f t="array" ref="J29">[1]!PVT_rsb_m3m3(D29,t_res_C,$J$22)</f>
-        <v>110.01911270138272</v>
+        <v>110.01911270138271</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B30">
         <v>150</v>
       </c>
       <c r="C30" s="23">
         <f t="array" ref="C30">[1]!unf_pvt_pb_Standing_MPa(B30,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>248.04343216453705</v>
+        <v>248.04343216453722</v>
       </c>
       <c r="D30" s="23">
         <f t="array" ref="D30">[1]!unf_pvt_pb_Valko_McCain_MPa(B30,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>252.49547384519579</v>
+        <v>252.49547384519565</v>
       </c>
       <c r="F30" t="str">
         <f t="array" ref="F30">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B30,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16074,24 +16052,24 @@
       </c>
       <c r="G30">
         <f t="array" ref="G30">[1]!PVT_pb_atma(t_res_C,F30)</f>
-        <v>252.49547384519579</v>
+        <v>252.49547384519565</v>
       </c>
       <c r="I30" s="24">
         <f t="array" ref="I30">[1]!PVT_rsb_m3m3(C30,t_res_C,$I$22)</f>
-        <v>150.00518563484465</v>
+        <v>150.00518563484462</v>
       </c>
       <c r="J30" s="24">
         <f t="array" ref="J30">[1]!PVT_rsb_m3m3(D30,t_res_C,$J$22)</f>
         <v>150.01739860952731</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B31">
         <v>190</v>
       </c>
       <c r="C31" s="23">
         <f t="array" ref="C31">[1]!unf_pvt_pb_Standing_MPa(B31,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>301.81267586222066</v>
+        <v>301.81267586222083</v>
       </c>
       <c r="D31" s="23">
         <f t="array" ref="D31">[1]!unf_pvt_pb_Valko_McCain_MPa(B31,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
@@ -16111,20 +16089,20 @@
       </c>
       <c r="J31" s="24">
         <f t="array" ref="J31">[1]!PVT_rsb_m3m3(D31,t_res_C,$J$22)</f>
-        <v>190.01616734921049</v>
+        <v>190.01616734921052</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B32">
         <v>230</v>
       </c>
       <c r="C32" s="23">
         <f t="array" ref="C32">[1]!unf_pvt_pb_Standing_MPa(B32,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>353.67640780212275</v>
+        <v>353.67640780212287</v>
       </c>
       <c r="D32" s="23">
         <f t="array" ref="D32">[1]!unf_pvt_pb_Valko_McCain_MPa(B32,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>332.67223073950203</v>
+        <v>332.67223073950186</v>
       </c>
       <c r="F32" t="str">
         <f t="array" ref="F32">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B32,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16132,28 +16110,28 @@
       </c>
       <c r="G32">
         <f t="array" ref="G32">[1]!PVT_pb_atma(t_res_C,F32)</f>
-        <v>332.67223073950203</v>
+        <v>332.67223073950191</v>
       </c>
       <c r="I32" s="24">
         <f t="array" ref="I32">[1]!PVT_rsb_m3m3(C32,t_res_C,$I$22)</f>
-        <v>230.00336210460028</v>
+        <v>230.00336210460026</v>
       </c>
       <c r="J32" s="24">
         <f t="array" ref="J32">[1]!PVT_rsb_m3m3(D32,t_res_C,$J$22)</f>
-        <v>230.01523869147576</v>
+        <v>230.01523869147599</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B33">
         <v>270</v>
       </c>
       <c r="C33" s="23">
         <f t="array" ref="C33">[1]!unf_pvt_pb_Standing_MPa(B33,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>404.02097397611681</v>
+        <v>404.02097397611703</v>
       </c>
       <c r="D33" s="23">
         <f t="array" ref="D33">[1]!unf_pvt_pb_Valko_McCain_MPa(B33,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>365.15217984314586</v>
+        <v>365.15217984314569</v>
       </c>
       <c r="F33" t="str">
         <f t="array" ref="F33">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B33,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16161,7 +16139,7 @@
       </c>
       <c r="G33">
         <f t="array" ref="G33">[1]!PVT_pb_atma(t_res_C,F33)</f>
-        <v>365.15217984314586</v>
+        <v>365.15217984314569</v>
       </c>
       <c r="I33" s="24">
         <f t="array" ref="I33">[1]!PVT_rsb_m3m3(C33,t_res_C,$I$22)</f>
@@ -16169,20 +16147,20 @@
       </c>
       <c r="J33" s="24">
         <f t="array" ref="J33">[1]!PVT_rsb_m3m3(D33,t_res_C,$J$22)</f>
-        <v>270.01451707721037</v>
+        <v>270.01451707721083</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B34">
         <v>310</v>
       </c>
       <c r="C34" s="23">
         <f t="array" ref="C34">[1]!unf_pvt_pb_Standing_MPa(B34,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>453.10848286447026</v>
+        <v>453.10848286447049</v>
       </c>
       <c r="D34" s="23">
         <f t="array" ref="D34">[1]!unf_pvt_pb_Valko_McCain_MPa(B34,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>393.69006660795321</v>
+        <v>393.69006660795338</v>
       </c>
       <c r="F34" t="str">
         <f t="array" ref="F34">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B34,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16190,28 +16168,28 @@
       </c>
       <c r="G34">
         <f t="array" ref="G34">[1]!PVT_pb_atma(t_res_C,F34)</f>
-        <v>393.69006660795321</v>
+        <v>393.69006660795338</v>
       </c>
       <c r="I34" s="24">
         <f t="array" ref="I34">[1]!PVT_rsb_m3m3(C34,t_res_C,$I$22)</f>
-        <v>310.00248746260195</v>
+        <v>310.00248746260189</v>
       </c>
       <c r="J34" s="24">
         <f t="array" ref="J34">[1]!PVT_rsb_m3m3(D34,t_res_C,$J$22)</f>
-        <v>310.0139461990276</v>
+        <v>310.01394619902834</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B35">
         <v>350</v>
       </c>
       <c r="C35" s="23">
         <f t="array" ref="C35">[1]!unf_pvt_pb_Standing_MPa(B35,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>501.12776305350866</v>
+        <v>501.12776305350894</v>
       </c>
       <c r="D35" s="23">
         <f t="array" ref="D35">[1]!unf_pvt_pb_Valko_McCain_MPa(B35,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>418.89203273740918</v>
+        <v>418.89203273740901</v>
       </c>
       <c r="F35" t="str">
         <f t="array" ref="F35">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B35,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16219,7 +16197,7 @@
       </c>
       <c r="G35">
         <f t="array" ref="G35">[1]!PVT_pb_atma(t_res_C,F35)</f>
-        <v>418.89203273740918</v>
+        <v>418.89203273740895</v>
       </c>
       <c r="I35" s="24">
         <f t="array" ref="I35">[1]!PVT_rsb_m3m3(C35,t_res_C,$I$22)</f>
@@ -16230,17 +16208,17 @@
         <v>350.01349049519706</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B36">
         <v>390</v>
       </c>
       <c r="C36" s="23">
         <f t="array" ref="C36">[1]!unf_pvt_pb_Standing_MPa(B36,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>548.22092849987689</v>
+        <v>548.22092849987712</v>
       </c>
       <c r="D36" s="23">
         <f t="array" ref="D36">[1]!unf_pvt_pb_Valko_McCain_MPa(B36,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>441.23836560123277</v>
+        <v>441.23836560123243</v>
       </c>
       <c r="F36" t="str">
         <f t="array" ref="F36">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B36,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16248,28 +16226,28 @@
       </c>
       <c r="G36">
         <f t="array" ref="G36">[1]!PVT_pb_atma(t_res_C,F36)</f>
-        <v>441.23836560123283</v>
+        <v>441.23836560123249</v>
       </c>
       <c r="I36" s="24">
         <f t="array" ref="I36">[1]!PVT_rsb_m3m3(C36,t_res_C,$I$22)</f>
-        <v>390.00197395933083</v>
+        <v>390.00197395933077</v>
       </c>
       <c r="J36" s="24">
         <f t="array" ref="J36">[1]!PVT_rsb_m3m3(D36,t_res_C,$J$22)</f>
-        <v>390.01312640546115</v>
+        <v>390.01312640546092</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B37">
         <v>430</v>
       </c>
       <c r="C37" s="23">
         <f t="array" ref="C37">[1]!unf_pvt_pb_Standing_MPa(B37,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>594.49855745182049</v>
+        <v>594.49855745182083</v>
       </c>
       <c r="D37" s="23">
         <f t="array" ref="D37">[1]!unf_pvt_pb_Valko_McCain_MPa(B37,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>461.11679300751973</v>
+        <v>461.1167930075195</v>
       </c>
       <c r="F37" t="str">
         <f t="array" ref="F37">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B37,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16277,28 +16255,28 @@
       </c>
       <c r="G37">
         <f t="array" ref="G37">[1]!PVT_pb_atma(t_res_C,F37)</f>
-        <v>461.11679300751973</v>
+        <v>461.1167930075195</v>
       </c>
       <c r="I37" s="24">
         <f t="array" ref="I37">[1]!PVT_rsb_m3m3(C37,t_res_C,$I$22)</f>
-        <v>430.00178927573404</v>
+        <v>430.00178927573398</v>
       </c>
       <c r="J37" s="24">
         <f t="array" ref="J37">[1]!PVT_rsb_m3m3(D37,t_res_C,$J$22)</f>
-        <v>430.01283781039996</v>
+        <v>430.0128378103995</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B38">
         <v>470</v>
       </c>
       <c r="C38" s="23">
         <f t="array" ref="C38">[1]!unf_pvt_pb_Standing_MPa(B38,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>640.04897894804401</v>
+        <v>640.04897894804446</v>
       </c>
       <c r="D38" s="23">
         <f t="array" ref="D38">[1]!unf_pvt_pb_Valko_McCain_MPa(B38,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>478.84516848321897</v>
+        <v>478.84516848321852</v>
       </c>
       <c r="F38" t="str">
         <f t="array" ref="F38">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B38,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16306,28 +16284,28 @@
       </c>
       <c r="G38">
         <f t="array" ref="G38">[1]!PVT_pb_atma(t_res_C,F38)</f>
-        <v>478.84516848321897</v>
+        <v>478.84516848321852</v>
       </c>
       <c r="I38" s="24">
         <f t="array" ref="I38">[1]!PVT_rsb_m3m3(C38,t_res_C,$I$22)</f>
-        <v>470.00163619429253</v>
+        <v>470.0016361942927</v>
       </c>
       <c r="J38" s="24">
         <f t="array" ref="J38">[1]!PVT_rsb_m3m3(D38,t_res_C,$J$22)</f>
-        <v>470.01261347751091</v>
+        <v>470.0126134775108</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B39">
         <v>510</v>
       </c>
       <c r="C39" s="23">
         <f t="array" ref="C39">[1]!unf_pvt_pb_Standing_MPa(B39,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>684.9442641679459</v>
+        <v>684.94426416794636</v>
       </c>
       <c r="D39" s="23">
         <f t="array" ref="D39">[1]!unf_pvt_pb_Valko_McCain_MPa(B39,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>494.68745080004754</v>
+        <v>494.68745080004715</v>
       </c>
       <c r="F39" t="str">
         <f t="array" ref="F39">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B39,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16335,7 +16313,7 @@
       </c>
       <c r="G39">
         <f t="array" ref="G39">[1]!PVT_pb_atma(t_res_C,F39)</f>
-        <v>494.68745080004754</v>
+        <v>494.68745080004715</v>
       </c>
       <c r="I39" s="24">
         <f t="array" ref="I39">[1]!PVT_rsb_m3m3(C39,t_res_C,$I$22)</f>
@@ -16343,20 +16321,20 @@
       </c>
       <c r="J39" s="24">
         <f t="array" ref="J39">[1]!PVT_rsb_m3m3(D39,t_res_C,$J$22)</f>
-        <v>510.01244555520441</v>
+        <v>510.01244555520412</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B40">
         <v>550</v>
       </c>
       <c r="C40" s="23">
         <f t="array" ref="C40">[1]!unf_pvt_pb_Standing_MPa(B40,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>729.24425980965975</v>
+        <v>729.24425980966021</v>
       </c>
       <c r="D40" s="23">
         <f t="array" ref="D40">[1]!unf_pvt_pb_Valko_McCain_MPa(B40,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>508.86527275976425</v>
+        <v>508.86527275976403</v>
       </c>
       <c r="F40" t="str">
         <f t="array" ref="F40">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B40,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16364,7 +16342,7 @@
       </c>
       <c r="G40">
         <f t="array" ref="G40">[1]!PVT_pb_atma(t_res_C,F40)</f>
-        <v>508.8652727597642</v>
+        <v>508.86527275976397</v>
       </c>
       <c r="I40" s="24">
         <f t="array" ref="I40">[1]!PVT_rsb_m3m3(C40,t_res_C,$I$22)</f>
@@ -16372,20 +16350,20 @@
       </c>
       <c r="J40" s="24">
         <f t="array" ref="J40">[1]!PVT_rsb_m3m3(D40,t_res_C,$J$22)</f>
-        <v>550.01232865339978</v>
+        <v>550.01232865340035</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B41">
         <v>590</v>
       </c>
       <c r="C41" s="23">
         <f t="array" ref="C41">[1]!unf_pvt_pb_Standing_MPa(B41,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>772.99939974004769</v>
+        <v>772.99939974004803</v>
       </c>
       <c r="D41" s="23">
         <f t="array" ref="D41">[1]!unf_pvt_pb_Valko_McCain_MPa(B41,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>521.56651174046658</v>
+        <v>521.56651174046624</v>
       </c>
       <c r="F41" t="str">
         <f t="array" ref="F41">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B41,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16393,28 +16371,28 @@
       </c>
       <c r="G41">
         <f t="array" ref="G41">[1]!PVT_pb_atma(t_res_C,F41)</f>
-        <v>521.56651174046658</v>
+        <v>521.56651174046613</v>
       </c>
       <c r="I41" s="24">
         <f t="array" ref="I41">[1]!PVT_rsb_m3m3(C41,t_res_C,$I$22)</f>
-        <v>590.0013020151564</v>
+        <v>590.00130201515628</v>
       </c>
       <c r="J41" s="24">
         <f t="array" ref="J41">[1]!PVT_rsb_m3m3(D41,t_res_C,$J$22)</f>
-        <v>590.01225927372332</v>
+        <v>590.01225927372252</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B42">
         <v>630</v>
       </c>
       <c r="C42" s="23">
         <f t="array" ref="C42">[1]!unf_pvt_pb_Standing_MPa(B42,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>816.25272295477441</v>
+        <v>816.25272295477498</v>
       </c>
       <c r="D42" s="23">
         <f t="array" ref="D42">[1]!unf_pvt_pb_Valko_McCain_MPa(B42,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>532.9517649485374</v>
+        <v>532.95176494853706</v>
       </c>
       <c r="F42" t="str">
         <f t="array" ref="F42">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B42,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16422,7 +16400,7 @@
       </c>
       <c r="G42">
         <f t="array" ref="G42">[1]!PVT_pb_atma(t_res_C,F42)</f>
-        <v>532.9517649485374</v>
+        <v>532.95176494853717</v>
       </c>
       <c r="I42" s="24">
         <f t="array" ref="I42">[1]!PVT_rsb_m3m3(C42,t_res_C,$I$22)</f>
@@ -16430,16 +16408,16 @@
       </c>
       <c r="J42" s="24">
         <f t="array" ref="J42">[1]!PVT_rsb_m3m3(D42,t_res_C,$J$22)</f>
-        <v>630.01223546176209</v>
+        <v>630.01223546176163</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B43">
         <v>670</v>
       </c>
       <c r="C43" s="23">
         <f t="array" ref="C43">[1]!unf_pvt_pb_Standing_MPa(B43,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>859.04135817139502</v>
+        <v>859.04135817139559</v>
       </c>
       <c r="D43" s="23">
         <f t="array" ref="D43">[1]!unf_pvt_pb_Valko_McCain_MPa(B43,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
@@ -16455,14 +16433,14 @@
       </c>
       <c r="I43" s="24">
         <f t="array" ref="I43">[1]!PVT_rsb_m3m3(C43,t_res_C,$I$22)</f>
-        <v>670.00114597835807</v>
+        <v>670.00114597835829</v>
       </c>
       <c r="J43" s="24">
         <f t="array" ref="J43">[1]!PVT_rsb_m3m3(D43,t_res_C,$J$22)</f>
-        <v>670.01225661138756</v>
+        <v>670.01225661138767</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B49" s="22" t="s">
         <v>48</v>
       </c>
@@ -16473,7 +16451,7 @@
       <c r="G49" s="20"/>
       <c r="H49" s="20"/>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B51" s="17" t="s">
         <v>42</v>
       </c>
@@ -16485,20 +16463,20 @@
         <v>{"gamma_gas":0.7,"gamma_oil":0.86,"gamma_wat":1.1,"rsb_m3m3":240,"PVT_corr_set":1}</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B52" s="17" t="s">
         <v>49</v>
       </c>
       <c r="C52" s="21">
         <f t="array" ref="C52">[1]!PVT_pb_atma(t_res_C,F51)</f>
-        <v>341.20095644869366</v>
+        <v>341.20095644869355</v>
       </c>
       <c r="F52" t="str">
         <f t="array" ref="F52">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,C51,C52,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
         <v>{"gamma_gas":0.7,"gamma_oil":0.86,"gamma_wat":1.1,"rsb_m3m3":240,"pb_atma":341.201,"t_res_C":80,"PVT_corr_set":1}</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B54" s="17" t="s">
         <v>50</v>
       </c>
@@ -16506,16 +16484,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B55" s="17" t="s">
         <v>51</v>
       </c>
       <c r="C55" s="18">
         <f>C52</f>
-        <v>341.20095644869366</v>
+        <v>341.20095644869355</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B56" s="17" t="s">
         <v>52</v>
       </c>
@@ -16523,7 +16501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B57" s="17" t="s">
         <v>53</v>
       </c>
@@ -16532,17 +16510,17 @@
         <v>[1,14.608,28.216,41.824,55.432,69.04,82.648,96.256,109.864,123.472,137.08,150.688,164.296,177.904,191.513,205.121,218.729,232.337,245.945,259.553,273.161,286.769,300.377,313.985,327.593,341.201]</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C59">
         <f t="array" ref="C59:C84">[1]!decode_json($C$57)</f>
         <v>1</v>
       </c>
       <c r="D59">
         <f t="array" ref="D59">[1]!PVT_rs_m3m3(C59,t_res_C,$F$52)</f>
-        <v>8.2271659062697899E-2</v>
+        <v>8.2271659062691072E-2</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C60">
         <v>14.608000000000001</v>
       </c>
@@ -16551,196 +16529,196 @@
         <v>18.022014659826571</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C61">
         <v>28.216000000000001</v>
       </c>
       <c r="D61">
         <f t="array" ref="D61">[1]!PVT_rs_m3m3(C61,t_res_C,$F$52)</f>
-        <v>28.259056830115654</v>
+        <v>28.259056830115661</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C62">
         <v>41.823999999999998</v>
       </c>
       <c r="D62">
         <f t="array" ref="D62">[1]!PVT_rs_m3m3(C62,t_res_C,$F$52)</f>
-        <v>36.880577262600646</v>
+        <v>36.880577262600667</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C63">
         <v>55.432000000000002</v>
       </c>
       <c r="D63">
         <f t="array" ref="D63">[1]!PVT_rs_m3m3(C63,t_res_C,$F$52)</f>
-        <v>44.700919980779858</v>
+        <v>44.700919980779865</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C64">
         <v>69.040000000000006</v>
       </c>
       <c r="D64">
         <f t="array" ref="D64">[1]!PVT_rs_m3m3(C64,t_res_C,$F$52)</f>
-        <v>52.074681365632486</v>
+        <v>52.074681365632507</v>
       </c>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C65">
         <v>82.647999999999996</v>
       </c>
       <c r="D65">
         <f t="array" ref="D65">[1]!PVT_rs_m3m3(C65,t_res_C,$F$52)</f>
-        <v>59.2054516936917</v>
+        <v>59.205451693691721</v>
       </c>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C66">
         <v>96.256</v>
       </c>
       <c r="D66">
         <f t="array" ref="D66">[1]!PVT_rs_m3m3(C66,t_res_C,$F$52)</f>
-        <v>66.229037764954583</v>
+        <v>66.229037764954597</v>
       </c>
     </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C67">
         <v>109.864</v>
       </c>
       <c r="D67">
         <f t="array" ref="D67">[1]!PVT_rs_m3m3(C67,t_res_C,$F$52)</f>
-        <v>73.245164700554881</v>
+        <v>73.245164700554909</v>
       </c>
     </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C68">
         <v>123.47199999999999</v>
       </c>
       <c r="D68">
         <f t="array" ref="D68">[1]!PVT_rs_m3m3(C68,t_res_C,$F$52)</f>
-        <v>80.332105990458729</v>
+        <v>80.332105990458743</v>
       </c>
     </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C69">
         <v>137.08000000000001</v>
       </c>
       <c r="D69">
         <f t="array" ref="D69">[1]!PVT_rs_m3m3(C69,t_res_C,$F$52)</f>
-        <v>87.554340117432034</v>
+        <v>87.554340117432062</v>
       </c>
     </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C70">
         <v>150.68799999999999</v>
       </c>
       <c r="D70">
         <f t="array" ref="D70">[1]!PVT_rs_m3m3(C70,t_res_C,$F$52)</f>
-        <v>94.96693491792567</v>
+        <v>94.966934917925684</v>
       </c>
     </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C71">
         <v>164.29599999999999</v>
       </c>
       <c r="D71">
         <f t="array" ref="D71">[1]!PVT_rs_m3m3(C71,t_res_C,$F$52)</f>
-        <v>102.61823487507657</v>
+        <v>102.61823487507661</v>
       </c>
     </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C72">
         <v>177.904</v>
       </c>
       <c r="D72">
         <f t="array" ref="D72">[1]!PVT_rs_m3m3(C72,t_res_C,$F$52)</f>
-        <v>110.55159866234952</v>
+        <v>110.55159866234955</v>
       </c>
     </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C73">
         <v>191.51300000000001</v>
       </c>
       <c r="D73">
         <f t="array" ref="D73">[1]!PVT_rs_m3m3(C73,t_res_C,$F$52)</f>
-        <v>118.80719158854971</v>
+        <v>118.80719158854976</v>
       </c>
     </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C74">
         <v>205.12100000000001</v>
       </c>
       <c r="D74">
         <f t="array" ref="D74">[1]!PVT_rs_m3m3(C74,t_res_C,$F$52)</f>
-        <v>127.42035661422511</v>
+        <v>127.42035661422514</v>
       </c>
     </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C75">
         <v>218.72900000000001</v>
       </c>
       <c r="D75">
         <f t="array" ref="D75">[1]!PVT_rs_m3m3(C75,t_res_C,$F$52)</f>
-        <v>136.42584203788834</v>
+        <v>136.4258420378884</v>
       </c>
     </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C76">
         <v>232.33699999999999</v>
       </c>
       <c r="D76">
         <f t="array" ref="D76">[1]!PVT_rs_m3m3(C76,t_res_C,$F$52)</f>
-        <v>145.85583986198873</v>
+        <v>145.85583986198881</v>
       </c>
     </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C77">
         <v>245.94499999999999</v>
       </c>
       <c r="D77">
         <f t="array" ref="D77">[1]!PVT_rs_m3m3(C77,t_res_C,$F$52)</f>
-        <v>155.74091151119103</v>
+        <v>155.74091151119109</v>
       </c>
     </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C78">
         <v>259.553</v>
       </c>
       <c r="D78">
         <f t="array" ref="D78">[1]!PVT_rs_m3m3(C78,t_res_C,$F$52)</f>
-        <v>166.11024348451087</v>
+        <v>166.1102434845109</v>
       </c>
     </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C79">
         <v>273.161</v>
       </c>
       <c r="D79">
         <f t="array" ref="D79">[1]!PVT_rs_m3m3(C79,t_res_C,$F$52)</f>
-        <v>176.99184801102425</v>
+        <v>176.99184801102427</v>
       </c>
     </row>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C80">
         <v>286.76900000000001</v>
       </c>
       <c r="D80">
         <f t="array" ref="D80">[1]!PVT_rs_m3m3(C80,t_res_C,$F$52)</f>
-        <v>188.41272296709593</v>
+        <v>188.4127229670959</v>
       </c>
     </row>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C81">
         <v>300.37700000000001</v>
       </c>
       <c r="D81">
         <f t="array" ref="D81">[1]!PVT_rs_m3m3(C81,t_res_C,$F$52)</f>
-        <v>200.39898108307841</v>
+        <v>200.39898108307844</v>
       </c>
     </row>
-    <row r="82" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C82">
         <v>313.98500000000001</v>
       </c>
@@ -16749,7 +16727,7 @@
         <v>212.97595563227983</v>
       </c>
     </row>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C83">
         <v>327.59300000000002</v>
       </c>
@@ -16758,7 +16736,7 @@
         <v>226.16828785320072</v>
       </c>
     </row>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:4" x14ac:dyDescent="0.4">
       <c r="C84">
         <v>341.20100000000002</v>
       </c>

--- a/examples/ex010.PVT.xlsx
+++ b/examples/ex010.PVT.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\unifloc\unifloc_vba\examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unifloc\unifloc_vba\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF1CB34-BE2C-4482-9845-2117489513B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09010B99-C66B-497A-A4E8-43CBCEC6DE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="графики от давления" sheetId="1" r:id="rId1"/>
@@ -762,40 +762,40 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.40799738531524399</c:v>
+                  <c:v>0.40799738531524365</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.2876798732693988</c:v>
+                  <c:v>7.2876798732693953</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15.871341736906073</c:v>
+                  <c:v>15.871341736906061</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>25.364647959839669</c:v>
+                  <c:v>25.364647959839644</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>35.514409899723063</c:v>
+                  <c:v>35.514409899723034</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46.186737869660327</c:v>
+                  <c:v>46.186737869660284</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>57.297169628895695</c:v>
+                  <c:v>57.297169628895659</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>68.78698135405061</c:v>
+                  <c:v>68.786981354050553</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>80.612708067538293</c:v>
+                  <c:v>80.61270806753825</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>92.74073547077991</c:v>
+                  <c:v>92.740735470779853</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>105.14420670385927</c:v>
+                  <c:v>105.1442067038592</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>117.80111687961013</c:v>
+                  <c:v>117.80111687961006</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>120</c:v>
@@ -1401,7 +1401,7 @@
                   <c:v>1.0397635791746314</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.0526284121419129</c:v>
+                  <c:v>1.0526284121419127</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1.0665526535566601</c:v>
@@ -1425,46 +1425,46 @@
                   <c:v>1.1677607082700996</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.1681208648753278</c:v>
+                  <c:v>1.1681208648753281</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.1653095028377116</c:v>
+                  <c:v>1.1653095028377118</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.1629022995124059</c:v>
+                  <c:v>1.1629022995124061</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.1608179512669563</c:v>
+                  <c:v>1.1608179512669565</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.1589955906641818</c:v>
+                  <c:v>1.158995590664182</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.1573887453687506</c:v>
+                  <c:v>1.1573887453687508</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.155961320312646</c:v>
+                  <c:v>1.1559613203126462</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.1546848543793078</c:v>
+                  <c:v>1.154684854379308</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.1535366036244397</c:v>
+                  <c:v>1.1535366036244399</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.1524981743992877</c:v>
+                  <c:v>1.1524981743992879</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.1515545307250843</c:v>
+                  <c:v>1.1515545307250845</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.1506932615900209</c:v>
+                  <c:v>1.1506932615900212</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.1499040320855163</c:v>
+                  <c:v>1.1499040320855165</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.1491781667287437</c:v>
+                  <c:v>1.149178166728744</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1608,82 +1608,82 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>1.0708724189280914</c:v>
+                  <c:v>1.0708724189280916</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>9.610985616575074E-2</c:v>
+                  <c:v>9.6109856165750726E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.947136451393775E-2</c:v>
+                  <c:v>4.9471364513937736E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.2889633443549185E-2</c:v>
+                  <c:v>3.2889633443549199E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.4380684165360097E-2</c:v>
+                  <c:v>2.4380684165360093E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.9205142672414865E-2</c:v>
+                  <c:v>1.9205142672414868E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.5732975062920217E-2</c:v>
+                  <c:v>1.5732975062920214E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3252751759032443E-2</c:v>
+                  <c:v>1.3252751759032448E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.1403718927349822E-2</c:v>
+                  <c:v>1.1403718927349827E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>9.9825502937632201E-3</c:v>
+                  <c:v>9.9825502937632253E-3</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>8.8651544161101083E-3</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>7.9709595167177967E-3</c:v>
+                  <c:v>7.9709595167177984E-3</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>7.2450472603989326E-3</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>6.6485393070144037E-3</c:v>
+                  <c:v>6.6485393070144045E-3</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>6.1530936470736543E-3</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>5.7375767199946692E-3</c:v>
+                  <c:v>5.7375767199946684E-3</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.3859511211398012E-3</c:v>
+                  <c:v>5.385951121139803E-3</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>5.0858769654652343E-3</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>4.8277520838183926E-3</c:v>
+                  <c:v>4.8277520838183943E-3</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>4.6040337859573023E-3</c:v>
+                  <c:v>4.604033785957304E-3</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>4.4087482379972179E-3</c:v>
+                  <c:v>4.4087482379972188E-3</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>4.2371289485194606E-3</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>4.0853464950866497E-3</c:v>
+                  <c:v>4.0853464950866506E-3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>3.950304120929421E-3</c:v>
+                  <c:v>3.9503041209294218E-3</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>3.8294816963589679E-3</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>3.720815668810704E-3</c:v>
+                  <c:v>3.7208156688107053E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1827,13 +1827,13 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>1.0096706043181005</c:v>
+                  <c:v>1.0096706043181007</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>1.0095813961309568</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0094816652760841</c:v>
+                  <c:v>1.0094816652760843</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1.0093714117534831</c:v>
@@ -1842,43 +1842,43 @@
                   <c:v>1.0092506355631534</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.009119336705095</c:v>
+                  <c:v>1.0091193367050952</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1.0089775151793081</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.0088251709857925</c:v>
+                  <c:v>1.0088251709857927</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.0086623041245484</c:v>
+                  <c:v>1.0086623041245486</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.0084889145955758</c:v>
+                  <c:v>1.008488914595576</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.0083050023988744</c:v>
+                  <c:v>1.0083050023988747</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>1.0081105675344446</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.0079056100022861</c:v>
+                  <c:v>1.0079056100022863</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1.007690129802399</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.0074641269347833</c:v>
+                  <c:v>1.0074641269347835</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.007227601399439</c:v>
+                  <c:v>1.0072276013994392</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>1.0069805531963663</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.0067229823255646</c:v>
+                  <c:v>1.0067229823255648</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>1.0064548887870346</c:v>
@@ -1893,16 +1893,16 @@
                   <c:v>1.0055874721650728</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.0052772879556282</c:v>
+                  <c:v>1.0052772879556284</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.0049565810784551</c:v>
+                  <c:v>1.0049565810784553</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>1.0046253515335535</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.0042835993209231</c:v>
+                  <c:v>1.0042835993209234</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2463,82 +2463,82 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>9.7713156529231906</c:v>
+                  <c:v>9.7713156529231888</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.9930993456852475</c:v>
+                  <c:v>6.9930993456852466</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.1397568149463044</c:v>
+                  <c:v>5.1397568149463062</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.9709702064959589</c:v>
+                  <c:v>3.9709702064959602</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.1972861301457316</c:v>
+                  <c:v>3.1972861301457325</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.6582574292633621</c:v>
+                  <c:v>2.6582574292633616</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2.2659362081661159</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.9699222555167233</c:v>
+                  <c:v>1.9699222555167235</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.7398587672578569</c:v>
+                  <c:v>1.7398587672578572</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.5566069111111438</c:v>
+                  <c:v>1.556606911111144</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.4076080220116909</c:v>
+                  <c:v>1.4076080220116916</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.2843310127570018</c:v>
+                  <c:v>1.2843310127570022</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.2926930197501159</c:v>
+                  <c:v>1.2926930197501152</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.326191017794796</c:v>
+                  <c:v>1.3261910177947958</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.3622131528629122</c:v>
+                  <c:v>1.3622131528629118</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.4005814298483232</c:v>
+                  <c:v>1.4005814298483223</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.4411346327141075</c:v>
+                  <c:v>1.4411346327141066</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.4837236136051828</c:v>
+                  <c:v>1.4837236136051819</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.5282077500006945</c:v>
+                  <c:v>1.5282077500006936</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.5744522715735527</c:v>
+                  <c:v>1.5744522715735518</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>1.6223262473590123</c:v>
+                  <c:v>1.6223262473590112</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1.6717010831085302</c:v>
+                  <c:v>1.6717010831085291</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1.7224494190043667</c:v>
+                  <c:v>1.7224494190043653</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.7744443457903813</c:v>
+                  <c:v>1.7744443457903811</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.8275588769643232</c:v>
+                  <c:v>1.8275588769643218</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.8816656286382254</c:v>
+                  <c:v>1.8816656286382238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2682,82 +2682,82 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.82711135330023045</c:v>
+                  <c:v>0.82711135330023133</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.83205590390069384</c:v>
+                  <c:v>0.83205590390069484</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.83711054604977353</c:v>
+                  <c:v>0.83711054604977453</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.84227527974746919</c:v>
+                  <c:v>0.84227527974747018</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.84755010499378114</c:v>
+                  <c:v>0.84755010499378214</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.85293502178870917</c:v>
+                  <c:v>0.85293502178871006</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.85843003013225316</c:v>
+                  <c:v>0.85843003013225416</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.86403513002441357</c:v>
+                  <c:v>0.86403513002441446</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.86975032146518971</c:v>
+                  <c:v>0.86975032146519071</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.87557560445458216</c:v>
+                  <c:v>0.87557560445458327</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.88151097899259068</c:v>
+                  <c:v>0.88151097899259179</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.88755644507921549</c:v>
+                  <c:v>0.88755644507921649</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.89371200271445617</c:v>
+                  <c:v>0.89371200271445739</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.89997765189831325</c:v>
+                  <c:v>0.89997765189831436</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.90635339263078618</c:v>
+                  <c:v>0.9063533926307874</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.91283922491187541</c:v>
+                  <c:v>0.91283922491187663</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.91943514874158094</c:v>
+                  <c:v>0.91943514874158194</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.92614116411990222</c:v>
+                  <c:v>0.92614116411990333</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.93295727104683968</c:v>
+                  <c:v>0.9329572710468409</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.93988346952239354</c:v>
+                  <c:v>0.93988346952239465</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.94691975954656327</c:v>
+                  <c:v>0.94691975954656449</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.95406614111934906</c:v>
+                  <c:v>0.9540661411193504</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.96132261424075138</c:v>
+                  <c:v>0.96132261424075238</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.96868917891076944</c:v>
+                  <c:v>0.96868917891077067</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.9761658351294038</c:v>
+                  <c:v>0.97616583512940491</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.98375258289665413</c:v>
+                  <c:v>0.98375258289665535</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2907,7 +2907,7 @@
                   <c:v>1.1803262208544711E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.198625057572044E-2</c:v>
+                  <c:v>1.1986250575720442E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1.220611654701194E-2</c:v>
@@ -2919,61 +2919,61 @@
                   <c:v>1.2750782199815394E-2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.3076968510634199E-2</c:v>
+                  <c:v>1.3076968510634203E-2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.3440112930067171E-2</c:v>
+                  <c:v>1.3440112930067173E-2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.3840188691857094E-2</c:v>
+                  <c:v>1.3840188691857097E-2</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>1.4276159115543989E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.4745918799782593E-2</c:v>
+                  <c:v>1.4745918799782596E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.5246397964708497E-2</c:v>
+                  <c:v>1.5246397964708501E-2</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.5773782410755825E-2</c:v>
+                  <c:v>1.5773782410755829E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.6323793809058015E-2</c:v>
+                  <c:v>1.6323793809058018E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.6891977917657234E-2</c:v>
+                  <c:v>1.6891977917657237E-2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.7473960164598033E-2</c:v>
+                  <c:v>1.7473960164598037E-2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.8065644186917869E-2</c:v>
+                  <c:v>1.8065644186917872E-2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.866334463351298E-2</c:v>
+                  <c:v>1.866334463351299E-2</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.9263857676805878E-2</c:v>
+                  <c:v>1.9263857676805881E-2</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>1.9864480053938104E-2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2.0462990438987638E-2</c:v>
+                  <c:v>2.0462990438987645E-2</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.1057606715007227E-2</c:v>
+                  <c:v>2.1057606715007234E-2</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>2.1646930620487406E-2</c:v>
+                  <c:v>2.164693062048741E-2</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.222988841787436E-2</c:v>
+                  <c:v>2.222988841787437E-2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.2805673430647544E-2</c:v>
+                  <c:v>2.2805673430647554E-2</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>2.3373693925737973E-2</c:v>
@@ -3527,82 +3527,82 @@
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>0.68450731108914853</c:v>
+                  <c:v>0.68450731108914831</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.6268972740510206</c:v>
+                  <c:v>7.6268972740510215</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>14.81705643662777</c:v>
+                  <c:v>14.817056436627773</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>22.287265720310756</c:v>
+                  <c:v>22.287265720310746</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>30.065604190118243</c:v>
+                  <c:v>30.065604190118247</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>38.167901822091991</c:v>
+                  <c:v>38.167901822091984</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46.591315187907206</c:v>
+                  <c:v>46.591315187907213</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>55.310777212770816</c:v>
+                  <c:v>55.310777212770795</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>64.279030785472969</c:v>
+                  <c:v>64.279030785472941</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>73.430133425720641</c:v>
+                  <c:v>73.430133425720598</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>82.685530966942565</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>91.961325165760698</c:v>
+                  <c:v>91.96132516576067</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>101.1753234525675</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>110.25278879326808</c:v>
+                  <c:v>110.25278879326807</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>119.13031753524774</c:v>
+                  <c:v>119.13031753524773</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>127.7577687886117</c:v>
+                  <c:v>127.75776878861171</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>136.09852438558238</c:v>
+                  <c:v>136.09852438558232</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>144.12853574269397</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>151.83464007129291</c:v>
+                  <c:v>151.83464007129285</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>159.21255882955808</c:v>
+                  <c:v>159.21255882955802</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>166.26488073925319</c:v>
+                  <c:v>166.26488073925313</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>172.99921926051653</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>179.42664126080516</c:v>
+                  <c:v>179.42664126080513</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>185.56039675941111</c:v>
+                  <c:v>185.56039675941105</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>191.41493761334542</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>197.00519059421654</c:v>
+                  <c:v>197.00519059421646</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3752,13 +3752,13 @@
                   <c:v>850.07405329425592</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>847.79750461929541</c:v>
+                  <c:v>847.79750461929552</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>844.99285399566725</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>841.73366643388874</c:v>
+                  <c:v>841.73366643388897</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>838.07939496700408</c:v>
@@ -3767,7 +3767,7 @@
                   <c:v>834.08186937898347</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>829.78712419752685</c:v>
+                  <c:v>829.78712419752674</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>825.23630653349448</c:v>
@@ -3782,46 +3782,46 @@
                   <c:v>810.39768506768735</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>811.52766678915111</c:v>
+                  <c:v>811.52766678915089</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>813.48551409866877</c:v>
+                  <c:v>813.48551409866866</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>815.16942601065614</c:v>
+                  <c:v>815.16942601065591</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>816.63313266766897</c:v>
+                  <c:v>816.63313266766875</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>817.91717555780713</c:v>
+                  <c:v>817.91717555780701</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>819.05272000720367</c:v>
+                  <c:v>819.05272000720345</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>820.06411749452855</c:v>
+                  <c:v>820.06411749452832</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>820.9706712655983</c:v>
+                  <c:v>820.97067126559818</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>821.78788000439636</c:v>
+                  <c:v>821.78788000439624</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>822.52833111349867</c:v>
+                  <c:v>822.52833111349844</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>823.20235360726588</c:v>
+                  <c:v>823.20235360726576</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>823.81850284767575</c:v>
+                  <c:v>823.81850284767563</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>824.38392557049644</c:v>
+                  <c:v>824.38392557049622</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>824.9046383281667</c:v>
+                  <c:v>824.90463832816647</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3968,16 +3968,16 @@
                   <c:v>1089.4642225846567</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1089.5604893429659</c:v>
+                  <c:v>1089.5604893429661</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1089.6681315149592</c:v>
+                  <c:v>1089.668131514959</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1089.7871558389757</c:v>
+                  <c:v>1089.7871558389759</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1089.9175697681965</c:v>
+                  <c:v>1089.9175697681967</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>1090.0593814718109</c:v>
@@ -3986,37 +3986,37 @@
                   <c:v>1090.2125998362967</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1090.3772344668148</c:v>
+                  <c:v>1090.3772344668146</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1090.5532956887157</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1090.7407945491618</c:v>
+                  <c:v>1090.7407945491616</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1090.939742818862</c:v>
+                  <c:v>1090.9397428188618</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>1091.1501529939233</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1091.3720382978174</c:v>
+                  <c:v>1091.3720382978172</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1091.6054126834629</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1091.8502908354244</c:v>
+                  <c:v>1091.8502908354242</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1092.1066881722297</c:v>
+                  <c:v>1092.1066881722295</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1092.3746208488044</c:v>
+                  <c:v>1092.3746208488046</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1092.6541057590266</c:v>
+                  <c:v>1092.6541057590264</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>1092.945160538397</c:v>
@@ -4040,7 +4040,7 @@
                   <c:v>1094.9355382291099</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1095.308138800433</c:v>
+                  <c:v>1095.3081388004327</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4580,67 +4580,67 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>3.9516569619629709</c:v>
+                  <c:v>3.9516569619629691</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.204265257695354</c:v>
+                  <c:v>26.20426525769534</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>65.220275414584947</c:v>
+                  <c:v>65.220275414584904</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>99.65912978060156</c:v>
+                  <c:v>99.659129780601489</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>131.76599936161304</c:v>
+                  <c:v>131.76599936161296</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>162.32793720118303</c:v>
+                  <c:v>162.32793720118292</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>191.74670764006245</c:v>
+                  <c:v>191.74670764006237</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>248.04343216453722</c:v>
+                  <c:v>248.04343216453705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>301.81267586222083</c:v>
+                  <c:v>301.81267586222066</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>353.67640780212287</c:v>
+                  <c:v>353.67640780212275</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>404.02097397611703</c:v>
+                  <c:v>404.02097397611681</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>453.10848286447049</c:v>
+                  <c:v>453.10848286447026</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>501.12776305350894</c:v>
+                  <c:v>501.12776305350866</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>548.22092849987712</c:v>
+                  <c:v>548.22092849987689</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>594.49855745182083</c:v>
+                  <c:v>594.49855745182049</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>640.04897894804446</c:v>
+                  <c:v>640.04897894804401</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>684.94426416794636</c:v>
+                  <c:v>684.9442641679459</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>729.24425980966021</c:v>
+                  <c:v>729.24425980965975</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>772.99939974004803</c:v>
+                  <c:v>772.99939974004769</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>816.25272295477498</c:v>
+                  <c:v>816.25272295477441</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>859.04135817139559</c:v>
+                  <c:v>859.04135817139502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4769,64 +4769,64 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>4.7652176471718679</c:v>
+                  <c:v>4.7652176471718688</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.622604514708922</c:v>
+                  <c:v>27.622604514708939</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70.525292114122337</c:v>
+                  <c:v>70.525292114122379</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108.56201380760591</c:v>
+                  <c:v>108.56201380760596</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>142.80213140879403</c:v>
+                  <c:v>142.80213140879411</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>173.89555548851538</c:v>
+                  <c:v>173.89555548851553</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>202.31347221879278</c:v>
+                  <c:v>202.31347221879295</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>252.49547384519565</c:v>
+                  <c:v>252.49547384519579</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>295.46729132686249</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>332.67223073950186</c:v>
+                  <c:v>332.67223073950203</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>365.15217984314569</c:v>
+                  <c:v>365.15217984314586</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>393.69006660795338</c:v>
+                  <c:v>393.69006660795321</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>418.89203273740901</c:v>
+                  <c:v>418.89203273740918</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>441.23836560123243</c:v>
+                  <c:v>441.23836560123277</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>461.1167930075195</c:v>
+                  <c:v>461.11679300751973</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>478.84516848321852</c:v>
+                  <c:v>478.84516848321897</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>494.68745080004715</c:v>
+                  <c:v>494.68745080004754</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>508.86527275976403</c:v>
+                  <c:v>508.86527275976425</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>521.56651174046624</c:v>
+                  <c:v>521.56651174046658</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>532.95176494853706</c:v>
+                  <c:v>532.9517649485374</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>543.15932534142394</c:v>
@@ -5352,67 +5352,67 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>3.9516569619629709</c:v>
+                  <c:v>3.9516569619629691</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.204265257695354</c:v>
+                  <c:v>26.20426525769534</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>65.220275414584947</c:v>
+                  <c:v>65.220275414584904</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>99.65912978060156</c:v>
+                  <c:v>99.659129780601489</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>131.76599936161304</c:v>
+                  <c:v>131.76599936161296</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>162.32793720118303</c:v>
+                  <c:v>162.32793720118292</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>191.74670764006245</c:v>
+                  <c:v>191.74670764006237</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>248.04343216453722</c:v>
+                  <c:v>248.04343216453705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>301.81267586222083</c:v>
+                  <c:v>301.81267586222066</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>353.67640780212287</c:v>
+                  <c:v>353.67640780212275</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>404.02097397611703</c:v>
+                  <c:v>404.02097397611681</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>453.10848286447049</c:v>
+                  <c:v>453.10848286447026</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>501.12776305350894</c:v>
+                  <c:v>501.12776305350866</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>548.22092849987712</c:v>
+                  <c:v>548.22092849987689</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>594.49855745182083</c:v>
+                  <c:v>594.49855745182049</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>640.04897894804446</c:v>
+                  <c:v>640.04897894804401</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>684.94426416794636</c:v>
+                  <c:v>684.9442641679459</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>729.24425980966021</c:v>
+                  <c:v>729.24425980965975</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>772.99939974004803</c:v>
+                  <c:v>772.99939974004769</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>816.25272295477498</c:v>
+                  <c:v>816.25272295477441</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>859.04135817139559</c:v>
+                  <c:v>859.04135817139502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5541,64 +5541,64 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>4.7652176471718679</c:v>
+                  <c:v>4.7652176471718688</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.622604514708922</c:v>
+                  <c:v>27.622604514708939</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70.525292114122337</c:v>
+                  <c:v>70.525292114122379</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108.56201380760591</c:v>
+                  <c:v>108.56201380760596</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>142.80213140879403</c:v>
+                  <c:v>142.80213140879411</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>173.89555548851538</c:v>
+                  <c:v>173.89555548851553</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>202.31347221879278</c:v>
+                  <c:v>202.31347221879295</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>252.49547384519565</c:v>
+                  <c:v>252.49547384519579</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>295.46729132686249</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>332.67223073950186</c:v>
+                  <c:v>332.67223073950203</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>365.15217984314569</c:v>
+                  <c:v>365.15217984314586</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>393.69006660795338</c:v>
+                  <c:v>393.69006660795321</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>418.89203273740901</c:v>
+                  <c:v>418.89203273740918</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>441.23836560123243</c:v>
+                  <c:v>441.23836560123277</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>461.1167930075195</c:v>
+                  <c:v>461.11679300751973</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>478.84516848321852</c:v>
+                  <c:v>478.84516848321897</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>494.68745080004715</c:v>
+                  <c:v>494.68745080004754</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>508.86527275976403</c:v>
+                  <c:v>508.86527275976425</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>521.56651174046624</c:v>
+                  <c:v>521.56651174046658</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>532.95176494853706</c:v>
+                  <c:v>532.9517649485374</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>543.15932534142394</c:v>
@@ -5730,64 +5730,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>4.7652176471718679</c:v>
+                  <c:v>4.7652176471718688</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.622604514708922</c:v>
+                  <c:v>27.622604514708939</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70.525292114122337</c:v>
+                  <c:v>70.525292114122365</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108.56201380760591</c:v>
+                  <c:v>108.56201380760596</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>142.80213140879403</c:v>
+                  <c:v>142.80213140879411</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>173.89555548851538</c:v>
+                  <c:v>173.89555548851553</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>202.31347221879278</c:v>
+                  <c:v>202.31347221879295</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>252.49547384519565</c:v>
+                  <c:v>252.49547384519579</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>295.46729132686249</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>332.67223073950191</c:v>
+                  <c:v>332.67223073950203</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>365.15217984314569</c:v>
+                  <c:v>365.15217984314586</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>393.69006660795338</c:v>
+                  <c:v>393.69006660795321</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>418.89203273740895</c:v>
+                  <c:v>418.89203273740918</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>441.23836560123249</c:v>
+                  <c:v>441.23836560123283</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>461.1167930075195</c:v>
+                  <c:v>461.11679300751973</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>478.84516848321852</c:v>
+                  <c:v>478.84516848321897</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>494.68745080004715</c:v>
+                  <c:v>494.68745080004754</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>508.86527275976397</c:v>
+                  <c:v>508.8652727597642</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>521.56651174046613</c:v>
+                  <c:v>521.56651174046658</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>532.95176494853717</c:v>
+                  <c:v>532.9517649485374</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>543.15932534142382</c:v>
@@ -6233,64 +6233,64 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>4.7652176471718679</c:v>
+                  <c:v>4.7652176471718688</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.622604514708922</c:v>
+                  <c:v>27.622604514708939</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70.525292114122337</c:v>
+                  <c:v>70.525292114122365</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108.56201380760591</c:v>
+                  <c:v>108.56201380760596</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>142.80213140879403</c:v>
+                  <c:v>142.80213140879411</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>173.89555548851538</c:v>
+                  <c:v>173.89555548851553</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>202.31347221879278</c:v>
+                  <c:v>202.31347221879295</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>252.49547384519565</c:v>
+                  <c:v>252.49547384519579</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>295.46729132686249</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>332.67223073950191</c:v>
+                  <c:v>332.67223073950203</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>365.15217984314569</c:v>
+                  <c:v>365.15217984314586</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>393.69006660795338</c:v>
+                  <c:v>393.69006660795321</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>418.89203273740895</c:v>
+                  <c:v>418.89203273740918</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>441.23836560123249</c:v>
+                  <c:v>441.23836560123283</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>461.1167930075195</c:v>
+                  <c:v>461.11679300751973</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>478.84516848321852</c:v>
+                  <c:v>478.84516848321897</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>494.68745080004715</c:v>
+                  <c:v>494.68745080004754</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>508.86527275976397</c:v>
+                  <c:v>508.8652727597642</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>521.56651174046613</c:v>
+                  <c:v>521.56651174046658</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>532.95176494853717</c:v>
+                  <c:v>532.9517649485374</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>543.15932534142382</c:v>
@@ -6501,73 +6501,73 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="26"/>
                 <c:pt idx="0">
-                  <c:v>8.2271659062691072E-2</c:v>
+                  <c:v>8.2271659062697899E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>18.022014659826571</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>28.259056830115661</c:v>
+                  <c:v>28.259056830115654</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>36.880577262600667</c:v>
+                  <c:v>36.880577262600646</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>44.700919980779865</c:v>
+                  <c:v>44.700919980779858</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>52.074681365632507</c:v>
+                  <c:v>52.074681365632486</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>59.205451693691721</c:v>
+                  <c:v>59.2054516936917</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>66.229037764954597</c:v>
+                  <c:v>66.229037764954583</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>73.245164700554909</c:v>
+                  <c:v>73.245164700554881</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>80.332105990458743</c:v>
+                  <c:v>80.332105990458729</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>87.554340117432062</c:v>
+                  <c:v>87.554340117432034</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>94.966934917925684</c:v>
+                  <c:v>94.96693491792567</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>102.61823487507661</c:v>
+                  <c:v>102.61823487507657</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>110.55159866234955</c:v>
+                  <c:v>110.55159866234952</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>118.80719158854976</c:v>
+                  <c:v>118.80719158854971</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>127.42035661422514</c:v>
+                  <c:v>127.42035661422511</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>136.4258420378884</c:v>
+                  <c:v>136.42584203788834</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>145.85583986198881</c:v>
+                  <c:v>145.85583986198873</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>155.74091151119109</c:v>
+                  <c:v>155.74091151119103</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>166.1102434845109</c:v>
+                  <c:v>166.11024348451087</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>176.99184801102427</c:v>
+                  <c:v>176.99184801102425</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>188.4127229670959</c:v>
+                  <c:v>188.41272296709593</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>200.39898108307844</c:v>
+                  <c:v>200.39898108307841</c:v>
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>212.97595563227983</c:v>
@@ -7112,67 +7112,67 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>3.9516569619629709</c:v>
+                  <c:v>3.9516569619629691</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.204265257695354</c:v>
+                  <c:v>26.20426525769534</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>65.220275414584947</c:v>
+                  <c:v>65.220275414584904</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>99.65912978060156</c:v>
+                  <c:v>99.659129780601489</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>131.76599936161304</c:v>
+                  <c:v>131.76599936161296</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>162.32793720118303</c:v>
+                  <c:v>162.32793720118292</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>191.74670764006245</c:v>
+                  <c:v>191.74670764006237</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>248.04343216453722</c:v>
+                  <c:v>248.04343216453705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>301.81267586222083</c:v>
+                  <c:v>301.81267586222066</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>353.67640780212287</c:v>
+                  <c:v>353.67640780212275</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>404.02097397611703</c:v>
+                  <c:v>404.02097397611681</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>453.10848286447049</c:v>
+                  <c:v>453.10848286447026</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>501.12776305350894</c:v>
+                  <c:v>501.12776305350866</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>548.22092849987712</c:v>
+                  <c:v>548.22092849987689</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>594.49855745182083</c:v>
+                  <c:v>594.49855745182049</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>640.04897894804446</c:v>
+                  <c:v>640.04897894804401</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>684.94426416794636</c:v>
+                  <c:v>684.9442641679459</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>729.24425980966021</c:v>
+                  <c:v>729.24425980965975</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>772.99939974004803</c:v>
+                  <c:v>772.99939974004769</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>816.25272295477498</c:v>
+                  <c:v>816.25272295477441</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>859.04135817139559</c:v>
+                  <c:v>859.04135817139502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7301,64 +7301,64 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>4.7652176471718679</c:v>
+                  <c:v>4.7652176471718688</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.622604514708922</c:v>
+                  <c:v>27.622604514708939</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>70.525292114122337</c:v>
+                  <c:v>70.525292114122379</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>108.56201380760591</c:v>
+                  <c:v>108.56201380760596</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>142.80213140879403</c:v>
+                  <c:v>142.80213140879411</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>173.89555548851538</c:v>
+                  <c:v>173.89555548851553</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>202.31347221879278</c:v>
+                  <c:v>202.31347221879295</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>252.49547384519565</c:v>
+                  <c:v>252.49547384519579</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>295.46729132686249</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>332.67223073950186</c:v>
+                  <c:v>332.67223073950203</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>365.15217984314569</c:v>
+                  <c:v>365.15217984314586</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>393.69006660795338</c:v>
+                  <c:v>393.69006660795321</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>418.89203273740901</c:v>
+                  <c:v>418.89203273740918</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>441.23836560123243</c:v>
+                  <c:v>441.23836560123277</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>461.1167930075195</c:v>
+                  <c:v>461.11679300751973</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>478.84516848321852</c:v>
+                  <c:v>478.84516848321897</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>494.68745080004715</c:v>
+                  <c:v>494.68745080004754</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>508.86527275976403</c:v>
+                  <c:v>508.86527275976425</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>521.56651174046624</c:v>
+                  <c:v>521.56651174046658</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>532.95176494853706</c:v>
+                  <c:v>532.9517649485374</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>543.15932534142394</c:v>
@@ -7418,16 +7418,16 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>1</c:v>
+                  <c:v>1.0000000000000002</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.116275144756642</c:v>
+                  <c:v>10.11627514475664</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30.027970672961317</c:v>
+                  <c:v>30.027970672961324</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>50.016124941183321</c:v>
+                  <c:v>50.016124941183307</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>70.011337046209462</c:v>
@@ -7436,34 +7436,34 @@
                   <c:v>90.008743154762044</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>110.00711568881245</c:v>
+                  <c:v>110.00711568881246</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>150.00518563484462</c:v>
+                  <c:v>150.00518563484465</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>190.0040793277731</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>230.00336210460026</c:v>
+                  <c:v>230.00336210460028</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>270.00285938923201</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>310.00248746260189</c:v>
+                  <c:v>310.00248746260195</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>350.00220115787874</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>390.00197395933077</c:v>
+                  <c:v>390.00197395933083</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>430.00178927573398</c:v>
+                  <c:v>430.00178927573404</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>470.0016361942927</c:v>
+                  <c:v>470.00163619429253</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>510.00150724273357</c:v>
@@ -7472,13 +7472,13 @@
                   <c:v>550.00139713245892</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>590.00130201515628</c:v>
+                  <c:v>590.0013020151564</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>630.0012190237419</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>670.00114597835829</c:v>
+                  <c:v>670.00114597835807</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7490,67 +7490,67 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="21"/>
                 <c:pt idx="0">
-                  <c:v>3.9516569619629709</c:v>
+                  <c:v>3.9516569619629691</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.204265257695354</c:v>
+                  <c:v>26.20426525769534</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>65.220275414584947</c:v>
+                  <c:v>65.220275414584904</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>99.65912978060156</c:v>
+                  <c:v>99.659129780601489</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>131.76599936161304</c:v>
+                  <c:v>131.76599936161296</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>162.32793720118303</c:v>
+                  <c:v>162.32793720118292</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>191.74670764006245</c:v>
+                  <c:v>191.74670764006237</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>248.04343216453722</c:v>
+                  <c:v>248.04343216453705</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>301.81267586222083</c:v>
+                  <c:v>301.81267586222066</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>353.67640780212287</c:v>
+                  <c:v>353.67640780212275</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>404.02097397611703</c:v>
+                  <c:v>404.02097397611681</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>453.10848286447049</c:v>
+                  <c:v>453.10848286447026</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>501.12776305350894</c:v>
+                  <c:v>501.12776305350866</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>548.22092849987712</c:v>
+                  <c:v>548.22092849987689</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>594.49855745182083</c:v>
+                  <c:v>594.49855745182049</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>640.04897894804446</c:v>
+                  <c:v>640.04897894804401</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>684.94426416794636</c:v>
+                  <c:v>684.9442641679459</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>729.24425980966021</c:v>
+                  <c:v>729.24425980965975</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>772.99939974004803</c:v>
+                  <c:v>772.99939974004769</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>816.25272295477498</c:v>
+                  <c:v>816.25272295477441</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>859.04135817139559</c:v>
+                  <c:v>859.04135817139502</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13365,28 +13365,28 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист1"/>
   <dimension ref="A1:U56"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.15234375" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" s="16" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>2</v>
       </c>
@@ -13394,7 +13394,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
@@ -13402,7 +13402,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
@@ -13410,7 +13410,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
@@ -13418,7 +13418,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -13426,7 +13426,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
@@ -13434,7 +13434,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
@@ -13442,7 +13442,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
@@ -13450,7 +13450,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
@@ -13458,7 +13458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
@@ -13467,17 +13467,17 @@
         <v>{"gamma_gas":0.6,"gamma_oil":0.86,"gamma_wat":1.1,"rsb_m3m3":120,"pb_atma":130,"t_res_C":80,"bob_m3m3":1.2,"muob_cP":0.6,"PVT_corr_set":0}</v>
       </c>
     </row>
-    <row r="19" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
         <v>15</v>
       </c>
@@ -13485,7 +13485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
@@ -13493,7 +13493,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="24" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
         <v>17</v>
       </c>
@@ -13501,7 +13501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
         <v>18</v>
       </c>
@@ -13510,7 +13510,7 @@
         <v>[1,10.96,20.92,30.88,40.84,50.8,60.76,70.72,80.68,90.64,100.6,110.56,120.52,130.48,140.44,150.4,160.36,170.32,180.28,190.24,200.2,210.16,220.12,230.08,240.04,250]</v>
       </c>
     </row>
-    <row r="26" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>19</v>
       </c>
@@ -13518,12 +13518,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="30" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B30" s="4" t="s">
         <v>12</v>
       </c>
@@ -13585,7 +13585,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="31" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B31" s="7">
         <f t="array" ref="B31:B56">[1]!decode_json(Массив_точек)</f>
         <v>1</v>
@@ -13596,7 +13596,7 @@
       </c>
       <c r="D31" s="8">
         <f t="array" ref="D31">[1]!PVT_rs_m3m3(B31,C31,PVT_json)</f>
-        <v>0.40799738531524399</v>
+        <v>0.40799738531524365</v>
       </c>
       <c r="E31" s="8">
         <f>[1]!PVT_bo_m3m3(B31,C31,PVT_json)</f>
@@ -13604,7 +13604,7 @@
       </c>
       <c r="F31" s="9">
         <f>[1]!PVT_mu_oil_cP(B31,C31,PVT_json)</f>
-        <v>9.7713156529231906</v>
+        <v>9.7713156529231888</v>
       </c>
       <c r="G31" s="10">
         <f>[1]!PVT_mu_gas_cP(B31,C31,PVT_json)</f>
@@ -13612,11 +13612,11 @@
       </c>
       <c r="H31" s="8">
         <f>[1]!PVT_mu_wat_cP(B31,C31,PVT_json)</f>
-        <v>0.82711135330023045</v>
+        <v>0.82711135330023133</v>
       </c>
       <c r="I31" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B31,C31,PVT_json)</f>
-        <v>0.68450731108914853</v>
+        <v>0.68450731108914831</v>
       </c>
       <c r="J31" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B31,C31,PVT_json)</f>
@@ -13628,15 +13628,15 @@
       </c>
       <c r="L31" s="12">
         <f>[1]!PVT_bg_m3m3(B31,C31,PVT_json)</f>
-        <v>1.0708724189280914</v>
+        <v>1.0708724189280916</v>
       </c>
       <c r="M31" s="12">
         <f>[1]!PVT_bw_m3m3(B31,C31,PVT_json)</f>
-        <v>1.0096706043181005</v>
+        <v>1.0096706043181007</v>
       </c>
       <c r="N31" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B31,C31,PVT_json)</f>
-        <v>2.8969477236995011E-2</v>
+        <v>2.8969477236995007E-2</v>
       </c>
       <c r="O31" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B31,C31,PVT_json)</f>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="Q31" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B31,C31,PVT_json)</f>
-        <v>2180.5754923629324</v>
+        <v>2180.5754923629329</v>
       </c>
       <c r="R31" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B31,C31,PVT_json)</f>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="S31" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B31,C31,PVT_json)</f>
-        <v>3.4370661312794928E-5</v>
+        <v>3.4370661312794921E-5</v>
       </c>
       <c r="T31" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B31,C31,PVT_json)</f>
@@ -13664,10 +13664,10 @@
       </c>
       <c r="U31" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B31,C31,PVT_json)</f>
-        <v>1.0016044501324981</v>
+        <v>1.0016044501325005</v>
       </c>
     </row>
-    <row r="32" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B32" s="7">
         <v>10.96</v>
       </c>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="D32" s="8">
         <f t="array" ref="D32">[1]!PVT_rs_m3m3(B32,C32,PVT_json)</f>
-        <v>7.2876798732693988</v>
+        <v>7.2876798732693953</v>
       </c>
       <c r="E32" s="8">
         <f>[1]!PVT_bo_m3m3(B32,C32,PVT_json)</f>
@@ -13685,7 +13685,7 @@
       </c>
       <c r="F32" s="9">
         <f>[1]!PVT_mu_oil_cP(B32,C32,PVT_json)</f>
-        <v>6.9930993456852475</v>
+        <v>6.9930993456852466</v>
       </c>
       <c r="G32" s="10">
         <f>[1]!PVT_mu_gas_cP(B32,C32,PVT_json)</f>
@@ -13693,15 +13693,15 @@
       </c>
       <c r="H32" s="8">
         <f>[1]!PVT_mu_wat_cP(B32,C32,PVT_json)</f>
-        <v>0.83205590390069384</v>
+        <v>0.83205590390069484</v>
       </c>
       <c r="I32" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B32,C32,PVT_json)</f>
-        <v>7.6268972740510206</v>
+        <v>7.6268972740510215</v>
       </c>
       <c r="J32" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B32,C32,PVT_json)</f>
-        <v>1089.5604893429659</v>
+        <v>1089.5604893429661</v>
       </c>
       <c r="K32" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B32,C32,PVT_json)</f>
@@ -13709,7 +13709,7 @@
       </c>
       <c r="L32" s="12">
         <f>[1]!PVT_bg_m3m3(B32,C32,PVT_json)</f>
-        <v>9.610985616575074E-2</v>
+        <v>9.6109856165750726E-2</v>
       </c>
       <c r="M32" s="12">
         <f>[1]!PVT_bw_m3m3(B32,C32,PVT_json)</f>
@@ -13717,7 +13717,7 @@
       </c>
       <c r="N32" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B32,C32,PVT_json)</f>
-        <v>2.8601027331509522E-2</v>
+        <v>2.8601027331509519E-2</v>
       </c>
       <c r="O32" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B32,C32,PVT_json)</f>
@@ -13729,7 +13729,7 @@
       </c>
       <c r="Q32" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B32,C32,PVT_json)</f>
-        <v>2144.9238338280934</v>
+        <v>2144.9238338280929</v>
       </c>
       <c r="R32" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B32,C32,PVT_json)</f>
@@ -13737,18 +13737,18 @@
       </c>
       <c r="S32" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B32,C32,PVT_json)</f>
-        <v>3.4287017433847842E-5</v>
+        <v>3.4287017433847835E-5</v>
       </c>
       <c r="T32" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B32,C32,PVT_json)</f>
-        <v>4.1443404591609036E-2</v>
+        <v>4.1443404591609029E-2</v>
       </c>
       <c r="U32" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B32,C32,PVT_json)</f>
-        <v>9.2952069162462111E-2</v>
+        <v>9.2952069162459822E-2</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B33" s="7">
         <v>20.92</v>
       </c>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="D33" s="8">
         <f t="array" ref="D33">[1]!PVT_rs_m3m3(B33,C33,PVT_json)</f>
-        <v>15.871341736906073</v>
+        <v>15.871341736906061</v>
       </c>
       <c r="E33" s="8">
         <f>[1]!PVT_bo_m3m3(B33,C33,PVT_json)</f>
@@ -13766,39 +13766,39 @@
       </c>
       <c r="F33" s="9">
         <f>[1]!PVT_mu_oil_cP(B33,C33,PVT_json)</f>
-        <v>5.1397568149463044</v>
+        <v>5.1397568149463062</v>
       </c>
       <c r="G33" s="10">
         <f>[1]!PVT_mu_gas_cP(B33,C33,PVT_json)</f>
-        <v>1.198625057572044E-2</v>
+        <v>1.1986250575720442E-2</v>
       </c>
       <c r="H33" s="8">
         <f>[1]!PVT_mu_wat_cP(B33,C33,PVT_json)</f>
-        <v>0.83711054604977353</v>
+        <v>0.83711054604977453</v>
       </c>
       <c r="I33" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B33,C33,PVT_json)</f>
-        <v>14.81705643662777</v>
+        <v>14.817056436627773</v>
       </c>
       <c r="J33" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B33,C33,PVT_json)</f>
-        <v>1089.6681315149592</v>
+        <v>1089.668131514959</v>
       </c>
       <c r="K33" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B33,C33,PVT_json)</f>
-        <v>847.79750461929541</v>
+        <v>847.79750461929552</v>
       </c>
       <c r="L33" s="12">
         <f>[1]!PVT_bg_m3m3(B33,C33,PVT_json)</f>
-        <v>4.947136451393775E-2</v>
+        <v>4.9471364513937736E-2</v>
       </c>
       <c r="M33" s="12">
         <f>[1]!PVT_bw_m3m3(B33,C33,PVT_json)</f>
-        <v>1.0094816652760841</v>
+        <v>1.0094816652760843</v>
       </c>
       <c r="N33" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B33,C33,PVT_json)</f>
-        <v>2.8237263576614241E-2</v>
+        <v>2.8237263576614238E-2</v>
       </c>
       <c r="O33" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B33,C33,PVT_json)</f>
@@ -13810,7 +13810,7 @@
       </c>
       <c r="Q33" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B33,C33,PVT_json)</f>
-        <v>2107.4096430143263</v>
+        <v>2107.4096430143254</v>
       </c>
       <c r="R33" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B33,C33,PVT_json)</f>
@@ -13818,18 +13818,18 @@
       </c>
       <c r="S33" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B33,C33,PVT_json)</f>
-        <v>3.4203779675322945E-5</v>
+        <v>3.4203779675322932E-5</v>
       </c>
       <c r="T33" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B33,C33,PVT_json)</f>
-        <v>2.3799326989926199E-2</v>
+        <v>2.3799326989926185E-2</v>
       </c>
       <c r="U33" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B33,C33,PVT_json)</f>
-        <v>4.9634378950726386E-2</v>
+        <v>4.9634378950722882E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B34" s="7">
         <v>30.88</v>
       </c>
@@ -13839,7 +13839,7 @@
       </c>
       <c r="D34" s="8">
         <f t="array" ref="D34">[1]!PVT_rs_m3m3(B34,C34,PVT_json)</f>
-        <v>25.364647959839669</v>
+        <v>25.364647959839644</v>
       </c>
       <c r="E34" s="8">
         <f>[1]!PVT_bo_m3m3(B34,C34,PVT_json)</f>
@@ -13847,7 +13847,7 @@
       </c>
       <c r="F34" s="9">
         <f>[1]!PVT_mu_oil_cP(B34,C34,PVT_json)</f>
-        <v>3.9709702064959589</v>
+        <v>3.9709702064959602</v>
       </c>
       <c r="G34" s="10">
         <f>[1]!PVT_mu_gas_cP(B34,C34,PVT_json)</f>
@@ -13855,15 +13855,15 @@
       </c>
       <c r="H34" s="8">
         <f>[1]!PVT_mu_wat_cP(B34,C34,PVT_json)</f>
-        <v>0.84227527974746919</v>
+        <v>0.84227527974747018</v>
       </c>
       <c r="I34" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B34,C34,PVT_json)</f>
-        <v>22.287265720310756</v>
+        <v>22.287265720310746</v>
       </c>
       <c r="J34" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B34,C34,PVT_json)</f>
-        <v>1089.7871558389757</v>
+        <v>1089.7871558389759</v>
       </c>
       <c r="K34" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B34,C34,PVT_json)</f>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="L34" s="12">
         <f>[1]!PVT_bg_m3m3(B34,C34,PVT_json)</f>
-        <v>3.2889633443549185E-2</v>
+        <v>3.2889633443549199E-2</v>
       </c>
       <c r="M34" s="12">
         <f>[1]!PVT_bw_m3m3(B34,C34,PVT_json)</f>
@@ -13899,18 +13899,18 @@
       </c>
       <c r="S34" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B34,C34,PVT_json)</f>
-        <v>3.4120945086597366E-5</v>
+        <v>3.4120945086597352E-5</v>
       </c>
       <c r="T34" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B34,C34,PVT_json)</f>
-        <v>1.6702949182722172E-2</v>
+        <v>1.6702949182722176E-2</v>
       </c>
       <c r="U34" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B34,C34,PVT_json)</f>
-        <v>3.4329183017040465E-2</v>
+        <v>3.4329183017041652E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B35" s="7">
         <v>40.840000000000003</v>
       </c>
@@ -13920,15 +13920,15 @@
       </c>
       <c r="D35" s="8">
         <f t="array" ref="D35">[1]!PVT_rs_m3m3(B35,C35,PVT_json)</f>
-        <v>35.514409899723063</v>
+        <v>35.514409899723034</v>
       </c>
       <c r="E35" s="8">
         <f>[1]!PVT_bo_m3m3(B35,C35,PVT_json)</f>
-        <v>1.0526284121419129</v>
+        <v>1.0526284121419127</v>
       </c>
       <c r="F35" s="9">
         <f>[1]!PVT_mu_oil_cP(B35,C35,PVT_json)</f>
-        <v>3.1972861301457316</v>
+        <v>3.1972861301457325</v>
       </c>
       <c r="G35" s="10">
         <f>[1]!PVT_mu_gas_cP(B35,C35,PVT_json)</f>
@@ -13936,23 +13936,23 @@
       </c>
       <c r="H35" s="8">
         <f>[1]!PVT_mu_wat_cP(B35,C35,PVT_json)</f>
-        <v>0.84755010499378114</v>
+        <v>0.84755010499378214</v>
       </c>
       <c r="I35" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B35,C35,PVT_json)</f>
-        <v>30.065604190118243</v>
+        <v>30.065604190118247</v>
       </c>
       <c r="J35" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B35,C35,PVT_json)</f>
-        <v>1089.9175697681965</v>
+        <v>1089.9175697681967</v>
       </c>
       <c r="K35" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B35,C35,PVT_json)</f>
-        <v>841.73366643388874</v>
+        <v>841.73366643388897</v>
       </c>
       <c r="L35" s="12">
         <f>[1]!PVT_bg_m3m3(B35,C35,PVT_json)</f>
-        <v>2.4380684165360097E-2</v>
+        <v>2.4380684165360093E-2</v>
       </c>
       <c r="M35" s="12">
         <f>[1]!PVT_bw_m3m3(B35,C35,PVT_json)</f>
@@ -13960,7 +13960,7 @@
       </c>
       <c r="N35" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B35,C35,PVT_json)</f>
-        <v>2.7523556872367412E-2</v>
+        <v>2.7523556872367409E-2</v>
       </c>
       <c r="O35" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B35,C35,PVT_json)</f>
@@ -13972,7 +13972,7 @@
       </c>
       <c r="Q35" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B35,C35,PVT_json)</f>
-        <v>2027.5193865688193</v>
+        <v>2027.5193865688188</v>
       </c>
       <c r="R35" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B35,C35,PVT_json)</f>
@@ -13980,18 +13980,18 @@
       </c>
       <c r="S35" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B35,C35,PVT_json)</f>
-        <v>3.4038510745562415E-5</v>
+        <v>3.4038510745562402E-5</v>
       </c>
       <c r="T35" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B35,C35,PVT_json)</f>
-        <v>1.274847773717386E-2</v>
+        <v>1.2748477737173858E-2</v>
       </c>
       <c r="U35" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B35,C35,PVT_json)</f>
-        <v>2.6511926884434035E-2</v>
+        <v>2.6511926884427977E-2</v>
       </c>
     </row>
-    <row r="36" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B36" s="7">
         <v>50.8</v>
       </c>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="D36" s="8">
         <f t="array" ref="D36">[1]!PVT_rs_m3m3(B36,C36,PVT_json)</f>
-        <v>46.186737869660327</v>
+        <v>46.186737869660284</v>
       </c>
       <c r="E36" s="8">
         <f>[1]!PVT_bo_m3m3(B36,C36,PVT_json)</f>
@@ -14009,7 +14009,7 @@
       </c>
       <c r="F36" s="9">
         <f>[1]!PVT_mu_oil_cP(B36,C36,PVT_json)</f>
-        <v>2.6582574292633621</v>
+        <v>2.6582574292633616</v>
       </c>
       <c r="G36" s="10">
         <f>[1]!PVT_mu_gas_cP(B36,C36,PVT_json)</f>
@@ -14017,11 +14017,11 @@
       </c>
       <c r="H36" s="8">
         <f>[1]!PVT_mu_wat_cP(B36,C36,PVT_json)</f>
-        <v>0.85293502178870917</v>
+        <v>0.85293502178871006</v>
       </c>
       <c r="I36" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B36,C36,PVT_json)</f>
-        <v>38.167901822091991</v>
+        <v>38.167901822091984</v>
       </c>
       <c r="J36" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B36,C36,PVT_json)</f>
@@ -14033,15 +14033,15 @@
       </c>
       <c r="L36" s="12">
         <f>[1]!PVT_bg_m3m3(B36,C36,PVT_json)</f>
-        <v>1.9205142672414865E-2</v>
+        <v>1.9205142672414868E-2</v>
       </c>
       <c r="M36" s="12">
         <f>[1]!PVT_bw_m3m3(B36,C36,PVT_json)</f>
-        <v>1.009119336705095</v>
+        <v>1.0091193367050952</v>
       </c>
       <c r="N36" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B36,C36,PVT_json)</f>
-        <v>2.7173496985359931E-2</v>
+        <v>2.7173496985359927E-2</v>
       </c>
       <c r="O36" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B36,C36,PVT_json)</f>
@@ -14061,7 +14061,7 @@
       </c>
       <c r="S36" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B36,C36,PVT_json)</f>
-        <v>3.395647375827996E-5</v>
+        <v>3.3956473758279953E-5</v>
       </c>
       <c r="T36" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B36,C36,PVT_json)</f>
@@ -14069,10 +14069,10 @@
       </c>
       <c r="U36" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B36,C36,PVT_json)</f>
-        <v>2.1741398826454584E-2</v>
+        <v>2.1741398826457058E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B37" s="7">
         <v>60.76</v>
       </c>
@@ -14082,7 +14082,7 @@
       </c>
       <c r="D37" s="8">
         <f t="array" ref="D37">[1]!PVT_rs_m3m3(B37,C37,PVT_json)</f>
-        <v>57.297169628895695</v>
+        <v>57.297169628895659</v>
       </c>
       <c r="E37" s="8">
         <f>[1]!PVT_bo_m3m3(B37,C37,PVT_json)</f>
@@ -14094,15 +14094,15 @@
       </c>
       <c r="G37" s="10">
         <f>[1]!PVT_mu_gas_cP(B37,C37,PVT_json)</f>
-        <v>1.3076968510634199E-2</v>
+        <v>1.3076968510634203E-2</v>
       </c>
       <c r="H37" s="8">
         <f>[1]!PVT_mu_wat_cP(B37,C37,PVT_json)</f>
-        <v>0.85843003013225316</v>
+        <v>0.85843003013225416</v>
       </c>
       <c r="I37" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B37,C37,PVT_json)</f>
-        <v>46.591315187907206</v>
+        <v>46.591315187907213</v>
       </c>
       <c r="J37" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B37,C37,PVT_json)</f>
@@ -14114,7 +14114,7 @@
       </c>
       <c r="L37" s="12">
         <f>[1]!PVT_bg_m3m3(B37,C37,PVT_json)</f>
-        <v>1.5732975062920217E-2</v>
+        <v>1.5732975062920214E-2</v>
       </c>
       <c r="M37" s="12">
         <f>[1]!PVT_bw_m3m3(B37,C37,PVT_json)</f>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="N37" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B37,C37,PVT_json)</f>
-        <v>2.6827889354471082E-2</v>
+        <v>2.6827889354471078E-2</v>
       </c>
       <c r="O37" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B37,C37,PVT_json)</f>
@@ -14134,7 +14134,7 @@
       </c>
       <c r="Q37" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B37,C37,PVT_json)</f>
-        <v>1946.5340857482618</v>
+        <v>1946.5340857482613</v>
       </c>
       <c r="R37" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B37,C37,PVT_json)</f>
@@ -14142,18 +14142,18 @@
       </c>
       <c r="S37" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B37,C37,PVT_json)</f>
-        <v>3.3874831258643788E-5</v>
+        <v>3.3874831258643775E-5</v>
       </c>
       <c r="T37" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B37,C37,PVT_json)</f>
-        <v>8.3777197633504233E-3</v>
+        <v>8.3777197633504198E-3</v>
       </c>
       <c r="U37" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B37,C37,PVT_json)</f>
-        <v>1.8483563307194244E-2</v>
+        <v>1.8483563307189196E-2</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B38" s="7">
         <v>70.72</v>
       </c>
@@ -14163,7 +14163,7 @@
       </c>
       <c r="D38" s="8">
         <f t="array" ref="D38">[1]!PVT_rs_m3m3(B38,C38,PVT_json)</f>
-        <v>68.78698135405061</v>
+        <v>68.786981354050553</v>
       </c>
       <c r="E38" s="8">
         <f>[1]!PVT_bo_m3m3(B38,C38,PVT_json)</f>
@@ -14171,39 +14171,39 @@
       </c>
       <c r="F38" s="9">
         <f>[1]!PVT_mu_oil_cP(B38,C38,PVT_json)</f>
-        <v>1.9699222555167233</v>
+        <v>1.9699222555167235</v>
       </c>
       <c r="G38" s="10">
         <f>[1]!PVT_mu_gas_cP(B38,C38,PVT_json)</f>
-        <v>1.3440112930067171E-2</v>
+        <v>1.3440112930067173E-2</v>
       </c>
       <c r="H38" s="8">
         <f>[1]!PVT_mu_wat_cP(B38,C38,PVT_json)</f>
-        <v>0.86403513002441357</v>
+        <v>0.86403513002441446</v>
       </c>
       <c r="I38" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B38,C38,PVT_json)</f>
-        <v>55.310777212770816</v>
+        <v>55.310777212770795</v>
       </c>
       <c r="J38" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B38,C38,PVT_json)</f>
-        <v>1090.3772344668148</v>
+        <v>1090.3772344668146</v>
       </c>
       <c r="K38" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B38,C38,PVT_json)</f>
-        <v>829.78712419752685</v>
+        <v>829.78712419752674</v>
       </c>
       <c r="L38" s="12">
         <f>[1]!PVT_bg_m3m3(B38,C38,PVT_json)</f>
-        <v>1.3252751759032443E-2</v>
+        <v>1.3252751759032448E-2</v>
       </c>
       <c r="M38" s="12">
         <f>[1]!PVT_bw_m3m3(B38,C38,PVT_json)</f>
-        <v>1.0088251709857925</v>
+        <v>1.0088251709857927</v>
       </c>
       <c r="N38" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B38,C38,PVT_json)</f>
-        <v>2.6486677353434112E-2</v>
+        <v>2.6486677353434109E-2</v>
       </c>
       <c r="O38" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B38,C38,PVT_json)</f>
@@ -14215,7 +14215,7 @@
       </c>
       <c r="Q38" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B38,C38,PVT_json)</f>
-        <v>1908.4540537444454</v>
+        <v>1908.4540537444457</v>
       </c>
       <c r="R38" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B38,C38,PVT_json)</f>
@@ -14223,7 +14223,7 @@
       </c>
       <c r="S38" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B38,C38,PVT_json)</f>
-        <v>3.3793580408045789E-5</v>
+        <v>3.3793580408045776E-5</v>
       </c>
       <c r="T38" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B38,C38,PVT_json)</f>
@@ -14234,7 +14234,7 @@
         <v>1.6070225769133948E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B39" s="7">
         <v>80.680000000000007</v>
       </c>
@@ -14244,7 +14244,7 @@
       </c>
       <c r="D39" s="8">
         <f t="array" ref="D39">[1]!PVT_rs_m3m3(B39,C39,PVT_json)</f>
-        <v>80.612708067538293</v>
+        <v>80.61270806753825</v>
       </c>
       <c r="E39" s="8">
         <f>[1]!PVT_bo_m3m3(B39,C39,PVT_json)</f>
@@ -14252,19 +14252,19 @@
       </c>
       <c r="F39" s="9">
         <f>[1]!PVT_mu_oil_cP(B39,C39,PVT_json)</f>
-        <v>1.7398587672578569</v>
+        <v>1.7398587672578572</v>
       </c>
       <c r="G39" s="10">
         <f>[1]!PVT_mu_gas_cP(B39,C39,PVT_json)</f>
-        <v>1.3840188691857094E-2</v>
+        <v>1.3840188691857097E-2</v>
       </c>
       <c r="H39" s="8">
         <f>[1]!PVT_mu_wat_cP(B39,C39,PVT_json)</f>
-        <v>0.86975032146518971</v>
+        <v>0.86975032146519071</v>
       </c>
       <c r="I39" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B39,C39,PVT_json)</f>
-        <v>64.279030785472969</v>
+        <v>64.279030785472941</v>
       </c>
       <c r="J39" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B39,C39,PVT_json)</f>
@@ -14276,11 +14276,11 @@
       </c>
       <c r="L39" s="12">
         <f>[1]!PVT_bg_m3m3(B39,C39,PVT_json)</f>
-        <v>1.1403718927349822E-2</v>
+        <v>1.1403718927349827E-2</v>
       </c>
       <c r="M39" s="12">
         <f>[1]!PVT_bw_m3m3(B39,C39,PVT_json)</f>
-        <v>1.0086623041245484</v>
+        <v>1.0086623041245486</v>
       </c>
       <c r="N39" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B39,C39,PVT_json)</f>
@@ -14296,7 +14296,7 @@
       </c>
       <c r="Q39" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B39,C39,PVT_json)</f>
-        <v>1873.4658782230824</v>
+        <v>1873.4658782230829</v>
       </c>
       <c r="R39" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B39,C39,PVT_json)</f>
@@ -14304,18 +14304,18 @@
       </c>
       <c r="S39" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B39,C39,PVT_json)</f>
-        <v>3.3712718395046994E-5</v>
+        <v>3.3712718395046981E-5</v>
       </c>
       <c r="T39" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B39,C39,PVT_json)</f>
-        <v>5.9886551116846484E-3</v>
+        <v>5.9886551116846501E-3</v>
       </c>
       <c r="U39" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B39,C39,PVT_json)</f>
-        <v>1.4169013400165777E-2</v>
+        <v>1.4169013400171022E-2</v>
       </c>
     </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B40" s="7">
         <v>90.64</v>
       </c>
@@ -14325,7 +14325,7 @@
       </c>
       <c r="D40" s="8">
         <f t="array" ref="D40">[1]!PVT_rs_m3m3(B40,C40,PVT_json)</f>
-        <v>92.74073547077991</v>
+        <v>92.740735470779853</v>
       </c>
       <c r="E40" s="8">
         <f>[1]!PVT_bo_m3m3(B40,C40,PVT_json)</f>
@@ -14333,7 +14333,7 @@
       </c>
       <c r="F40" s="9">
         <f>[1]!PVT_mu_oil_cP(B40,C40,PVT_json)</f>
-        <v>1.5566069111111438</v>
+        <v>1.556606911111144</v>
       </c>
       <c r="G40" s="10">
         <f>[1]!PVT_mu_gas_cP(B40,C40,PVT_json)</f>
@@ -14341,15 +14341,15 @@
       </c>
       <c r="H40" s="8">
         <f>[1]!PVT_mu_wat_cP(B40,C40,PVT_json)</f>
-        <v>0.87557560445458216</v>
+        <v>0.87557560445458327</v>
       </c>
       <c r="I40" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B40,C40,PVT_json)</f>
-        <v>73.430133425720641</v>
+        <v>73.430133425720598</v>
       </c>
       <c r="J40" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B40,C40,PVT_json)</f>
-        <v>1090.7407945491618</v>
+        <v>1090.7407945491616</v>
       </c>
       <c r="K40" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B40,C40,PVT_json)</f>
@@ -14357,11 +14357,11 @@
       </c>
       <c r="L40" s="12">
         <f>[1]!PVT_bg_m3m3(B40,C40,PVT_json)</f>
-        <v>9.9825502937632201E-3</v>
+        <v>9.9825502937632253E-3</v>
       </c>
       <c r="M40" s="12">
         <f>[1]!PVT_bw_m3m3(B40,C40,PVT_json)</f>
-        <v>1.0084889145955758</v>
+        <v>1.008488914595576</v>
       </c>
       <c r="N40" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B40,C40,PVT_json)</f>
@@ -14377,7 +14377,7 @@
       </c>
       <c r="Q40" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B40,C40,PVT_json)</f>
-        <v>1842.4461242884254</v>
+        <v>1842.4461242884263</v>
       </c>
       <c r="R40" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B40,C40,PVT_json)</f>
@@ -14385,18 +14385,18 @@
       </c>
       <c r="S40" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B40,C40,PVT_json)</f>
-        <v>3.3632242435053287E-5</v>
+        <v>3.363224243505328E-5</v>
       </c>
       <c r="T40" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B40,C40,PVT_json)</f>
-        <v>5.1635950123179696E-3</v>
+        <v>5.1635950123179704E-3</v>
       </c>
       <c r="U40" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B40,C40,PVT_json)</f>
-        <v>1.2601282976989016E-2</v>
+        <v>1.2601282976993014E-2</v>
       </c>
     </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B41" s="7">
         <v>100.6</v>
       </c>
@@ -14406,7 +14406,7 @@
       </c>
       <c r="D41" s="8">
         <f t="array" ref="D41">[1]!PVT_rs_m3m3(B41,C41,PVT_json)</f>
-        <v>105.14420670385927</v>
+        <v>105.1442067038592</v>
       </c>
       <c r="E41" s="8">
         <f>[1]!PVT_bo_m3m3(B41,C41,PVT_json)</f>
@@ -14414,15 +14414,15 @@
       </c>
       <c r="F41" s="9">
         <f>[1]!PVT_mu_oil_cP(B41,C41,PVT_json)</f>
-        <v>1.4076080220116909</v>
+        <v>1.4076080220116916</v>
       </c>
       <c r="G41" s="10">
         <f>[1]!PVT_mu_gas_cP(B41,C41,PVT_json)</f>
-        <v>1.4745918799782593E-2</v>
+        <v>1.4745918799782596E-2</v>
       </c>
       <c r="H41" s="8">
         <f>[1]!PVT_mu_wat_cP(B41,C41,PVT_json)</f>
-        <v>0.88151097899259068</v>
+        <v>0.88151097899259179</v>
       </c>
       <c r="I41" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B41,C41,PVT_json)</f>
@@ -14430,7 +14430,7 @@
       </c>
       <c r="J41" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B41,C41,PVT_json)</f>
-        <v>1090.939742818862</v>
+        <v>1090.9397428188618</v>
       </c>
       <c r="K41" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B41,C41,PVT_json)</f>
@@ -14442,11 +14442,11 @@
       </c>
       <c r="M41" s="12">
         <f>[1]!PVT_bw_m3m3(B41,C41,PVT_json)</f>
-        <v>1.0083050023988744</v>
+        <v>1.0083050023988747</v>
       </c>
       <c r="N41" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B41,C41,PVT_json)</f>
-        <v>2.5488859614988302E-2</v>
+        <v>2.5488859614988299E-2</v>
       </c>
       <c r="O41" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B41,C41,PVT_json)</f>
@@ -14466,18 +14466,18 @@
       </c>
       <c r="S41" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B41,C41,PVT_json)</f>
-        <v>3.3552149769995769E-5</v>
+        <v>3.3552149769995756E-5</v>
       </c>
       <c r="T41" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B41,C41,PVT_json)</f>
-        <v>4.4975548856352856E-3</v>
+        <v>4.4975548856352838E-3</v>
       </c>
       <c r="U41" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B41,C41,PVT_json)</f>
-        <v>1.126654632023812E-2</v>
+        <v>1.1266546320236766E-2</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B42" s="7">
         <v>110.56</v>
       </c>
@@ -14487,7 +14487,7 @@
       </c>
       <c r="D42" s="8">
         <f t="array" ref="D42">[1]!PVT_rs_m3m3(B42,C42,PVT_json)</f>
-        <v>117.80111687961013</v>
+        <v>117.80111687961006</v>
       </c>
       <c r="E42" s="8">
         <f>[1]!PVT_bo_m3m3(B42,C42,PVT_json)</f>
@@ -14495,19 +14495,19 @@
       </c>
       <c r="F42" s="9">
         <f>[1]!PVT_mu_oil_cP(B42,C42,PVT_json)</f>
-        <v>1.2843310127570018</v>
+        <v>1.2843310127570022</v>
       </c>
       <c r="G42" s="10">
         <f>[1]!PVT_mu_gas_cP(B42,C42,PVT_json)</f>
-        <v>1.5246397964708497E-2</v>
+        <v>1.5246397964708501E-2</v>
       </c>
       <c r="H42" s="8">
         <f>[1]!PVT_mu_wat_cP(B42,C42,PVT_json)</f>
-        <v>0.88755644507921549</v>
+        <v>0.88755644507921649</v>
       </c>
       <c r="I42" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B42,C42,PVT_json)</f>
-        <v>91.961325165760698</v>
+        <v>91.96132516576067</v>
       </c>
       <c r="J42" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B42,C42,PVT_json)</f>
@@ -14519,7 +14519,7 @@
       </c>
       <c r="L42" s="12">
         <f>[1]!PVT_bg_m3m3(B42,C42,PVT_json)</f>
-        <v>7.9709595167177967E-3</v>
+        <v>7.9709595167177984E-3</v>
       </c>
       <c r="M42" s="12">
         <f>[1]!PVT_bw_m3m3(B42,C42,PVT_json)</f>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="N42" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B42,C42,PVT_json)</f>
-        <v>2.5164678138075686E-2</v>
+        <v>2.5164678138075682E-2</v>
       </c>
       <c r="O42" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B42,C42,PVT_json)</f>
@@ -14539,7 +14539,7 @@
       </c>
       <c r="Q42" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B42,C42,PVT_json)</f>
-        <v>1794.49406788644</v>
+        <v>1794.4940678864402</v>
       </c>
       <c r="R42" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B42,C42,PVT_json)</f>
@@ -14547,7 +14547,7 @@
       </c>
       <c r="S42" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B42,C42,PVT_json)</f>
-        <v>3.3472437668015654E-5</v>
+        <v>3.347243766801564E-5</v>
       </c>
       <c r="T42" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B42,C42,PVT_json)</f>
@@ -14555,10 +14555,10 @@
       </c>
       <c r="U42" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B42,C42,PVT_json)</f>
-        <v>1.0106457074250322E-2</v>
+        <v>1.010645707425032E-2</v>
       </c>
     </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B43" s="7">
         <v>120.52</v>
       </c>
@@ -14572,19 +14572,19 @@
       </c>
       <c r="E43" s="8">
         <f>[1]!PVT_bo_m3m3(B43,C43,PVT_json)</f>
-        <v>1.1681208648753278</v>
+        <v>1.1681208648753281</v>
       </c>
       <c r="F43" s="9">
         <f>[1]!PVT_mu_oil_cP(B43,C43,PVT_json)</f>
-        <v>1.2926930197501159</v>
+        <v>1.2926930197501152</v>
       </c>
       <c r="G43" s="10">
         <f>[1]!PVT_mu_gas_cP(B43,C43,PVT_json)</f>
-        <v>1.5773782410755825E-2</v>
+        <v>1.5773782410755829E-2</v>
       </c>
       <c r="H43" s="8">
         <f>[1]!PVT_mu_wat_cP(B43,C43,PVT_json)</f>
-        <v>0.89371200271445617</v>
+        <v>0.89371200271445739</v>
       </c>
       <c r="I43" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B43,C43,PVT_json)</f>
@@ -14592,11 +14592,11 @@
       </c>
       <c r="J43" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B43,C43,PVT_json)</f>
-        <v>1091.3720382978174</v>
+        <v>1091.3720382978172</v>
       </c>
       <c r="K43" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B43,C43,PVT_json)</f>
-        <v>811.52766678915111</v>
+        <v>811.52766678915089</v>
       </c>
       <c r="L43" s="12">
         <f>[1]!PVT_bg_m3m3(B43,C43,PVT_json)</f>
@@ -14604,11 +14604,11 @@
       </c>
       <c r="M43" s="12">
         <f>[1]!PVT_bw_m3m3(B43,C43,PVT_json)</f>
-        <v>1.0079056100022861</v>
+        <v>1.0079056100022863</v>
       </c>
       <c r="N43" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B43,C43,PVT_json)</f>
-        <v>2.4844619781285385E-2</v>
+        <v>2.4844619781285382E-2</v>
       </c>
       <c r="O43" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B43,C43,PVT_json)</f>
@@ -14620,7 +14620,7 @@
       </c>
       <c r="Q43" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B43,C43,PVT_json)</f>
-        <v>1778.0081172029584</v>
+        <v>1778.0081172029581</v>
       </c>
       <c r="R43" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B43,C43,PVT_json)</f>
@@ -14628,18 +14628,18 @@
       </c>
       <c r="S43" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B43,C43,PVT_json)</f>
-        <v>3.3393103423153658E-5</v>
+        <v>3.3393103423153651E-5</v>
       </c>
       <c r="T43" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B43,C43,PVT_json)</f>
-        <v>1.568550441800501E-4</v>
+        <v>1.5685504418005018E-4</v>
       </c>
       <c r="U43" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B43,C43,PVT_json)</f>
         <v>9.0859261789447837E-3</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B44" s="7">
         <v>130.47999999999999</v>
       </c>
@@ -14653,23 +14653,23 @@
       </c>
       <c r="E44" s="8">
         <f>[1]!PVT_bo_m3m3(B44,C44,PVT_json)</f>
-        <v>1.1653095028377116</v>
+        <v>1.1653095028377118</v>
       </c>
       <c r="F44" s="9">
         <f>[1]!PVT_mu_oil_cP(B44,C44,PVT_json)</f>
-        <v>1.326191017794796</v>
+        <v>1.3261910177947958</v>
       </c>
       <c r="G44" s="10">
         <f>[1]!PVT_mu_gas_cP(B44,C44,PVT_json)</f>
-        <v>1.6323793809058015E-2</v>
+        <v>1.6323793809058018E-2</v>
       </c>
       <c r="H44" s="8">
         <f>[1]!PVT_mu_wat_cP(B44,C44,PVT_json)</f>
-        <v>0.89997765189831325</v>
+        <v>0.89997765189831436</v>
       </c>
       <c r="I44" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B44,C44,PVT_json)</f>
-        <v>110.25278879326808</v>
+        <v>110.25278879326807</v>
       </c>
       <c r="J44" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B44,C44,PVT_json)</f>
@@ -14677,11 +14677,11 @@
       </c>
       <c r="K44" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B44,C44,PVT_json)</f>
-        <v>813.48551409866877</v>
+        <v>813.48551409866866</v>
       </c>
       <c r="L44" s="12">
         <f>[1]!PVT_bg_m3m3(B44,C44,PVT_json)</f>
-        <v>6.6485393070144037E-3</v>
+        <v>6.6485393070144045E-3</v>
       </c>
       <c r="M44" s="12">
         <f>[1]!PVT_bw_m3m3(B44,C44,PVT_json)</f>
@@ -14689,7 +14689,7 @@
       </c>
       <c r="N44" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B44,C44,PVT_json)</f>
-        <v>2.4528632104485075E-2</v>
+        <v>2.4528632104485072E-2</v>
       </c>
       <c r="O44" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B44,C44,PVT_json)</f>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="Q44" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B44,C44,PVT_json)</f>
-        <v>1766.4590833965174</v>
+        <v>1766.4590833965171</v>
       </c>
       <c r="R44" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B44,C44,PVT_json)</f>
@@ -14709,18 +14709,18 @@
       </c>
       <c r="S44" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B44,C44,PVT_json)</f>
-        <v>3.3314144355043828E-5</v>
+        <v>3.3314144355043821E-5</v>
       </c>
       <c r="T44" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B44,C44,PVT_json)</f>
-        <v>1.4488174375061033E-4</v>
+        <v>1.4488174375061044E-4</v>
       </c>
       <c r="U44" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B44,C44,PVT_json)</f>
-        <v>8.1826702166266641E-3</v>
+        <v>8.1826702166252763E-3</v>
       </c>
     </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B45" s="7">
         <v>140.44</v>
       </c>
@@ -14734,31 +14734,31 @@
       </c>
       <c r="E45" s="8">
         <f>[1]!PVT_bo_m3m3(B45,C45,PVT_json)</f>
-        <v>1.1629022995124059</v>
+        <v>1.1629022995124061</v>
       </c>
       <c r="F45" s="9">
         <f>[1]!PVT_mu_oil_cP(B45,C45,PVT_json)</f>
-        <v>1.3622131528629122</v>
+        <v>1.3622131528629118</v>
       </c>
       <c r="G45" s="10">
         <f>[1]!PVT_mu_gas_cP(B45,C45,PVT_json)</f>
-        <v>1.6891977917657234E-2</v>
+        <v>1.6891977917657237E-2</v>
       </c>
       <c r="H45" s="8">
         <f>[1]!PVT_mu_wat_cP(B45,C45,PVT_json)</f>
-        <v>0.90635339263078618</v>
+        <v>0.9063533926307874</v>
       </c>
       <c r="I45" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B45,C45,PVT_json)</f>
-        <v>119.13031753524774</v>
+        <v>119.13031753524773</v>
       </c>
       <c r="J45" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B45,C45,PVT_json)</f>
-        <v>1091.8502908354244</v>
+        <v>1091.8502908354242</v>
       </c>
       <c r="K45" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B45,C45,PVT_json)</f>
-        <v>815.16942601065614</v>
+        <v>815.16942601065591</v>
       </c>
       <c r="L45" s="12">
         <f>[1]!PVT_bg_m3m3(B45,C45,PVT_json)</f>
@@ -14766,11 +14766,11 @@
       </c>
       <c r="M45" s="12">
         <f>[1]!PVT_bw_m3m3(B45,C45,PVT_json)</f>
-        <v>1.0074641269347833</v>
+        <v>1.0074641269347835</v>
       </c>
       <c r="N45" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B45,C45,PVT_json)</f>
-        <v>2.421666333450518E-2</v>
+        <v>2.4216663334505176E-2</v>
       </c>
       <c r="O45" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B45,C45,PVT_json)</f>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="Q45" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B45,C45,PVT_json)</f>
-        <v>1759.6153392775941</v>
+        <v>1759.6153392775939</v>
       </c>
       <c r="R45" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B45,C45,PVT_json)</f>
@@ -14790,18 +14790,18 @@
       </c>
       <c r="S45" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B45,C45,PVT_json)</f>
-        <v>3.3235557808611648E-5</v>
+        <v>3.3235557808611641E-5</v>
       </c>
       <c r="T45" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B45,C45,PVT_json)</f>
-        <v>1.3460673543562828E-4</v>
+        <v>1.3460673543562836E-4</v>
       </c>
       <c r="U45" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B45,C45,PVT_json)</f>
-        <v>7.3813348221432222E-3</v>
+        <v>7.3813348221404311E-3</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B46" s="7">
         <v>150.4</v>
       </c>
@@ -14815,43 +14815,43 @@
       </c>
       <c r="E46" s="8">
         <f>[1]!PVT_bo_m3m3(B46,C46,PVT_json)</f>
-        <v>1.1608179512669563</v>
+        <v>1.1608179512669565</v>
       </c>
       <c r="F46" s="9">
         <f>[1]!PVT_mu_oil_cP(B46,C46,PVT_json)</f>
-        <v>1.4005814298483232</v>
+        <v>1.4005814298483223</v>
       </c>
       <c r="G46" s="10">
         <f>[1]!PVT_mu_gas_cP(B46,C46,PVT_json)</f>
-        <v>1.7473960164598033E-2</v>
+        <v>1.7473960164598037E-2</v>
       </c>
       <c r="H46" s="8">
         <f>[1]!PVT_mu_wat_cP(B46,C46,PVT_json)</f>
-        <v>0.91283922491187541</v>
+        <v>0.91283922491187663</v>
       </c>
       <c r="I46" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B46,C46,PVT_json)</f>
-        <v>127.7577687886117</v>
+        <v>127.75776878861171</v>
       </c>
       <c r="J46" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B46,C46,PVT_json)</f>
-        <v>1092.1066881722297</v>
+        <v>1092.1066881722295</v>
       </c>
       <c r="K46" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B46,C46,PVT_json)</f>
-        <v>816.63313266766897</v>
+        <v>816.63313266766875</v>
       </c>
       <c r="L46" s="12">
         <f>[1]!PVT_bg_m3m3(B46,C46,PVT_json)</f>
-        <v>5.7375767199946692E-3</v>
+        <v>5.7375767199946684E-3</v>
       </c>
       <c r="M46" s="12">
         <f>[1]!PVT_bw_m3m3(B46,C46,PVT_json)</f>
-        <v>1.007227601399439</v>
+        <v>1.0072276013994392</v>
       </c>
       <c r="N46" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B46,C46,PVT_json)</f>
-        <v>2.3908662356656056E-2</v>
+        <v>2.3908662356656053E-2</v>
       </c>
       <c r="O46" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B46,C46,PVT_json)</f>
@@ -14863,7 +14863,7 @@
       </c>
       <c r="Q46" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B46,C46,PVT_json)</f>
-        <v>1757.1536362210625</v>
+        <v>1757.1536362210618</v>
       </c>
       <c r="R46" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B46,C46,PVT_json)</f>
@@ -14871,18 +14871,18 @@
       </c>
       <c r="S46" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B46,C46,PVT_json)</f>
-        <v>3.315734115377644E-5</v>
+        <v>3.3157341153776427E-5</v>
       </c>
       <c r="T46" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B46,C46,PVT_json)</f>
-        <v>1.2569261917938588E-4</v>
+        <v>1.2569261917938593E-4</v>
       </c>
       <c r="U46" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B46,C46,PVT_json)</f>
-        <v>6.6702438953282856E-3</v>
+        <v>6.6702438953240911E-3</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B47" s="7">
         <v>160.36000000000001</v>
       </c>
@@ -14896,35 +14896,35 @@
       </c>
       <c r="E47" s="8">
         <f>[1]!PVT_bo_m3m3(B47,C47,PVT_json)</f>
-        <v>1.1589955906641818</v>
+        <v>1.158995590664182</v>
       </c>
       <c r="F47" s="9">
         <f>[1]!PVT_mu_oil_cP(B47,C47,PVT_json)</f>
-        <v>1.4411346327141075</v>
+        <v>1.4411346327141066</v>
       </c>
       <c r="G47" s="10">
         <f>[1]!PVT_mu_gas_cP(B47,C47,PVT_json)</f>
-        <v>1.8065644186917869E-2</v>
+        <v>1.8065644186917872E-2</v>
       </c>
       <c r="H47" s="8">
         <f>[1]!PVT_mu_wat_cP(B47,C47,PVT_json)</f>
-        <v>0.91943514874158094</v>
+        <v>0.91943514874158194</v>
       </c>
       <c r="I47" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B47,C47,PVT_json)</f>
-        <v>136.09852438558238</v>
+        <v>136.09852438558232</v>
       </c>
       <c r="J47" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B47,C47,PVT_json)</f>
-        <v>1092.3746208488044</v>
+        <v>1092.3746208488046</v>
       </c>
       <c r="K47" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B47,C47,PVT_json)</f>
-        <v>817.91717555780713</v>
+        <v>817.91717555780701</v>
       </c>
       <c r="L47" s="12">
         <f>[1]!PVT_bg_m3m3(B47,C47,PVT_json)</f>
-        <v>5.3859511211398012E-3</v>
+        <v>5.385951121139803E-3</v>
       </c>
       <c r="M47" s="12">
         <f>[1]!PVT_bw_m3m3(B47,C47,PVT_json)</f>
@@ -14944,7 +14944,7 @@
       </c>
       <c r="Q47" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B47,C47,PVT_json)</f>
-        <v>1758.7003454838439</v>
+        <v>1758.7003454838443</v>
       </c>
       <c r="R47" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B47,C47,PVT_json)</f>
@@ -14952,18 +14952,18 @@
       </c>
       <c r="S47" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B47,C47,PVT_json)</f>
-        <v>3.3079491785157945E-5</v>
+        <v>3.3079491785157932E-5</v>
       </c>
       <c r="T47" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B47,C47,PVT_json)</f>
-        <v>1.1788581893601666E-4</v>
+        <v>1.1788581893601677E-4</v>
       </c>
       <c r="U47" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B47,C47,PVT_json)</f>
-        <v>6.0396792287000121E-3</v>
+        <v>6.0396792286972183E-3</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B48" s="7">
         <v>170.32</v>
       </c>
@@ -14977,19 +14977,19 @@
       </c>
       <c r="E48" s="8">
         <f>[1]!PVT_bo_m3m3(B48,C48,PVT_json)</f>
-        <v>1.1573887453687506</v>
+        <v>1.1573887453687508</v>
       </c>
       <c r="F48" s="9">
         <f>[1]!PVT_mu_oil_cP(B48,C48,PVT_json)</f>
-        <v>1.4837236136051828</v>
+        <v>1.4837236136051819</v>
       </c>
       <c r="G48" s="10">
         <f>[1]!PVT_mu_gas_cP(B48,C48,PVT_json)</f>
-        <v>1.866334463351298E-2</v>
+        <v>1.866334463351299E-2</v>
       </c>
       <c r="H48" s="8">
         <f>[1]!PVT_mu_wat_cP(B48,C48,PVT_json)</f>
-        <v>0.92614116411990222</v>
+        <v>0.92614116411990333</v>
       </c>
       <c r="I48" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B48,C48,PVT_json)</f>
@@ -14997,11 +14997,11 @@
       </c>
       <c r="J48" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B48,C48,PVT_json)</f>
-        <v>1092.6541057590266</v>
+        <v>1092.6541057590264</v>
       </c>
       <c r="K48" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B48,C48,PVT_json)</f>
-        <v>819.05272000720367</v>
+        <v>819.05272000720345</v>
       </c>
       <c r="L48" s="12">
         <f>[1]!PVT_bg_m3m3(B48,C48,PVT_json)</f>
@@ -15009,11 +15009,11 @@
       </c>
       <c r="M48" s="12">
         <f>[1]!PVT_bw_m3m3(B48,C48,PVT_json)</f>
-        <v>1.0067229823255646</v>
+        <v>1.0067229823255648</v>
       </c>
       <c r="N48" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B48,C48,PVT_json)</f>
-        <v>2.3304362560848248E-2</v>
+        <v>2.3304362560848245E-2</v>
       </c>
       <c r="O48" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B48,C48,PVT_json)</f>
@@ -15025,7 +15025,7 @@
       </c>
       <c r="Q48" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B48,C48,PVT_json)</f>
-        <v>1763.8631685330099</v>
+        <v>1763.8631685330097</v>
       </c>
       <c r="R48" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B48,C48,PVT_json)</f>
@@ -15033,18 +15033,18 @@
       </c>
       <c r="S48" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B48,C48,PVT_json)</f>
-        <v>3.3002007121787047E-5</v>
+        <v>3.300200712178704E-5</v>
       </c>
       <c r="T48" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B48,C48,PVT_json)</f>
-        <v>1.1099207330072591E-4</v>
+        <v>1.1099207330072599E-4</v>
       </c>
       <c r="U48" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B48,C48,PVT_json)</f>
-        <v>5.4810353399603355E-3</v>
+        <v>5.4810353399547635E-3</v>
       </c>
     </row>
-    <row r="49" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B49" s="7">
         <v>180.28</v>
       </c>
@@ -15058,23 +15058,23 @@
       </c>
       <c r="E49" s="8">
         <f>[1]!PVT_bo_m3m3(B49,C49,PVT_json)</f>
-        <v>1.155961320312646</v>
+        <v>1.1559613203126462</v>
       </c>
       <c r="F49" s="9">
         <f>[1]!PVT_mu_oil_cP(B49,C49,PVT_json)</f>
-        <v>1.5282077500006945</v>
+        <v>1.5282077500006936</v>
       </c>
       <c r="G49" s="10">
         <f>[1]!PVT_mu_gas_cP(B49,C49,PVT_json)</f>
-        <v>1.9263857676805878E-2</v>
+        <v>1.9263857676805881E-2</v>
       </c>
       <c r="H49" s="8">
         <f>[1]!PVT_mu_wat_cP(B49,C49,PVT_json)</f>
-        <v>0.93295727104683968</v>
+        <v>0.9329572710468409</v>
       </c>
       <c r="I49" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B49,C49,PVT_json)</f>
-        <v>151.83464007129291</v>
+        <v>151.83464007129285</v>
       </c>
       <c r="J49" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B49,C49,PVT_json)</f>
@@ -15082,11 +15082,11 @@
       </c>
       <c r="K49" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B49,C49,PVT_json)</f>
-        <v>820.06411749452855</v>
+        <v>820.06411749452832</v>
       </c>
       <c r="L49" s="12">
         <f>[1]!PVT_bg_m3m3(B49,C49,PVT_json)</f>
-        <v>4.8277520838183926E-3</v>
+        <v>4.8277520838183943E-3</v>
       </c>
       <c r="M49" s="12">
         <f>[1]!PVT_bw_m3m3(B49,C49,PVT_json)</f>
@@ -15106,7 +15106,7 @@
       </c>
       <c r="Q49" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B49,C49,PVT_json)</f>
-        <v>1772.2537457799388</v>
+        <v>1772.253745779939</v>
       </c>
       <c r="R49" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B49,C49,PVT_json)</f>
@@ -15114,18 +15114,18 @@
       </c>
       <c r="S49" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B49,C49,PVT_json)</f>
-        <v>3.2924884606820553E-5</v>
+        <v>3.2924884606820539E-5</v>
       </c>
       <c r="T49" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B49,C49,PVT_json)</f>
-        <v>1.0486005061337717E-4</v>
+        <v>1.0486005061337724E-4</v>
       </c>
       <c r="U49" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B49,C49,PVT_json)</f>
-        <v>4.9864510387410401E-3</v>
+        <v>4.9864510387451991E-3</v>
       </c>
     </row>
-    <row r="50" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="50" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B50" s="7">
         <v>190.24</v>
       </c>
@@ -15139,11 +15139,11 @@
       </c>
       <c r="E50" s="8">
         <f>[1]!PVT_bo_m3m3(B50,C50,PVT_json)</f>
-        <v>1.1546848543793078</v>
+        <v>1.154684854379308</v>
       </c>
       <c r="F50" s="9">
         <f>[1]!PVT_mu_oil_cP(B50,C50,PVT_json)</f>
-        <v>1.5744522715735527</v>
+        <v>1.5744522715735518</v>
       </c>
       <c r="G50" s="10">
         <f>[1]!PVT_mu_gas_cP(B50,C50,PVT_json)</f>
@@ -15151,11 +15151,11 @@
       </c>
       <c r="H50" s="8">
         <f>[1]!PVT_mu_wat_cP(B50,C50,PVT_json)</f>
-        <v>0.93988346952239354</v>
+        <v>0.93988346952239465</v>
       </c>
       <c r="I50" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B50,C50,PVT_json)</f>
-        <v>159.21255882955808</v>
+        <v>159.21255882955802</v>
       </c>
       <c r="J50" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B50,C50,PVT_json)</f>
@@ -15163,11 +15163,11 @@
       </c>
       <c r="K50" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B50,C50,PVT_json)</f>
-        <v>820.9706712655983</v>
+        <v>820.97067126559818</v>
       </c>
       <c r="L50" s="12">
         <f>[1]!PVT_bg_m3m3(B50,C50,PVT_json)</f>
-        <v>4.6040337859573023E-3</v>
+        <v>4.604033785957304E-3</v>
       </c>
       <c r="M50" s="12">
         <f>[1]!PVT_bw_m3m3(B50,C50,PVT_json)</f>
@@ -15175,7 +15175,7 @@
       </c>
       <c r="N50" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B50,C50,PVT_json)</f>
-        <v>2.2715336653548534E-2</v>
+        <v>2.271533665354853E-2</v>
       </c>
       <c r="O50" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B50,C50,PVT_json)</f>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="Q50" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B50,C50,PVT_json)</f>
-        <v>1783.5025425591436</v>
+        <v>1783.5025425591439</v>
       </c>
       <c r="R50" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B50,C50,PVT_json)</f>
@@ -15195,18 +15195,18 @@
       </c>
       <c r="S50" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B50,C50,PVT_json)</f>
-        <v>3.2848121707259906E-5</v>
+        <v>3.2848121707259892E-5</v>
       </c>
       <c r="T50" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B50,C50,PVT_json)</f>
-        <v>9.9370111041734814E-5</v>
+        <v>9.9370111041734908E-5</v>
       </c>
       <c r="U50" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B50,C50,PVT_json)</f>
-        <v>4.5486800289201356E-3</v>
+        <v>4.5486800289187583E-3</v>
       </c>
     </row>
-    <row r="51" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B51" s="7">
         <v>200.2</v>
       </c>
@@ -15220,23 +15220,23 @@
       </c>
       <c r="E51" s="8">
         <f>[1]!PVT_bo_m3m3(B51,C51,PVT_json)</f>
-        <v>1.1535366036244397</v>
+        <v>1.1535366036244399</v>
       </c>
       <c r="F51" s="9">
         <f>[1]!PVT_mu_oil_cP(B51,C51,PVT_json)</f>
-        <v>1.6223262473590123</v>
+        <v>1.6223262473590112</v>
       </c>
       <c r="G51" s="10">
         <f>[1]!PVT_mu_gas_cP(B51,C51,PVT_json)</f>
-        <v>2.0462990438987638E-2</v>
+        <v>2.0462990438987645E-2</v>
       </c>
       <c r="H51" s="8">
         <f>[1]!PVT_mu_wat_cP(B51,C51,PVT_json)</f>
-        <v>0.94691975954656327</v>
+        <v>0.94691975954656449</v>
       </c>
       <c r="I51" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B51,C51,PVT_json)</f>
-        <v>166.26488073925319</v>
+        <v>166.26488073925313</v>
       </c>
       <c r="J51" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B51,C51,PVT_json)</f>
@@ -15244,11 +15244,11 @@
       </c>
       <c r="K51" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B51,C51,PVT_json)</f>
-        <v>821.78788000439636</v>
+        <v>821.78788000439624</v>
       </c>
       <c r="L51" s="12">
         <f>[1]!PVT_bg_m3m3(B51,C51,PVT_json)</f>
-        <v>4.4087482379972179E-3</v>
+        <v>4.4087482379972188E-3</v>
       </c>
       <c r="M51" s="12">
         <f>[1]!PVT_bw_m3m3(B51,C51,PVT_json)</f>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="N51" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B51,C51,PVT_json)</f>
-        <v>2.2426430382489457E-2</v>
+        <v>2.2426430382489454E-2</v>
       </c>
       <c r="O51" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B51,C51,PVT_json)</f>
@@ -15268,7 +15268,7 @@
       </c>
       <c r="Q51" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B51,C51,PVT_json)</f>
-        <v>1797.2676853078917</v>
+        <v>1797.267685307892</v>
       </c>
       <c r="R51" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B51,C51,PVT_json)</f>
@@ -15276,18 +15276,18 @@
       </c>
       <c r="S51" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B51,C51,PVT_json)</f>
-        <v>3.2771715913673913E-5</v>
+        <v>3.2771715913673899E-5</v>
       </c>
       <c r="T51" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B51,C51,PVT_json)</f>
-        <v>9.4426423199698477E-5</v>
+        <v>9.4426423199698545E-5</v>
       </c>
       <c r="U51" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B51,C51,PVT_json)</f>
         <v>4.161065204668986E-3</v>
       </c>
     </row>
-    <row r="52" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B52" s="7">
         <v>210.16</v>
       </c>
@@ -15301,19 +15301,19 @@
       </c>
       <c r="E52" s="8">
         <f>[1]!PVT_bo_m3m3(B52,C52,PVT_json)</f>
-        <v>1.1524981743992877</v>
+        <v>1.1524981743992879</v>
       </c>
       <c r="F52" s="9">
         <f>[1]!PVT_mu_oil_cP(B52,C52,PVT_json)</f>
-        <v>1.6717010831085302</v>
+        <v>1.6717010831085291</v>
       </c>
       <c r="G52" s="10">
         <f>[1]!PVT_mu_gas_cP(B52,C52,PVT_json)</f>
-        <v>2.1057606715007227E-2</v>
+        <v>2.1057606715007234E-2</v>
       </c>
       <c r="H52" s="8">
         <f>[1]!PVT_mu_wat_cP(B52,C52,PVT_json)</f>
-        <v>0.95406614111934906</v>
+        <v>0.9540661411193504</v>
       </c>
       <c r="I52" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B52,C52,PVT_json)</f>
@@ -15325,7 +15325,7 @@
       </c>
       <c r="K52" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B52,C52,PVT_json)</f>
-        <v>822.52833111349867</v>
+        <v>822.52833111349844</v>
       </c>
       <c r="L52" s="12">
         <f>[1]!PVT_bg_m3m3(B52,C52,PVT_json)</f>
@@ -15337,7 +15337,7 @@
       </c>
       <c r="N52" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B52,C52,PVT_json)</f>
-        <v>2.2141198581887511E-2</v>
+        <v>2.2141198581887508E-2</v>
       </c>
       <c r="O52" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B52,C52,PVT_json)</f>
@@ -15349,7 +15349,7 @@
       </c>
       <c r="Q52" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B52,C52,PVT_json)</f>
-        <v>1813.2393462205034</v>
+        <v>1813.2393462205036</v>
       </c>
       <c r="R52" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B52,C52,PVT_json)</f>
@@ -15357,18 +15357,18 @@
       </c>
       <c r="S52" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B52,C52,PVT_json)</f>
-        <v>3.2695664739925259E-5</v>
+        <v>3.2695664739925253E-5</v>
       </c>
       <c r="T52" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B52,C52,PVT_json)</f>
-        <v>8.9951322442803733E-5</v>
+        <v>8.9951322442803814E-5</v>
       </c>
       <c r="U52" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B52,C52,PVT_json)</f>
         <v>3.8175450846443947E-3</v>
       </c>
     </row>
-    <row r="53" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="53" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B53" s="7">
         <v>220.12</v>
       </c>
@@ -15382,23 +15382,23 @@
       </c>
       <c r="E53" s="8">
         <f>[1]!PVT_bo_m3m3(B53,C53,PVT_json)</f>
-        <v>1.1515545307250843</v>
+        <v>1.1515545307250845</v>
       </c>
       <c r="F53" s="9">
         <f>[1]!PVT_mu_oil_cP(B53,C53,PVT_json)</f>
-        <v>1.7224494190043667</v>
+        <v>1.7224494190043653</v>
       </c>
       <c r="G53" s="10">
         <f>[1]!PVT_mu_gas_cP(B53,C53,PVT_json)</f>
-        <v>2.1646930620487406E-2</v>
+        <v>2.164693062048741E-2</v>
       </c>
       <c r="H53" s="8">
         <f>[1]!PVT_mu_wat_cP(B53,C53,PVT_json)</f>
-        <v>0.96132261424075138</v>
+        <v>0.96132261424075238</v>
       </c>
       <c r="I53" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B53,C53,PVT_json)</f>
-        <v>179.42664126080516</v>
+        <v>179.42664126080513</v>
       </c>
       <c r="J53" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B53,C53,PVT_json)</f>
@@ -15406,19 +15406,19 @@
       </c>
       <c r="K53" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B53,C53,PVT_json)</f>
-        <v>823.20235360726588</v>
+        <v>823.20235360726576</v>
       </c>
       <c r="L53" s="12">
         <f>[1]!PVT_bg_m3m3(B53,C53,PVT_json)</f>
-        <v>4.0853464950866497E-3</v>
+        <v>4.0853464950866506E-3</v>
       </c>
       <c r="M53" s="12">
         <f>[1]!PVT_bw_m3m3(B53,C53,PVT_json)</f>
-        <v>1.0052772879556282</v>
+        <v>1.0052772879556284</v>
       </c>
       <c r="N53" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B53,C53,PVT_json)</f>
-        <v>2.1859594517786071E-2</v>
+        <v>2.1859594517786067E-2</v>
       </c>
       <c r="O53" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B53,C53,PVT_json)</f>
@@ -15430,7 +15430,7 @@
       </c>
       <c r="Q53" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B53,C53,PVT_json)</f>
-        <v>1831.1410323141022</v>
+        <v>1831.1410323141026</v>
       </c>
       <c r="R53" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B53,C53,PVT_json)</f>
@@ -15438,18 +15438,18 @@
       </c>
       <c r="S53" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B53,C53,PVT_json)</f>
-        <v>3.2619965722900879E-5</v>
+        <v>3.2619965722900872E-5</v>
       </c>
       <c r="T53" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B53,C53,PVT_json)</f>
-        <v>8.5881200820369042E-5</v>
+        <v>8.5881200820369109E-5</v>
       </c>
       <c r="U53" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B53,C53,PVT_json)</f>
-        <v>3.5126588071656612E-3</v>
+        <v>3.5126588071723703E-3</v>
       </c>
     </row>
-    <row r="54" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B54" s="7">
         <v>230.08</v>
       </c>
@@ -15463,23 +15463,23 @@
       </c>
       <c r="E54" s="8">
         <f>[1]!PVT_bo_m3m3(B54,C54,PVT_json)</f>
-        <v>1.1506932615900209</v>
+        <v>1.1506932615900212</v>
       </c>
       <c r="F54" s="9">
         <f>[1]!PVT_mu_oil_cP(B54,C54,PVT_json)</f>
-        <v>1.7744443457903813</v>
+        <v>1.7744443457903811</v>
       </c>
       <c r="G54" s="10">
         <f>[1]!PVT_mu_gas_cP(B54,C54,PVT_json)</f>
-        <v>2.222988841787436E-2</v>
+        <v>2.222988841787437E-2</v>
       </c>
       <c r="H54" s="8">
         <f>[1]!PVT_mu_wat_cP(B54,C54,PVT_json)</f>
-        <v>0.96868917891076944</v>
+        <v>0.96868917891077067</v>
       </c>
       <c r="I54" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B54,C54,PVT_json)</f>
-        <v>185.56039675941111</v>
+        <v>185.56039675941105</v>
       </c>
       <c r="J54" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B54,C54,PVT_json)</f>
@@ -15487,19 +15487,19 @@
       </c>
       <c r="K54" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B54,C54,PVT_json)</f>
-        <v>823.81850284767575</v>
+        <v>823.81850284767563</v>
       </c>
       <c r="L54" s="12">
         <f>[1]!PVT_bg_m3m3(B54,C54,PVT_json)</f>
-        <v>3.950304120929421E-3</v>
+        <v>3.9503041209294218E-3</v>
       </c>
       <c r="M54" s="12">
         <f>[1]!PVT_bw_m3m3(B54,C54,PVT_json)</f>
-        <v>1.0049565810784551</v>
+        <v>1.0049565810784553</v>
       </c>
       <c r="N54" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B54,C54,PVT_json)</f>
-        <v>2.1581572050616938E-2</v>
+        <v>2.1581572050616935E-2</v>
       </c>
       <c r="O54" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B54,C54,PVT_json)</f>
@@ -15519,18 +15519,18 @@
       </c>
       <c r="S54" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B54,C54,PVT_json)</f>
-        <v>3.2544616422246009E-5</v>
+        <v>3.2544616422246003E-5</v>
       </c>
       <c r="T54" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B54,C54,PVT_json)</f>
-        <v>8.2163464553979641E-5</v>
+        <v>8.2163464553979695E-5</v>
       </c>
       <c r="U54" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B54,C54,PVT_json)</f>
-        <v>3.2415372867238821E-3</v>
+        <v>3.2415372867212271E-3</v>
       </c>
     </row>
-    <row r="55" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B55" s="7">
         <v>240.04</v>
       </c>
@@ -15544,19 +15544,19 @@
       </c>
       <c r="E55" s="8">
         <f>[1]!PVT_bo_m3m3(B55,C55,PVT_json)</f>
-        <v>1.1499040320855163</v>
+        <v>1.1499040320855165</v>
       </c>
       <c r="F55" s="9">
         <f>[1]!PVT_mu_oil_cP(B55,C55,PVT_json)</f>
-        <v>1.8275588769643232</v>
+        <v>1.8275588769643218</v>
       </c>
       <c r="G55" s="10">
         <f>[1]!PVT_mu_gas_cP(B55,C55,PVT_json)</f>
-        <v>2.2805673430647544E-2</v>
+        <v>2.2805673430647554E-2</v>
       </c>
       <c r="H55" s="8">
         <f>[1]!PVT_mu_wat_cP(B55,C55,PVT_json)</f>
-        <v>0.9761658351294038</v>
+        <v>0.97616583512940491</v>
       </c>
       <c r="I55" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B55,C55,PVT_json)</f>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="K55" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B55,C55,PVT_json)</f>
-        <v>824.38392557049644</v>
+        <v>824.38392557049622</v>
       </c>
       <c r="L55" s="12">
         <f>[1]!PVT_bg_m3m3(B55,C55,PVT_json)</f>
@@ -15592,7 +15592,7 @@
       </c>
       <c r="Q55" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B55,C55,PVT_json)</f>
-        <v>1871.7895129764195</v>
+        <v>1871.789512976419</v>
       </c>
       <c r="R55" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B55,C55,PVT_json)</f>
@@ -15600,18 +15600,18 @@
       </c>
       <c r="S55" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B55,C55,PVT_json)</f>
-        <v>3.2469614420101958E-5</v>
+        <v>3.2469614420101945E-5</v>
       </c>
       <c r="T55" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B55,C55,PVT_json)</f>
-        <v>7.875424897758555E-5</v>
+        <v>7.8754248977585604E-5</v>
       </c>
       <c r="U55" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B55,C55,PVT_json)</f>
-        <v>2.9998788826407735E-3</v>
+        <v>2.9998788826381484E-3</v>
       </c>
     </row>
-    <row r="56" spans="2:21" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B56" s="7">
         <v>250</v>
       </c>
@@ -15625,11 +15625,11 @@
       </c>
       <c r="E56" s="8">
         <f>[1]!PVT_bo_m3m3(B56,C56,PVT_json)</f>
-        <v>1.1491781667287437</v>
+        <v>1.149178166728744</v>
       </c>
       <c r="F56" s="9">
         <f>[1]!PVT_mu_oil_cP(B56,C56,PVT_json)</f>
-        <v>1.8816656286382254</v>
+        <v>1.8816656286382238</v>
       </c>
       <c r="G56" s="10">
         <f>[1]!PVT_mu_gas_cP(B56,C56,PVT_json)</f>
@@ -15637,31 +15637,31 @@
       </c>
       <c r="H56" s="8">
         <f>[1]!PVT_mu_wat_cP(B56,C56,PVT_json)</f>
-        <v>0.98375258289665413</v>
+        <v>0.98375258289665535</v>
       </c>
       <c r="I56" s="9">
         <f>[1]!PVT_rho_gas_kgm3(B56,C56,PVT_json)</f>
-        <v>197.00519059421654</v>
+        <v>197.00519059421646</v>
       </c>
       <c r="J56" s="11">
         <f>[1]!PVT_rho_wat_kgm3(B56,C56,PVT_json)</f>
-        <v>1095.308138800433</v>
+        <v>1095.3081388004327</v>
       </c>
       <c r="K56" s="11">
         <f>[1]!PVT_rho_oil_kgm3(B56,C56,PVT_json)</f>
-        <v>824.9046383281667</v>
+        <v>824.90463832816647</v>
       </c>
       <c r="L56" s="12">
         <f>[1]!PVT_bg_m3m3(B56,C56,PVT_json)</f>
-        <v>3.720815668810704E-3</v>
+        <v>3.7208156688107053E-3</v>
       </c>
       <c r="M56" s="12">
         <f>[1]!PVT_bw_m3m3(B56,C56,PVT_json)</f>
-        <v>1.0042835993209231</v>
+        <v>1.0042835993209234</v>
       </c>
       <c r="N56" s="10">
         <f>[1]!PVT_ST_oilgas_Nm(B56,C56,PVT_json)</f>
-        <v>2.1036090275482474E-2</v>
+        <v>2.1036090275482471E-2</v>
       </c>
       <c r="O56" s="12">
         <f>[1]!PVT_ST_watgas_Nm(B56,C56,PVT_json)</f>
@@ -15673,7 +15673,7 @@
       </c>
       <c r="Q56" s="13">
         <f>[1]!PVT_cp_gas_JkgC(B56,C56,PVT_json)</f>
-        <v>1894.1377412469885</v>
+        <v>1894.1377412469892</v>
       </c>
       <c r="R56" s="13">
         <f>[1]!PVT_cp_wat_JkgC(B56,C56,PVT_json)</f>
@@ -15681,15 +15681,15 @@
       </c>
       <c r="S56" s="14">
         <f>[1]!PVT_compressibility_wat_1atm(B56,C56,PVT_json)</f>
-        <v>3.2394957320847468E-5</v>
+        <v>3.2394957320847461E-5</v>
       </c>
       <c r="T56" s="14">
         <f>[1]!PVT_compressibility_oil_1atm(B56,C56,PVT_json)</f>
-        <v>7.5616679698318546E-5</v>
+        <v>7.5616679698318586E-5</v>
       </c>
       <c r="U56" s="14">
         <f>[1]!PVT_compressibility_gas_1atm(B56,C56,PVT_json)</f>
-        <v>2.7839125929281917E-3</v>
+        <v>2.7839125929281922E-3</v>
       </c>
     </row>
   </sheetData>
@@ -15703,19 +15703,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Лист2"/>
   <dimension ref="B5:J84"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="16.53515625" customWidth="1"/>
-    <col min="3" max="3" width="12.69140625" customWidth="1"/>
-    <col min="4" max="4" width="11.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" s="17" t="s">
         <v>2</v>
       </c>
@@ -15723,7 +15723,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="17" t="s">
         <v>3</v>
       </c>
@@ -15731,7 +15731,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="17" t="s">
         <v>4</v>
       </c>
@@ -15739,7 +15739,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="17" t="s">
         <v>5</v>
       </c>
@@ -15747,13 +15747,13 @@
         <v>200</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="17" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="20"/>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="17" t="s">
         <v>7</v>
       </c>
@@ -15761,19 +15761,19 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="17" t="s">
         <v>8</v>
       </c>
       <c r="C13" s="20"/>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="17" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="20"/>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="17" t="s">
         <v>10</v>
       </c>
@@ -15781,7 +15781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B16" s="17" t="s">
         <v>11</v>
       </c>
@@ -15790,7 +15790,7 @@
         <v>{"gamma_gas":0.7,"gamma_oil":0.86,"gamma_wat":1.1,"rsb_m3m3":200,"PVT_corr_set":1}</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="22" t="s">
         <v>41</v>
       </c>
@@ -15801,12 +15801,12 @@
       <c r="G19" s="20"/>
       <c r="H19" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="I21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>42</v>
       </c>
@@ -15831,17 +15831,17 @@
         <v>{"gamma_gas":0.7,"gamma_oil":0.86,"gamma_wat":1.1,"rsb_m3m3":200,"PVT_corr_set":1}</v>
       </c>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" s="23">
         <f t="array" ref="C23">[1]!unf_pvt_pb_Standing_MPa(B23,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>3.9516569619629709</v>
+        <v>3.9516569619629691</v>
       </c>
       <c r="D23" s="23">
         <f t="array" ref="D23">[1]!unf_pvt_pb_Valko_McCain_MPa(B23,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>4.7652176471718679</v>
+        <v>4.7652176471718688</v>
       </c>
       <c r="F23" t="str">
         <f t="array" ref="F23">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B23,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -15849,28 +15849,28 @@
       </c>
       <c r="G23">
         <f t="array" ref="G23">[1]!PVT_pb_atma(t_res_C,F23)</f>
-        <v>4.7652176471718679</v>
+        <v>4.7652176471718688</v>
       </c>
       <c r="I23" s="24">
         <f t="array" ref="I23">[1]!PVT_rsb_m3m3(C23,t_res_C,$I$22)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="J23" s="24">
         <f t="array" ref="J23">[1]!PVT_rsb_m3m3(D23,t_res_C,$J$22)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24">
         <v>10</v>
       </c>
       <c r="C24" s="23">
         <f t="array" ref="C24">[1]!unf_pvt_pb_Standing_MPa(B24,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>26.204265257695354</v>
+        <v>26.20426525769534</v>
       </c>
       <c r="D24" s="23">
         <f t="array" ref="D24">[1]!unf_pvt_pb_Valko_McCain_MPa(B24,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>27.622604514708922</v>
+        <v>27.622604514708939</v>
       </c>
       <c r="F24" t="str">
         <f t="array" ref="F24">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B24,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -15878,28 +15878,28 @@
       </c>
       <c r="G24">
         <f t="array" ref="G24">[1]!PVT_pb_atma(t_res_C,F24)</f>
-        <v>27.622604514708922</v>
+        <v>27.622604514708939</v>
       </c>
       <c r="I24" s="24">
         <f t="array" ref="I24">[1]!PVT_rsb_m3m3(C24,t_res_C,$I$22)</f>
-        <v>10.116275144756642</v>
+        <v>10.11627514475664</v>
       </c>
       <c r="J24" s="24">
         <f t="array" ref="J24">[1]!PVT_rsb_m3m3(D24,t_res_C,$J$22)</f>
-        <v>10.088350183735288</v>
+        <v>10.08835018373529</v>
       </c>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25">
         <v>30</v>
       </c>
       <c r="C25" s="23">
         <f t="array" ref="C25">[1]!unf_pvt_pb_Standing_MPa(B25,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>65.220275414584947</v>
+        <v>65.220275414584904</v>
       </c>
       <c r="D25" s="23">
         <f t="array" ref="D25">[1]!unf_pvt_pb_Valko_McCain_MPa(B25,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>70.525292114122337</v>
+        <v>70.525292114122379</v>
       </c>
       <c r="F25" t="str">
         <f t="array" ref="F25">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B25,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -15907,28 +15907,28 @@
       </c>
       <c r="G25">
         <f t="array" ref="G25">[1]!PVT_pb_atma(t_res_C,F25)</f>
-        <v>70.525292114122337</v>
+        <v>70.525292114122365</v>
       </c>
       <c r="I25" s="24">
         <f t="array" ref="I25">[1]!PVT_rsb_m3m3(C25,t_res_C,$I$22)</f>
-        <v>30.027970672961317</v>
+        <v>30.027970672961324</v>
       </c>
       <c r="J25" s="24">
         <f t="array" ref="J25">[1]!PVT_rsb_m3m3(D25,t_res_C,$J$22)</f>
-        <v>30.02699818793041</v>
+        <v>30.02699818793042</v>
       </c>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26">
         <v>50</v>
       </c>
       <c r="C26" s="23">
         <f t="array" ref="C26">[1]!unf_pvt_pb_Standing_MPa(B26,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>99.65912978060156</v>
+        <v>99.659129780601489</v>
       </c>
       <c r="D26" s="23">
         <f t="array" ref="D26">[1]!unf_pvt_pb_Valko_McCain_MPa(B26,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>108.56201380760591</v>
+        <v>108.56201380760596</v>
       </c>
       <c r="F26" t="str">
         <f t="array" ref="F26">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B26,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -15936,28 +15936,28 @@
       </c>
       <c r="G26">
         <f t="array" ref="G26">[1]!PVT_pb_atma(t_res_C,F26)</f>
-        <v>108.56201380760591</v>
+        <v>108.56201380760596</v>
       </c>
       <c r="I26" s="24">
         <f t="array" ref="I26">[1]!PVT_rsb_m3m3(C26,t_res_C,$I$22)</f>
-        <v>50.016124941183321</v>
+        <v>50.016124941183307</v>
       </c>
       <c r="J26" s="24">
         <f t="array" ref="J26">[1]!PVT_rsb_m3m3(D26,t_res_C,$J$22)</f>
-        <v>50.023708263487187</v>
+        <v>50.023708263487215</v>
       </c>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27">
         <v>70</v>
       </c>
       <c r="C27" s="23">
         <f t="array" ref="C27">[1]!unf_pvt_pb_Standing_MPa(B27,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>131.76599936161304</v>
+        <v>131.76599936161296</v>
       </c>
       <c r="D27" s="23">
         <f t="array" ref="D27">[1]!unf_pvt_pb_Valko_McCain_MPa(B27,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>142.80213140879403</v>
+        <v>142.80213140879411</v>
       </c>
       <c r="F27" t="str">
         <f t="array" ref="F27">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B27,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -15965,7 +15965,7 @@
       </c>
       <c r="G27">
         <f t="array" ref="G27">[1]!PVT_pb_atma(t_res_C,F27)</f>
-        <v>142.80213140879403</v>
+        <v>142.80213140879411</v>
       </c>
       <c r="I27" s="24">
         <f t="array" ref="I27">[1]!PVT_rsb_m3m3(C27,t_res_C,$I$22)</f>
@@ -15973,20 +15973,20 @@
       </c>
       <c r="J27" s="24">
         <f t="array" ref="J27">[1]!PVT_rsb_m3m3(D27,t_res_C,$J$22)</f>
-        <v>70.021720723616838</v>
+        <v>70.021720723616852</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28">
         <v>90</v>
       </c>
       <c r="C28" s="23">
         <f t="array" ref="C28">[1]!unf_pvt_pb_Standing_MPa(B28,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>162.32793720118303</v>
+        <v>162.32793720118292</v>
       </c>
       <c r="D28" s="23">
         <f t="array" ref="D28">[1]!unf_pvt_pb_Valko_McCain_MPa(B28,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>173.89555548851538</v>
+        <v>173.89555548851553</v>
       </c>
       <c r="F28" t="str">
         <f t="array" ref="F28">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B28,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="G28">
         <f t="array" ref="G28">[1]!PVT_pb_atma(t_res_C,F28)</f>
-        <v>173.89555548851538</v>
+        <v>173.89555548851553</v>
       </c>
       <c r="I28" s="24">
         <f t="array" ref="I28">[1]!PVT_rsb_m3m3(C28,t_res_C,$I$22)</f>
@@ -16002,20 +16002,20 @@
       </c>
       <c r="J28" s="24">
         <f t="array" ref="J28">[1]!PVT_rsb_m3m3(D28,t_res_C,$J$22)</f>
-        <v>90.020260044318292</v>
+        <v>90.02026004431832</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29">
         <v>110</v>
       </c>
       <c r="C29" s="23">
         <f t="array" ref="C29">[1]!unf_pvt_pb_Standing_MPa(B29,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>191.74670764006245</v>
+        <v>191.74670764006237</v>
       </c>
       <c r="D29" s="23">
         <f t="array" ref="D29">[1]!unf_pvt_pb_Valko_McCain_MPa(B29,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>202.31347221879278</v>
+        <v>202.31347221879295</v>
       </c>
       <c r="F29" t="str">
         <f t="array" ref="F29">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B29,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16023,28 +16023,28 @@
       </c>
       <c r="G29">
         <f t="array" ref="G29">[1]!PVT_pb_atma(t_res_C,F29)</f>
-        <v>202.31347221879278</v>
+        <v>202.31347221879295</v>
       </c>
       <c r="I29" s="24">
         <f t="array" ref="I29">[1]!PVT_rsb_m3m3(C29,t_res_C,$I$22)</f>
-        <v>110.00711568881245</v>
+        <v>110.00711568881246</v>
       </c>
       <c r="J29" s="24">
         <f t="array" ref="J29">[1]!PVT_rsb_m3m3(D29,t_res_C,$J$22)</f>
-        <v>110.01911270138271</v>
+        <v>110.01911270138272</v>
       </c>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30">
         <v>150</v>
       </c>
       <c r="C30" s="23">
         <f t="array" ref="C30">[1]!unf_pvt_pb_Standing_MPa(B30,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>248.04343216453722</v>
+        <v>248.04343216453705</v>
       </c>
       <c r="D30" s="23">
         <f t="array" ref="D30">[1]!unf_pvt_pb_Valko_McCain_MPa(B30,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>252.49547384519565</v>
+        <v>252.49547384519579</v>
       </c>
       <c r="F30" t="str">
         <f t="array" ref="F30">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B30,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16052,24 +16052,24 @@
       </c>
       <c r="G30">
         <f t="array" ref="G30">[1]!PVT_pb_atma(t_res_C,F30)</f>
-        <v>252.49547384519565</v>
+        <v>252.49547384519579</v>
       </c>
       <c r="I30" s="24">
         <f t="array" ref="I30">[1]!PVT_rsb_m3m3(C30,t_res_C,$I$22)</f>
-        <v>150.00518563484462</v>
+        <v>150.00518563484465</v>
       </c>
       <c r="J30" s="24">
         <f t="array" ref="J30">[1]!PVT_rsb_m3m3(D30,t_res_C,$J$22)</f>
         <v>150.01739860952731</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31">
         <v>190</v>
       </c>
       <c r="C31" s="23">
         <f t="array" ref="C31">[1]!unf_pvt_pb_Standing_MPa(B31,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>301.81267586222083</v>
+        <v>301.81267586222066</v>
       </c>
       <c r="D31" s="23">
         <f t="array" ref="D31">[1]!unf_pvt_pb_Valko_McCain_MPa(B31,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
@@ -16089,20 +16089,20 @@
       </c>
       <c r="J31" s="24">
         <f t="array" ref="J31">[1]!PVT_rsb_m3m3(D31,t_res_C,$J$22)</f>
-        <v>190.01616734921052</v>
+        <v>190.01616734921049</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32">
         <v>230</v>
       </c>
       <c r="C32" s="23">
         <f t="array" ref="C32">[1]!unf_pvt_pb_Standing_MPa(B32,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>353.67640780212287</v>
+        <v>353.67640780212275</v>
       </c>
       <c r="D32" s="23">
         <f t="array" ref="D32">[1]!unf_pvt_pb_Valko_McCain_MPa(B32,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>332.67223073950186</v>
+        <v>332.67223073950203</v>
       </c>
       <c r="F32" t="str">
         <f t="array" ref="F32">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B32,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16110,28 +16110,28 @@
       </c>
       <c r="G32">
         <f t="array" ref="G32">[1]!PVT_pb_atma(t_res_C,F32)</f>
-        <v>332.67223073950191</v>
+        <v>332.67223073950203</v>
       </c>
       <c r="I32" s="24">
         <f t="array" ref="I32">[1]!PVT_rsb_m3m3(C32,t_res_C,$I$22)</f>
-        <v>230.00336210460026</v>
+        <v>230.00336210460028</v>
       </c>
       <c r="J32" s="24">
         <f t="array" ref="J32">[1]!PVT_rsb_m3m3(D32,t_res_C,$J$22)</f>
-        <v>230.01523869147599</v>
+        <v>230.01523869147576</v>
       </c>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33">
         <v>270</v>
       </c>
       <c r="C33" s="23">
         <f t="array" ref="C33">[1]!unf_pvt_pb_Standing_MPa(B33,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>404.02097397611703</v>
+        <v>404.02097397611681</v>
       </c>
       <c r="D33" s="23">
         <f t="array" ref="D33">[1]!unf_pvt_pb_Valko_McCain_MPa(B33,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>365.15217984314569</v>
+        <v>365.15217984314586</v>
       </c>
       <c r="F33" t="str">
         <f t="array" ref="F33">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B33,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16139,7 +16139,7 @@
       </c>
       <c r="G33">
         <f t="array" ref="G33">[1]!PVT_pb_atma(t_res_C,F33)</f>
-        <v>365.15217984314569</v>
+        <v>365.15217984314586</v>
       </c>
       <c r="I33" s="24">
         <f t="array" ref="I33">[1]!PVT_rsb_m3m3(C33,t_res_C,$I$22)</f>
@@ -16147,20 +16147,20 @@
       </c>
       <c r="J33" s="24">
         <f t="array" ref="J33">[1]!PVT_rsb_m3m3(D33,t_res_C,$J$22)</f>
-        <v>270.01451707721083</v>
+        <v>270.01451707721037</v>
       </c>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34">
         <v>310</v>
       </c>
       <c r="C34" s="23">
         <f t="array" ref="C34">[1]!unf_pvt_pb_Standing_MPa(B34,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>453.10848286447049</v>
+        <v>453.10848286447026</v>
       </c>
       <c r="D34" s="23">
         <f t="array" ref="D34">[1]!unf_pvt_pb_Valko_McCain_MPa(B34,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>393.69006660795338</v>
+        <v>393.69006660795321</v>
       </c>
       <c r="F34" t="str">
         <f t="array" ref="F34">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B34,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16168,28 +16168,28 @@
       </c>
       <c r="G34">
         <f t="array" ref="G34">[1]!PVT_pb_atma(t_res_C,F34)</f>
-        <v>393.69006660795338</v>
+        <v>393.69006660795321</v>
       </c>
       <c r="I34" s="24">
         <f t="array" ref="I34">[1]!PVT_rsb_m3m3(C34,t_res_C,$I$22)</f>
-        <v>310.00248746260189</v>
+        <v>310.00248746260195</v>
       </c>
       <c r="J34" s="24">
         <f t="array" ref="J34">[1]!PVT_rsb_m3m3(D34,t_res_C,$J$22)</f>
-        <v>310.01394619902834</v>
+        <v>310.0139461990276</v>
       </c>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35">
         <v>350</v>
       </c>
       <c r="C35" s="23">
         <f t="array" ref="C35">[1]!unf_pvt_pb_Standing_MPa(B35,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>501.12776305350894</v>
+        <v>501.12776305350866</v>
       </c>
       <c r="D35" s="23">
         <f t="array" ref="D35">[1]!unf_pvt_pb_Valko_McCain_MPa(B35,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>418.89203273740901</v>
+        <v>418.89203273740918</v>
       </c>
       <c r="F35" t="str">
         <f t="array" ref="F35">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B35,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16197,7 +16197,7 @@
       </c>
       <c r="G35">
         <f t="array" ref="G35">[1]!PVT_pb_atma(t_res_C,F35)</f>
-        <v>418.89203273740895</v>
+        <v>418.89203273740918</v>
       </c>
       <c r="I35" s="24">
         <f t="array" ref="I35">[1]!PVT_rsb_m3m3(C35,t_res_C,$I$22)</f>
@@ -16208,17 +16208,17 @@
         <v>350.01349049519706</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36">
         <v>390</v>
       </c>
       <c r="C36" s="23">
         <f t="array" ref="C36">[1]!unf_pvt_pb_Standing_MPa(B36,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>548.22092849987712</v>
+        <v>548.22092849987689</v>
       </c>
       <c r="D36" s="23">
         <f t="array" ref="D36">[1]!unf_pvt_pb_Valko_McCain_MPa(B36,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>441.23836560123243</v>
+        <v>441.23836560123277</v>
       </c>
       <c r="F36" t="str">
         <f t="array" ref="F36">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B36,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16226,28 +16226,28 @@
       </c>
       <c r="G36">
         <f t="array" ref="G36">[1]!PVT_pb_atma(t_res_C,F36)</f>
-        <v>441.23836560123249</v>
+        <v>441.23836560123283</v>
       </c>
       <c r="I36" s="24">
         <f t="array" ref="I36">[1]!PVT_rsb_m3m3(C36,t_res_C,$I$22)</f>
-        <v>390.00197395933077</v>
+        <v>390.00197395933083</v>
       </c>
       <c r="J36" s="24">
         <f t="array" ref="J36">[1]!PVT_rsb_m3m3(D36,t_res_C,$J$22)</f>
-        <v>390.01312640546092</v>
+        <v>390.01312640546115</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37">
         <v>430</v>
       </c>
       <c r="C37" s="23">
         <f t="array" ref="C37">[1]!unf_pvt_pb_Standing_MPa(B37,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>594.49855745182083</v>
+        <v>594.49855745182049</v>
       </c>
       <c r="D37" s="23">
         <f t="array" ref="D37">[1]!unf_pvt_pb_Valko_McCain_MPa(B37,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>461.1167930075195</v>
+        <v>461.11679300751973</v>
       </c>
       <c r="F37" t="str">
         <f t="array" ref="F37">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B37,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16255,28 +16255,28 @@
       </c>
       <c r="G37">
         <f t="array" ref="G37">[1]!PVT_pb_atma(t_res_C,F37)</f>
-        <v>461.1167930075195</v>
+        <v>461.11679300751973</v>
       </c>
       <c r="I37" s="24">
         <f t="array" ref="I37">[1]!PVT_rsb_m3m3(C37,t_res_C,$I$22)</f>
-        <v>430.00178927573398</v>
+        <v>430.00178927573404</v>
       </c>
       <c r="J37" s="24">
         <f t="array" ref="J37">[1]!PVT_rsb_m3m3(D37,t_res_C,$J$22)</f>
-        <v>430.0128378103995</v>
+        <v>430.01283781039996</v>
       </c>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38">
         <v>470</v>
       </c>
       <c r="C38" s="23">
         <f t="array" ref="C38">[1]!unf_pvt_pb_Standing_MPa(B38,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>640.04897894804446</v>
+        <v>640.04897894804401</v>
       </c>
       <c r="D38" s="23">
         <f t="array" ref="D38">[1]!unf_pvt_pb_Valko_McCain_MPa(B38,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>478.84516848321852</v>
+        <v>478.84516848321897</v>
       </c>
       <c r="F38" t="str">
         <f t="array" ref="F38">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B38,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16284,28 +16284,28 @@
       </c>
       <c r="G38">
         <f t="array" ref="G38">[1]!PVT_pb_atma(t_res_C,F38)</f>
-        <v>478.84516848321852</v>
+        <v>478.84516848321897</v>
       </c>
       <c r="I38" s="24">
         <f t="array" ref="I38">[1]!PVT_rsb_m3m3(C38,t_res_C,$I$22)</f>
-        <v>470.0016361942927</v>
+        <v>470.00163619429253</v>
       </c>
       <c r="J38" s="24">
         <f t="array" ref="J38">[1]!PVT_rsb_m3m3(D38,t_res_C,$J$22)</f>
-        <v>470.0126134775108</v>
+        <v>470.01261347751091</v>
       </c>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39">
         <v>510</v>
       </c>
       <c r="C39" s="23">
         <f t="array" ref="C39">[1]!unf_pvt_pb_Standing_MPa(B39,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>684.94426416794636</v>
+        <v>684.9442641679459</v>
       </c>
       <c r="D39" s="23">
         <f t="array" ref="D39">[1]!unf_pvt_pb_Valko_McCain_MPa(B39,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>494.68745080004715</v>
+        <v>494.68745080004754</v>
       </c>
       <c r="F39" t="str">
         <f t="array" ref="F39">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B39,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16313,7 +16313,7 @@
       </c>
       <c r="G39">
         <f t="array" ref="G39">[1]!PVT_pb_atma(t_res_C,F39)</f>
-        <v>494.68745080004715</v>
+        <v>494.68745080004754</v>
       </c>
       <c r="I39" s="24">
         <f t="array" ref="I39">[1]!PVT_rsb_m3m3(C39,t_res_C,$I$22)</f>
@@ -16321,20 +16321,20 @@
       </c>
       <c r="J39" s="24">
         <f t="array" ref="J39">[1]!PVT_rsb_m3m3(D39,t_res_C,$J$22)</f>
-        <v>510.01244555520412</v>
+        <v>510.01244555520441</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40">
         <v>550</v>
       </c>
       <c r="C40" s="23">
         <f t="array" ref="C40">[1]!unf_pvt_pb_Standing_MPa(B40,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>729.24425980966021</v>
+        <v>729.24425980965975</v>
       </c>
       <c r="D40" s="23">
         <f t="array" ref="D40">[1]!unf_pvt_pb_Valko_McCain_MPa(B40,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>508.86527275976403</v>
+        <v>508.86527275976425</v>
       </c>
       <c r="F40" t="str">
         <f t="array" ref="F40">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B40,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="G40">
         <f t="array" ref="G40">[1]!PVT_pb_atma(t_res_C,F40)</f>
-        <v>508.86527275976397</v>
+        <v>508.8652727597642</v>
       </c>
       <c r="I40" s="24">
         <f t="array" ref="I40">[1]!PVT_rsb_m3m3(C40,t_res_C,$I$22)</f>
@@ -16350,20 +16350,20 @@
       </c>
       <c r="J40" s="24">
         <f t="array" ref="J40">[1]!PVT_rsb_m3m3(D40,t_res_C,$J$22)</f>
-        <v>550.01232865340035</v>
+        <v>550.01232865339978</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41">
         <v>590</v>
       </c>
       <c r="C41" s="23">
         <f t="array" ref="C41">[1]!unf_pvt_pb_Standing_MPa(B41,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>772.99939974004803</v>
+        <v>772.99939974004769</v>
       </c>
       <c r="D41" s="23">
         <f t="array" ref="D41">[1]!unf_pvt_pb_Valko_McCain_MPa(B41,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>521.56651174046624</v>
+        <v>521.56651174046658</v>
       </c>
       <c r="F41" t="str">
         <f t="array" ref="F41">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B41,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16371,28 +16371,28 @@
       </c>
       <c r="G41">
         <f t="array" ref="G41">[1]!PVT_pb_atma(t_res_C,F41)</f>
-        <v>521.56651174046613</v>
+        <v>521.56651174046658</v>
       </c>
       <c r="I41" s="24">
         <f t="array" ref="I41">[1]!PVT_rsb_m3m3(C41,t_res_C,$I$22)</f>
-        <v>590.00130201515628</v>
+        <v>590.0013020151564</v>
       </c>
       <c r="J41" s="24">
         <f t="array" ref="J41">[1]!PVT_rsb_m3m3(D41,t_res_C,$J$22)</f>
-        <v>590.01225927372252</v>
+        <v>590.01225927372332</v>
       </c>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42">
         <v>630</v>
       </c>
       <c r="C42" s="23">
         <f t="array" ref="C42">[1]!unf_pvt_pb_Standing_MPa(B42,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>816.25272295477498</v>
+        <v>816.25272295477441</v>
       </c>
       <c r="D42" s="23">
         <f t="array" ref="D42">[1]!unf_pvt_pb_Valko_McCain_MPa(B42,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>532.95176494853706</v>
+        <v>532.9517649485374</v>
       </c>
       <c r="F42" t="str">
         <f t="array" ref="F42">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,B42,pb_atma,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
@@ -16400,7 +16400,7 @@
       </c>
       <c r="G42">
         <f t="array" ref="G42">[1]!PVT_pb_atma(t_res_C,F42)</f>
-        <v>532.95176494853717</v>
+        <v>532.9517649485374</v>
       </c>
       <c r="I42" s="24">
         <f t="array" ref="I42">[1]!PVT_rsb_m3m3(C42,t_res_C,$I$22)</f>
@@ -16408,16 +16408,16 @@
       </c>
       <c r="J42" s="24">
         <f t="array" ref="J42">[1]!PVT_rsb_m3m3(D42,t_res_C,$J$22)</f>
-        <v>630.01223546176163</v>
+        <v>630.01223546176209</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.4">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43">
         <v>670</v>
       </c>
       <c r="C43" s="23">
         <f t="array" ref="C43">[1]!unf_pvt_pb_Standing_MPa(B43,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
-        <v>859.04135817139559</v>
+        <v>859.04135817139502</v>
       </c>
       <c r="D43" s="23">
         <f t="array" ref="D43">[1]!unf_pvt_pb_Valko_McCain_MPa(B43,gamma_gas,t_res_C+273,gamma_oil)*10/1.01325</f>
@@ -16433,14 +16433,14 @@
       </c>
       <c r="I43" s="24">
         <f t="array" ref="I43">[1]!PVT_rsb_m3m3(C43,t_res_C,$I$22)</f>
-        <v>670.00114597835829</v>
+        <v>670.00114597835807</v>
       </c>
       <c r="J43" s="24">
         <f t="array" ref="J43">[1]!PVT_rsb_m3m3(D43,t_res_C,$J$22)</f>
-        <v>670.01225661138767</v>
+        <v>670.01225661138756</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B49" s="22" t="s">
         <v>48</v>
       </c>
@@ -16451,7 +16451,7 @@
       <c r="G49" s="20"/>
       <c r="H49" s="20"/>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B51" s="17" t="s">
         <v>42</v>
       </c>
@@ -16463,20 +16463,20 @@
         <v>{"gamma_gas":0.7,"gamma_oil":0.86,"gamma_wat":1.1,"rsb_m3m3":240,"PVT_corr_set":1}</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B52" s="17" t="s">
         <v>49</v>
       </c>
       <c r="C52" s="21">
         <f t="array" ref="C52">[1]!PVT_pb_atma(t_res_C,F51)</f>
-        <v>341.20095644869355</v>
+        <v>341.20095644869366</v>
       </c>
       <c r="F52" t="str">
         <f t="array" ref="F52">[1]!encode_PVT(gamma_gas,gamma_oil,gamma_wat,C51,C52,t_res_C,bob_m3m3,muob_cP,pvt_corr_set)</f>
         <v>{"gamma_gas":0.7,"gamma_oil":0.86,"gamma_wat":1.1,"rsb_m3m3":240,"pb_atma":341.201,"t_res_C":80,"PVT_corr_set":1}</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B54" s="17" t="s">
         <v>50</v>
       </c>
@@ -16484,16 +16484,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B55" s="17" t="s">
         <v>51</v>
       </c>
       <c r="C55" s="18">
         <f>C52</f>
-        <v>341.20095644869355</v>
+        <v>341.20095644869366</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B56" s="17" t="s">
         <v>52</v>
       </c>
@@ -16501,7 +16501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57" s="17" t="s">
         <v>53</v>
       </c>
@@ -16510,17 +16510,17 @@
         <v>[1,14.608,28.216,41.824,55.432,69.04,82.648,96.256,109.864,123.472,137.08,150.688,164.296,177.904,191.513,205.121,218.729,232.337,245.945,259.553,273.161,286.769,300.377,313.985,327.593,341.201]</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C59">
         <f t="array" ref="C59:C84">[1]!decode_json($C$57)</f>
         <v>1</v>
       </c>
       <c r="D59">
         <f t="array" ref="D59">[1]!PVT_rs_m3m3(C59,t_res_C,$F$52)</f>
-        <v>8.2271659062691072E-2</v>
+        <v>8.2271659062697899E-2</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C60">
         <v>14.608000000000001</v>
       </c>
@@ -16529,196 +16529,196 @@
         <v>18.022014659826571</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C61">
         <v>28.216000000000001</v>
       </c>
       <c r="D61">
         <f t="array" ref="D61">[1]!PVT_rs_m3m3(C61,t_res_C,$F$52)</f>
-        <v>28.259056830115661</v>
+        <v>28.259056830115654</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C62">
         <v>41.823999999999998</v>
       </c>
       <c r="D62">
         <f t="array" ref="D62">[1]!PVT_rs_m3m3(C62,t_res_C,$F$52)</f>
-        <v>36.880577262600667</v>
+        <v>36.880577262600646</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C63">
         <v>55.432000000000002</v>
       </c>
       <c r="D63">
         <f t="array" ref="D63">[1]!PVT_rs_m3m3(C63,t_res_C,$F$52)</f>
-        <v>44.700919980779865</v>
+        <v>44.700919980779858</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C64">
         <v>69.040000000000006</v>
       </c>
       <c r="D64">
         <f t="array" ref="D64">[1]!PVT_rs_m3m3(C64,t_res_C,$F$52)</f>
-        <v>52.074681365632507</v>
+        <v>52.074681365632486</v>
       </c>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C65">
         <v>82.647999999999996</v>
       </c>
       <c r="D65">
         <f t="array" ref="D65">[1]!PVT_rs_m3m3(C65,t_res_C,$F$52)</f>
-        <v>59.205451693691721</v>
+        <v>59.2054516936917</v>
       </c>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C66">
         <v>96.256</v>
       </c>
       <c r="D66">
         <f t="array" ref="D66">[1]!PVT_rs_m3m3(C66,t_res_C,$F$52)</f>
-        <v>66.229037764954597</v>
+        <v>66.229037764954583</v>
       </c>
     </row>
-    <row r="67" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="67" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C67">
         <v>109.864</v>
       </c>
       <c r="D67">
         <f t="array" ref="D67">[1]!PVT_rs_m3m3(C67,t_res_C,$F$52)</f>
-        <v>73.245164700554909</v>
+        <v>73.245164700554881</v>
       </c>
     </row>
-    <row r="68" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="68" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C68">
         <v>123.47199999999999</v>
       </c>
       <c r="D68">
         <f t="array" ref="D68">[1]!PVT_rs_m3m3(C68,t_res_C,$F$52)</f>
-        <v>80.332105990458743</v>
+        <v>80.332105990458729</v>
       </c>
     </row>
-    <row r="69" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="69" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C69">
         <v>137.08000000000001</v>
       </c>
       <c r="D69">
         <f t="array" ref="D69">[1]!PVT_rs_m3m3(C69,t_res_C,$F$52)</f>
-        <v>87.554340117432062</v>
+        <v>87.554340117432034</v>
       </c>
     </row>
-    <row r="70" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="70" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C70">
         <v>150.68799999999999</v>
       </c>
       <c r="D70">
         <f t="array" ref="D70">[1]!PVT_rs_m3m3(C70,t_res_C,$F$52)</f>
-        <v>94.966934917925684</v>
+        <v>94.96693491792567</v>
       </c>
     </row>
-    <row r="71" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="71" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C71">
         <v>164.29599999999999</v>
       </c>
       <c r="D71">
         <f t="array" ref="D71">[1]!PVT_rs_m3m3(C71,t_res_C,$F$52)</f>
-        <v>102.61823487507661</v>
+        <v>102.61823487507657</v>
       </c>
     </row>
-    <row r="72" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="72" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C72">
         <v>177.904</v>
       </c>
       <c r="D72">
         <f t="array" ref="D72">[1]!PVT_rs_m3m3(C72,t_res_C,$F$52)</f>
-        <v>110.55159866234955</v>
+        <v>110.55159866234952</v>
       </c>
     </row>
-    <row r="73" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="73" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C73">
         <v>191.51300000000001</v>
       </c>
       <c r="D73">
         <f t="array" ref="D73">[1]!PVT_rs_m3m3(C73,t_res_C,$F$52)</f>
-        <v>118.80719158854976</v>
+        <v>118.80719158854971</v>
       </c>
     </row>
-    <row r="74" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="74" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C74">
         <v>205.12100000000001</v>
       </c>
       <c r="D74">
         <f t="array" ref="D74">[1]!PVT_rs_m3m3(C74,t_res_C,$F$52)</f>
-        <v>127.42035661422514</v>
+        <v>127.42035661422511</v>
       </c>
     </row>
-    <row r="75" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="75" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C75">
         <v>218.72900000000001</v>
       </c>
       <c r="D75">
         <f t="array" ref="D75">[1]!PVT_rs_m3m3(C75,t_res_C,$F$52)</f>
-        <v>136.4258420378884</v>
+        <v>136.42584203788834</v>
       </c>
     </row>
-    <row r="76" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="76" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C76">
         <v>232.33699999999999</v>
       </c>
       <c r="D76">
         <f t="array" ref="D76">[1]!PVT_rs_m3m3(C76,t_res_C,$F$52)</f>
-        <v>145.85583986198881</v>
+        <v>145.85583986198873</v>
       </c>
     </row>
-    <row r="77" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="77" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C77">
         <v>245.94499999999999</v>
       </c>
       <c r="D77">
         <f t="array" ref="D77">[1]!PVT_rs_m3m3(C77,t_res_C,$F$52)</f>
-        <v>155.74091151119109</v>
+        <v>155.74091151119103</v>
       </c>
     </row>
-    <row r="78" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="78" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C78">
         <v>259.553</v>
       </c>
       <c r="D78">
         <f t="array" ref="D78">[1]!PVT_rs_m3m3(C78,t_res_C,$F$52)</f>
-        <v>166.1102434845109</v>
+        <v>166.11024348451087</v>
       </c>
     </row>
-    <row r="79" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="79" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C79">
         <v>273.161</v>
       </c>
       <c r="D79">
         <f t="array" ref="D79">[1]!PVT_rs_m3m3(C79,t_res_C,$F$52)</f>
-        <v>176.99184801102427</v>
+        <v>176.99184801102425</v>
       </c>
     </row>
-    <row r="80" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="80" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C80">
         <v>286.76900000000001</v>
       </c>
       <c r="D80">
         <f t="array" ref="D80">[1]!PVT_rs_m3m3(C80,t_res_C,$F$52)</f>
-        <v>188.4127229670959</v>
+        <v>188.41272296709593</v>
       </c>
     </row>
-    <row r="81" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="81" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C81">
         <v>300.37700000000001</v>
       </c>
       <c r="D81">
         <f t="array" ref="D81">[1]!PVT_rs_m3m3(C81,t_res_C,$F$52)</f>
-        <v>200.39898108307844</v>
+        <v>200.39898108307841</v>
       </c>
     </row>
-    <row r="82" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="82" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C82">
         <v>313.98500000000001</v>
       </c>
@@ -16727,7 +16727,7 @@
         <v>212.97595563227983</v>
       </c>
     </row>
-    <row r="83" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="83" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C83">
         <v>327.59300000000002</v>
       </c>
@@ -16736,7 +16736,7 @@
         <v>226.16828785320072</v>
       </c>
     </row>
-    <row r="84" spans="3:4" x14ac:dyDescent="0.4">
+    <row r="84" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C84">
         <v>341.20100000000002</v>
       </c>
